--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dvagov-my.sharepoint.com/personal/bernard_chan_va_gov/Documents/Microsoft Teams Chat Files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="32" documentId="11_87A73CECC8785890643FEBC9776139824E07390D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6FBD9288-455B-4BDB-B75A-50160EBB466F}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="11_87A73CECC8785890643FEBC9776139824E07390D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F5AB7BF2-2BC3-4B49-8586-63508233A50F}"/>
   <bookViews>
     <workbookView xWindow="5055" yWindow="1740" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2046" uniqueCount="866">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2046" uniqueCount="869">
   <si>
     <t>category</t>
   </si>
@@ -2618,6 +2618,15 @@
   </si>
   <si>
     <t>D 20</t>
+  </si>
+  <si>
+    <t>100 sensors</t>
+  </si>
+  <si>
+    <t>30 boxes (90)</t>
+  </si>
+  <si>
+    <t>30 sensors</t>
   </si>
 </sst>
 </file>
@@ -2692,6 +2701,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3190,7 +3203,7 @@
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3" t="s">
-        <v>35</v>
+        <v>866</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>36</v>
@@ -3222,7 +3235,7 @@
       </c>
       <c r="F7" s="3"/>
       <c r="G7" s="3" t="s">
-        <v>42</v>
+        <v>867</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>43</v>
@@ -3254,7 +3267,7 @@
       </c>
       <c r="F8" s="3"/>
       <c r="G8" s="3" t="s">
-        <v>35</v>
+        <v>868</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>35</v>
@@ -3286,7 +3299,7 @@
       </c>
       <c r="F9" s="3"/>
       <c r="G9" s="3" t="s">
-        <v>35</v>
+        <v>866</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>36</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,14 +8,30 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dvagov-my.sharepoint.com/personal/bernard_chan_va_gov/Documents/Microsoft Teams Chat Files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="11_87A73CECC8785890643FEBC9776139824E07390D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F5AB7BF2-2BC3-4B49-8586-63508233A50F}"/>
+  <xr:revisionPtr revIDLastSave="41" documentId="11_87A73CECC8785890643FEBC9776139824E07390D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1DC67227-D43E-4D83-9019-D21FCC478F9F}"/>
   <bookViews>
-    <workbookView xWindow="5055" yWindow="1740" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Items" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -127,15 +143,18 @@
     <t>15 days</t>
   </si>
   <si>
+    <t>100 sensors</t>
+  </si>
+  <si>
+    <t>2 sensors</t>
+  </si>
+  <si>
+    <t>1 sensor</t>
+  </si>
+  <si>
     <t>3 sensors</t>
   </si>
   <si>
-    <t>2 sensors</t>
-  </si>
-  <si>
-    <t>1 sensor</t>
-  </si>
-  <si>
     <t>15-day wear = 2 sensors per month.</t>
   </si>
   <si>
@@ -148,15 +167,18 @@
     <t>10 days</t>
   </si>
   <si>
+    <t>30 boxes (90)</t>
+  </si>
+  <si>
+    <t>1 box (3)</t>
+  </si>
+  <si>
+    <t>box of 3</t>
+  </si>
+  <si>
     <t>3 boxes (9)</t>
   </si>
   <si>
-    <t>1 box (3)</t>
-  </si>
-  <si>
-    <t>box of 3</t>
-  </si>
-  <si>
     <t>10-day wear = 3 sensors per month, sold as a 3-pack.</t>
   </si>
   <si>
@@ -166,6 +188,9 @@
     <t>Dexcom G7 Sensor</t>
   </si>
   <si>
+    <t>30 sensors</t>
+  </si>
+  <si>
     <t>10-day wear = 3 sensors per month.</t>
   </si>
   <si>
@@ -178,6 +203,9 @@
     <t>Autosoft 90</t>
   </si>
   <si>
+    <t>43in</t>
+  </si>
+  <si>
     <t>1002818</t>
   </si>
   <si>
@@ -196,13 +224,37 @@
     <t>D 10</t>
   </si>
   <si>
+    <t>23in</t>
+  </si>
+  <si>
+    <t>1002817</t>
+  </si>
+  <si>
+    <t>D 11</t>
+  </si>
+  <si>
     <t>Autosoft XC</t>
   </si>
   <si>
     <t>1001729</t>
   </si>
   <si>
-    <t>D 11</t>
+    <t>D 12</t>
+  </si>
+  <si>
+    <t>32in</t>
+  </si>
+  <si>
+    <t>1003912</t>
+  </si>
+  <si>
+    <t>D 13</t>
+  </si>
+  <si>
+    <t>1001681</t>
+  </si>
+  <si>
+    <t>D 14</t>
   </si>
   <si>
     <t>Autosoft 30</t>
@@ -211,7 +263,7 @@
     <t>1002826</t>
   </si>
   <si>
-    <t>D 12</t>
+    <t>D 15</t>
   </si>
   <si>
     <t>MiniMed Reservoir</t>
@@ -223,7 +275,7 @@
     <t>Reservoir replaced with each ~3-day site change.</t>
   </si>
   <si>
-    <t>D 13</t>
+    <t>D 16</t>
   </si>
   <si>
     <t>MiniMed Misc Supplies</t>
@@ -238,7 +290,7 @@
     <t>Mixed bin; stock and dispense per item.</t>
   </si>
   <si>
-    <t>D 14</t>
+    <t>D 17</t>
   </si>
   <si>
     <t>Contact Detach</t>
@@ -247,7 +299,7 @@
     <t>FG000016-03</t>
   </si>
   <si>
-    <t>D 15</t>
+    <t>D 18</t>
   </si>
   <si>
     <t>T:Slim X2 Cartridge</t>
@@ -262,7 +314,7 @@
     <t>Cartridge replaced every ~3 days = 10/month.</t>
   </si>
   <si>
-    <t>D 16</t>
+    <t>D 19</t>
   </si>
   <si>
     <t>TruSteel Infusion Set</t>
@@ -277,7 +329,7 @@
     <t>Steel cannula sets are changed every ~2 days, so ~15/month.</t>
   </si>
   <si>
-    <t>D 17</t>
+    <t>D 20</t>
   </si>
   <si>
     <t>Alpha-Stim Conduction Solutionn</t>
@@ -382,9 +434,6 @@
     <t>box of 30</t>
   </si>
   <si>
-    <t>Washed and reused ~1 day, so one per day.</t>
-  </si>
-  <si>
     <t>F 6</t>
   </si>
   <si>
@@ -397,9 +446,6 @@
     <t>30</t>
   </si>
   <si>
-    <t>One med syringe per day, washed between doses; sell loose.</t>
-  </si>
-  <si>
     <t>F 7</t>
   </si>
   <si>
@@ -2593,40 +2639,10 @@
     <t>4 boxes (120)</t>
   </si>
   <si>
-    <t>43in</t>
-  </si>
-  <si>
-    <t>23in</t>
-  </si>
-  <si>
-    <t>1002817</t>
-  </si>
-  <si>
-    <t>32in</t>
-  </si>
-  <si>
-    <t>1003912</t>
-  </si>
-  <si>
-    <t>1001681</t>
-  </si>
-  <si>
-    <t>D 18</t>
-  </si>
-  <si>
-    <t>D 19</t>
-  </si>
-  <si>
-    <t>D 20</t>
-  </si>
-  <si>
-    <t>100 sensors</t>
-  </si>
-  <si>
-    <t>30 boxes (90)</t>
-  </si>
-  <si>
-    <t>30 sensors</t>
+    <t>One med syringe every 3 days, washed between doses</t>
+  </si>
+  <si>
+    <t>Washed and reused ~3 days, so one per day.</t>
   </si>
 </sst>
 </file>
@@ -2701,10 +2717,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3203,7 +3215,7 @@
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3" t="s">
-        <v>866</v>
+        <v>35</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>36</v>
@@ -3213,10 +3225,10 @@
         <v>37</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -3225,30 +3237,30 @@
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F7" s="3"/>
       <c r="G7" s="3" t="s">
-        <v>867</v>
+        <v>43</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -3257,30 +3269,30 @@
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F8" s="3"/>
       <c r="G8" s="3" t="s">
-        <v>868</v>
+        <v>50</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I8" s="3"/>
       <c r="J8" s="3" t="s">
         <v>37</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
@@ -3289,17 +3301,17 @@
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>34</v>
       </c>
       <c r="F9" s="3"/>
       <c r="G9" s="3" t="s">
-        <v>866</v>
+        <v>35</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>36</v>
@@ -3309,10 +3321,10 @@
         <v>37</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
@@ -3321,32 +3333,32 @@
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>857</v>
+        <v>55</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="I10" s="3"/>
       <c r="J10" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -3355,32 +3367,32 @@
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G11" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>858</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>859</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="H11" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="I11" s="3"/>
       <c r="J11" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
@@ -3389,32 +3401,32 @@
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D12" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="H12" s="3" t="s">
         <v>58</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>857</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>54</v>
       </c>
       <c r="I12" s="3"/>
       <c r="J12" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
@@ -3423,31 +3435,31 @@
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D13" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="H13" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>860</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>861</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="J13" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
@@ -3456,31 +3468,31 @@
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D14" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="H14" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>858</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>862</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="J14" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
@@ -3492,29 +3504,29 @@
         <v>72</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>857</v>
+        <v>55</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="I15" s="3"/>
       <c r="J15" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
@@ -3526,27 +3538,27 @@
         <v>75</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="I16" s="3"/>
       <c r="J16" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
@@ -3555,28 +3567,28 @@
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>80</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>68</v>
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="I17" s="3"/>
       <c r="J17" s="3" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
@@ -3585,30 +3597,30 @@
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>85</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>73</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="I18" s="3"/>
       <c r="J18" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
@@ -3617,32 +3629,32 @@
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="3" t="s">
-        <v>863</v>
+        <v>87</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="I19" s="3"/>
       <c r="J19" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
@@ -3651,30 +3663,30 @@
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="3" t="s">
-        <v>864</v>
+        <v>92</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I20" s="3"/>
       <c r="J20" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
@@ -3683,218 +3695,218 @@
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3" t="s">
-        <v>865</v>
+        <v>97</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="I21" s="3"/>
       <c r="J21" s="3" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="3" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="E22" s="3"/>
       <c r="F22" s="3" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="I22" s="3"/>
       <c r="J22" s="3" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="3" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="I23" s="3"/>
       <c r="J23" s="3" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="B24" s="3"/>
       <c r="C24" s="3" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="I24" s="3"/>
       <c r="J24" s="3" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="3" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="I25" s="3"/>
       <c r="J25" s="3" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="B26" s="3"/>
       <c r="C26" s="3" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>118</v>
+        <v>402</v>
       </c>
       <c r="I26" s="3"/>
       <c r="J26" s="3" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>120</v>
+        <v>868</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="B27" s="3"/>
       <c r="C27" s="3" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>124</v>
+        <v>402</v>
       </c>
       <c r="I27" s="3"/>
       <c r="J27" s="3" t="s">
@@ -3904,1409 +3916,1409 @@
         <v>17</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>125</v>
+        <v>867</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="3" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="I28" s="3"/>
       <c r="J28" s="3" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="3" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="I29" s="3"/>
       <c r="J29" s="3" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="B30" s="3"/>
       <c r="C30" s="3" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="I30" s="3"/>
       <c r="J30" s="3" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="3" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="I31" s="3"/>
       <c r="J31" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="B32" s="3"/>
       <c r="C32" s="3" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="I32" s="3"/>
       <c r="J32" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L32" s="3" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="B33" s="3"/>
       <c r="C33" s="3" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="I33" s="3"/>
       <c r="J33" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="B34" s="3"/>
       <c r="C34" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="E34" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="D34" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>141</v>
-      </c>
       <c r="F34" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="G34" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="G34" s="3" t="s">
-        <v>143</v>
-      </c>
       <c r="H34" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="I34" s="3"/>
       <c r="J34" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L34" s="3" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="B35" s="3"/>
       <c r="C35" s="3" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="I35" s="3"/>
       <c r="J35" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L35" s="3" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="B36" s="3"/>
       <c r="C36" s="3" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I36" s="3"/>
       <c r="J36" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L36" s="3" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="B37" s="3"/>
       <c r="C37" s="3" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I37" s="3"/>
       <c r="J37" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="B38" s="3"/>
       <c r="C38" s="3" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="D38" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="E38" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="E38" s="3" t="s">
-        <v>149</v>
-      </c>
       <c r="F38" s="3" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I38" s="3"/>
       <c r="J38" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L38" s="3" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="B39" s="3"/>
       <c r="C39" s="3" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I39" s="3"/>
       <c r="J39" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L39" s="3" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="B40" s="3"/>
       <c r="C40" s="3" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="D40" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G40" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="E40" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>157</v>
-      </c>
       <c r="H40" s="3" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I40" s="3"/>
       <c r="J40" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L40" s="3" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="B41" s="3"/>
       <c r="C41" s="3" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="D41" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="G41" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="E41" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>157</v>
-      </c>
       <c r="H41" s="3" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I41" s="3"/>
       <c r="J41" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L41" s="3" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="B42" s="3"/>
       <c r="C42" s="3" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="E42" s="3"/>
       <c r="F42" s="3" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I42" s="3"/>
       <c r="J42" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L42" s="3" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="B43" s="3"/>
       <c r="C43" s="3" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="E43" s="3"/>
       <c r="F43" s="3" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I43" s="3"/>
       <c r="J43" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L43" s="3" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="B44" s="3"/>
       <c r="C44" s="3" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="I44" s="3"/>
       <c r="J44" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L44" s="3" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="B45" s="3"/>
       <c r="C45" s="3" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="I45" s="3"/>
       <c r="J45" s="3" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="L45" s="3" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="B46" s="3"/>
       <c r="C46" s="3" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="I46" s="3"/>
       <c r="J46" s="3" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="K46" s="3" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="L46" s="3" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="B47" s="3"/>
       <c r="C47" s="3" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="E47" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="H47" s="3" t="s">
         <v>202</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>192</v>
       </c>
       <c r="I47" s="3"/>
       <c r="J47" s="3" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="L47" s="3" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="B48" s="3"/>
       <c r="C48" s="3" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="E48" s="3"/>
       <c r="F48" s="3" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="I48" s="3"/>
       <c r="J48" s="3" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="K48" s="3" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="L48" s="3" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="B49" s="3"/>
       <c r="C49" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="E49" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="E49" s="3" t="s">
+      <c r="F49" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="H49" s="3" t="s">
         <v>202</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>192</v>
       </c>
       <c r="I49" s="3"/>
       <c r="J49" s="3" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="L49" s="3" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="B50" s="3"/>
       <c r="C50" s="3" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="I50" s="3"/>
       <c r="J50" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L50" s="3" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="B51" s="3"/>
       <c r="C51" s="3" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="I51" s="3"/>
       <c r="J51" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K51" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L51" s="3" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="B52" s="3"/>
       <c r="C52" s="3" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="I52" s="3"/>
       <c r="J52" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L52" s="3" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="B53" s="3"/>
       <c r="C53" s="3" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="I53" s="3"/>
       <c r="J53" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L53" s="3" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="B54" s="3"/>
       <c r="C54" s="3" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="I54" s="3"/>
       <c r="J54" s="3" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="K54" s="3" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="L54" s="3" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="B55" s="3"/>
       <c r="C55" s="3" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="I55" s="3"/>
       <c r="J55" s="3" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="K55" s="3" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="L55" s="3" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="B56" s="3"/>
       <c r="C56" s="3" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="I56" s="3"/>
       <c r="J56" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K56" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L56" s="3" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="B57" s="3"/>
       <c r="C57" s="3" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="F57" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="G57" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>242</v>
-      </c>
       <c r="H57" s="3" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="I57" s="3"/>
       <c r="J57" s="3" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="K57" s="3" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="L57" s="3" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="B58" s="3"/>
       <c r="C58" s="3" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="I58" s="3"/>
       <c r="J58" s="3" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="K58" s="3" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="L58" s="3" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="B59" s="3"/>
       <c r="C59" s="3" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="I59" s="3"/>
       <c r="J59" s="3" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="K59" s="3" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="L59" s="3" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="B60" s="3"/>
       <c r="C60" s="3" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="I60" s="3"/>
       <c r="J60" s="3" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="K60" s="3" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="L60" s="3" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="B61" s="3"/>
       <c r="C61" s="3" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="I61" s="3"/>
       <c r="J61" s="3" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="K61" s="3" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="L61" s="3" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="B62" s="3"/>
       <c r="C62" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="E62" s="3" t="s">
         <v>273</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>263</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="I62" s="3"/>
       <c r="J62" s="3" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="K62" s="3" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="L62" s="3" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="B63" s="3"/>
       <c r="C63" s="3" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="I63" s="3"/>
       <c r="J63" s="3" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="K63" s="3" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="L63" s="3" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="B64" s="3"/>
       <c r="C64" s="3" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="I64" s="3"/>
       <c r="J64" s="3" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="K64" s="3" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="L64" s="3" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="B65" s="3"/>
       <c r="C65" s="3" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="I65" s="3"/>
       <c r="J65" s="3" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="K65" s="3" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="L65" s="3" t="s">
-        <v>291</v>
+        <v>301</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="B66" s="3"/>
       <c r="C66" s="3" t="s">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="D66" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="E66" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="E66" s="3" t="s">
-        <v>283</v>
-      </c>
       <c r="F66" s="3" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="I66" s="3"/>
       <c r="J66" s="3" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="L66" s="3" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="B67" s="3"/>
       <c r="C67" s="3" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="I67" s="3"/>
       <c r="J67" s="3" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="K67" s="3" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="L67" s="3" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="B68" s="3"/>
       <c r="C68" s="3" t="s">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="I68" s="3"/>
       <c r="J68" s="3" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="K68" s="3" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="L68" s="3" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="B69" s="3"/>
       <c r="C69" s="3" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I69" s="3"/>
       <c r="J69" s="3" t="s">
@@ -5316,29 +5328,29 @@
         <v>17</v>
       </c>
       <c r="L69" s="3" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="B70" s="3"/>
       <c r="C70" s="3" t="s">
-        <v>306</v>
+        <v>316</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I70" s="3"/>
       <c r="J70" s="3" t="s">
@@ -5348,29 +5360,29 @@
         <v>17</v>
       </c>
       <c r="L70" s="3" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="B71" s="3"/>
       <c r="C71" s="3" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I71" s="3"/>
       <c r="J71" s="3" t="s">
@@ -5380,22 +5392,22 @@
         <v>17</v>
       </c>
       <c r="L71" s="3" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="B72" s="3"/>
       <c r="C72" s="3" t="s">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
@@ -5410,22 +5422,22 @@
         <v>16</v>
       </c>
       <c r="L72" s="3" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="B73" s="3"/>
       <c r="C73" s="3" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
@@ -5440,29 +5452,29 @@
         <v>16</v>
       </c>
       <c r="L73" s="3" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="B74" s="3"/>
       <c r="C74" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="D74" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="D74" s="3" t="s">
-        <v>307</v>
-      </c>
       <c r="E74" s="3" t="s">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I74" s="3"/>
       <c r="J74" s="3" t="s">
@@ -5472,86 +5484,86 @@
         <v>17</v>
       </c>
       <c r="L74" s="3" t="s">
-        <v>319</v>
+        <v>329</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="B75" s="3"/>
       <c r="C75" s="3" t="s">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I75" s="3"/>
       <c r="J75" s="3" t="s">
         <v>30</v>
       </c>
       <c r="K75" s="3" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="L75" s="3" t="s">
-        <v>319</v>
+        <v>329</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="B76" s="3"/>
       <c r="C76" s="3" t="s">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I76" s="3"/>
       <c r="J76" s="3" t="s">
         <v>30</v>
       </c>
       <c r="K76" s="3" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="L76" s="3" t="s">
-        <v>319</v>
+        <v>329</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="B77" s="3"/>
       <c r="C77" s="3" t="s">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
@@ -5566,22 +5578,22 @@
         <v>17</v>
       </c>
       <c r="L77" s="3" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="B78" s="3"/>
       <c r="C78" s="3" t="s">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
@@ -5596,22 +5608,22 @@
         <v>17</v>
       </c>
       <c r="L78" s="3" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="B79" s="3"/>
       <c r="C79" s="3" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
@@ -5626,22 +5638,22 @@
         <v>17</v>
       </c>
       <c r="L79" s="3" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="B80" s="3"/>
       <c r="C80" s="3" t="s">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
@@ -5656,22 +5668,22 @@
         <v>17</v>
       </c>
       <c r="L80" s="3" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="B81" s="3"/>
       <c r="C81" s="3" t="s">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
@@ -5686,22 +5698,22 @@
         <v>17</v>
       </c>
       <c r="L81" s="3" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="B82" s="3"/>
       <c r="C82" s="3" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
@@ -5716,22 +5728,22 @@
         <v>17</v>
       </c>
       <c r="L82" s="3" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="B83" s="3"/>
       <c r="C83" s="3" t="s">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
@@ -5746,22 +5758,22 @@
         <v>17</v>
       </c>
       <c r="L83" s="3" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="B84" s="3"/>
       <c r="C84" s="3" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
@@ -5776,22 +5788,22 @@
         <v>17</v>
       </c>
       <c r="L84" s="3" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="B85" s="3"/>
       <c r="C85" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="D85" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="D85" s="3" t="s">
-        <v>334</v>
-      </c>
       <c r="E85" s="3" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
@@ -5806,22 +5818,22 @@
         <v>17</v>
       </c>
       <c r="L85" s="3" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="B86" s="3"/>
       <c r="C86" s="3" t="s">
-        <v>346</v>
+        <v>356</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
@@ -5836,22 +5848,22 @@
         <v>17</v>
       </c>
       <c r="L86" s="3" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="B87" s="3"/>
       <c r="C87" s="3" t="s">
-        <v>348</v>
+        <v>358</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="F87" s="3"/>
       <c r="G87" s="3" t="s">
@@ -5866,22 +5878,22 @@
         <v>17</v>
       </c>
       <c r="L87" s="3" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="B88" s="3"/>
       <c r="C88" s="3" t="s">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="F88" s="3"/>
       <c r="G88" s="3" t="s">
@@ -5896,22 +5908,22 @@
         <v>17</v>
       </c>
       <c r="L88" s="3" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="B89" s="3"/>
       <c r="C89" s="3" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="F89" s="3"/>
       <c r="G89" s="3" t="s">
@@ -5926,22 +5938,22 @@
         <v>17</v>
       </c>
       <c r="L89" s="3" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="B90" s="3"/>
       <c r="C90" s="3" t="s">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="F90" s="3"/>
       <c r="G90" s="3" t="s">
@@ -5956,22 +5968,22 @@
         <v>17</v>
       </c>
       <c r="L90" s="3" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="B91" s="3"/>
       <c r="C91" s="3" t="s">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
@@ -5986,22 +5998,22 @@
         <v>17</v>
       </c>
       <c r="L91" s="3" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="B92" s="3"/>
       <c r="C92" s="3" t="s">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="F92" s="3"/>
       <c r="G92" s="3" t="s">
@@ -6016,22 +6028,22 @@
         <v>17</v>
       </c>
       <c r="L92" s="3" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="B93" s="3"/>
       <c r="C93" s="3" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="F93" s="3"/>
       <c r="G93" s="3" t="s">
@@ -6046,22 +6058,22 @@
         <v>17</v>
       </c>
       <c r="L93" s="3" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="B94" s="3"/>
       <c r="C94" s="3" t="s">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="F94" s="3"/>
       <c r="G94" s="3" t="s">
@@ -6076,22 +6088,22 @@
         <v>17</v>
       </c>
       <c r="L94" s="3" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="B95" s="3"/>
       <c r="C95" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="D95" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="D95" s="3" t="s">
-        <v>355</v>
-      </c>
       <c r="E95" s="3" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="F95" s="3"/>
       <c r="G95" s="3" t="s">
@@ -6106,86 +6118,86 @@
         <v>17</v>
       </c>
       <c r="L95" s="3" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="B96" s="3"/>
       <c r="C96" s="3" t="s">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="F96" s="3"/>
       <c r="G96" s="3" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="I96" s="3"/>
       <c r="J96" s="3" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="K96" s="3" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="L96" s="3" t="s">
-        <v>370</v>
+        <v>380</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="B97" s="3"/>
       <c r="C97" s="3" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="F97" s="3"/>
       <c r="G97" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I97" s="3"/>
       <c r="J97" s="3" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="K97" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="L97" s="3" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="B98" s="3"/>
       <c r="C98" s="3" t="s">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="F98" s="3"/>
       <c r="G98" s="3" t="s">
@@ -6200,22 +6212,22 @@
         <v>17</v>
       </c>
       <c r="L98" s="3" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="B99" s="3"/>
       <c r="C99" s="3" t="s">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="F99" s="3"/>
       <c r="G99" s="3" t="s">
@@ -6230,22 +6242,22 @@
         <v>17</v>
       </c>
       <c r="L99" s="3" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="B100" s="3"/>
       <c r="C100" s="3" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="F100" s="3"/>
       <c r="G100" s="3" t="s">
@@ -6260,490 +6272,490 @@
         <v>17</v>
       </c>
       <c r="L100" s="3" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="B101" s="3"/>
       <c r="C101" s="3" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="F101" s="3" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="G101" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I101" s="3"/>
       <c r="J101" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K101" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L101" s="3" t="s">
-        <v>384</v>
+        <v>394</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="B102" s="3"/>
       <c r="C102" s="3" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>386</v>
+        <v>396</v>
       </c>
       <c r="F102" s="3" t="s">
-        <v>387</v>
+        <v>397</v>
       </c>
       <c r="G102" s="3" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="I102" s="3"/>
       <c r="J102" s="3" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="K102" s="3" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="L102" s="3" t="s">
-        <v>388</v>
+        <v>398</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="B103" s="3"/>
       <c r="C103" s="3" t="s">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="E103" s="3"/>
       <c r="F103" s="3" t="s">
-        <v>391</v>
+        <v>401</v>
       </c>
       <c r="G103" s="3" t="s">
-        <v>392</v>
+        <v>402</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>392</v>
+        <v>402</v>
       </c>
       <c r="I103" s="3"/>
       <c r="J103" s="3" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="K103" s="3" t="s">
-        <v>392</v>
+        <v>402</v>
       </c>
       <c r="L103" s="3" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="B104" s="3"/>
       <c r="C104" s="3" t="s">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>396</v>
+        <v>406</v>
       </c>
       <c r="F104" s="3" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="G104" s="3" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="I104" s="3"/>
       <c r="J104" s="3" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="K104" s="3" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="L104" s="3" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="B105" s="3"/>
       <c r="C105" s="3" t="s">
-        <v>402</v>
+        <v>412</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="F105" s="3" t="s">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="G105" s="3" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="I105" s="3"/>
       <c r="J105" s="3" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="K105" s="3" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="L105" s="3" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="B106" s="3"/>
       <c r="C106" s="3" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="E106" s="3"/>
       <c r="F106" s="3" t="s">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="G106" s="3" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="I106" s="3"/>
       <c r="J106" s="3" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="K106" s="3" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="L106" s="3" t="s">
-        <v>408</v>
+        <v>418</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="B107" s="3"/>
       <c r="C107" s="3" t="s">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>411</v>
+        <v>421</v>
       </c>
       <c r="F107" s="3" t="s">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="G107" s="3" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="H107" s="3" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="I107" s="3"/>
       <c r="J107" s="3" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="K107" s="3" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="L107" s="3" t="s">
-        <v>413</v>
+        <v>423</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="B108" s="3"/>
       <c r="C108" s="3" t="s">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="F108" s="3" t="s">
-        <v>416</v>
+        <v>426</v>
       </c>
       <c r="G108" s="3" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="H108" s="3" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="I108" s="3"/>
       <c r="J108" s="3" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="K108" s="3" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="L108" s="3" t="s">
-        <v>413</v>
+        <v>423</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="B109" s="3"/>
       <c r="C109" s="3" t="s">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>418</v>
+        <v>428</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>419</v>
+        <v>429</v>
       </c>
       <c r="F109" s="3" t="s">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="G109" s="3" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="H109" s="3" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="I109" s="3"/>
       <c r="J109" s="3" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="K109" s="3" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="L109" s="3" t="s">
-        <v>413</v>
+        <v>423</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="B110" s="3"/>
       <c r="C110" s="3" t="s">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>422</v>
+        <v>432</v>
       </c>
       <c r="E110" s="3"/>
       <c r="F110" s="3" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="G110" s="3" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="I110" s="3"/>
       <c r="J110" s="3" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="K110" s="3" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="L110" s="3" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="B111" s="3"/>
       <c r="C111" s="3" t="s">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="E111" s="3"/>
       <c r="F111" s="3" t="s">
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="G111" s="3" t="s">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="H111" s="3" t="s">
-        <v>429</v>
+        <v>439</v>
       </c>
       <c r="I111" s="3"/>
       <c r="J111" s="3" t="s">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="K111" s="3" t="s">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="L111" s="3" t="s">
-        <v>431</v>
+        <v>441</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="B112" s="3"/>
       <c r="C112" s="3" t="s">
-        <v>432</v>
+        <v>442</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>433</v>
+        <v>443</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>434</v>
+        <v>444</v>
       </c>
       <c r="F112" s="3" t="s">
-        <v>435</v>
+        <v>445</v>
       </c>
       <c r="G112" s="3" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="H112" s="3" t="s">
-        <v>436</v>
+        <v>446</v>
       </c>
       <c r="I112" s="3"/>
       <c r="J112" s="3" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="K112" s="3" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="L112" s="3" t="s">
-        <v>437</v>
+        <v>447</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="B113" s="3"/>
       <c r="C113" s="3" t="s">
-        <v>438</v>
+        <v>448</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>439</v>
+        <v>449</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>440</v>
+        <v>450</v>
       </c>
       <c r="F113" s="3" t="s">
-        <v>441</v>
+        <v>451</v>
       </c>
       <c r="G113" s="3" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="H113" s="3" t="s">
-        <v>443</v>
+        <v>453</v>
       </c>
       <c r="I113" s="3"/>
       <c r="J113" s="3" t="s">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="K113" s="3" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="L113" s="3" t="s">
-        <v>445</v>
+        <v>455</v>
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="B114" s="3"/>
       <c r="C114" s="3" t="s">
-        <v>446</v>
+        <v>456</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>439</v>
+        <v>449</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>447</v>
+        <v>457</v>
       </c>
       <c r="F114" s="3" t="s">
-        <v>448</v>
+        <v>458</v>
       </c>
       <c r="G114" s="3" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="H114" s="3" t="s">
-        <v>443</v>
+        <v>453</v>
       </c>
       <c r="I114" s="3"/>
       <c r="J114" s="3" t="s">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="K114" s="3" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="L114" s="3" t="s">
-        <v>449</v>
+        <v>459</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="B115" s="3"/>
       <c r="C115" s="3" t="s">
-        <v>451</v>
+        <v>461</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>452</v>
+        <v>462</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>453</v>
+        <v>463</v>
       </c>
       <c r="F115" s="3"/>
       <c r="G115" s="3" t="s">
@@ -6760,422 +6772,422 @@
         <v>16</v>
       </c>
       <c r="L115" s="3" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="B116" s="3"/>
       <c r="C116" s="3" t="s">
-        <v>455</v>
+        <v>465</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>456</v>
+        <v>466</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>457</v>
+        <v>467</v>
       </c>
       <c r="F116" s="3" t="s">
-        <v>458</v>
+        <v>468</v>
       </c>
       <c r="G116" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H116" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="I116" s="3"/>
       <c r="J116" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K116" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L116" s="3" t="s">
-        <v>459</v>
+        <v>469</v>
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="B117" s="3"/>
       <c r="C117" s="3" t="s">
-        <v>460</v>
+        <v>470</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>461</v>
+        <v>471</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>462</v>
+        <v>472</v>
       </c>
       <c r="F117" s="3" t="s">
-        <v>463</v>
+        <v>473</v>
       </c>
       <c r="G117" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H117" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="I117" s="3"/>
       <c r="J117" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K117" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L117" s="3" t="s">
-        <v>464</v>
+        <v>474</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="B118" s="3"/>
       <c r="C118" s="3" t="s">
-        <v>465</v>
+        <v>475</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>461</v>
+        <v>471</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>466</v>
+        <v>476</v>
       </c>
       <c r="F118" s="3" t="s">
-        <v>467</v>
+        <v>477</v>
       </c>
       <c r="G118" s="3" t="s">
-        <v>468</v>
+        <v>478</v>
       </c>
       <c r="H118" s="3" t="s">
-        <v>469</v>
+        <v>479</v>
       </c>
       <c r="I118" s="3"/>
       <c r="J118" s="3" t="s">
-        <v>470</v>
+        <v>480</v>
       </c>
       <c r="K118" s="3" t="s">
-        <v>468</v>
+        <v>478</v>
       </c>
       <c r="L118" s="3" t="s">
-        <v>464</v>
+        <v>474</v>
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="B119" s="3"/>
       <c r="C119" s="3" t="s">
-        <v>471</v>
+        <v>481</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>472</v>
+        <v>482</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>473</v>
+        <v>483</v>
       </c>
       <c r="F119" s="3" t="s">
-        <v>474</v>
+        <v>484</v>
       </c>
       <c r="G119" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H119" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="I119" s="3"/>
       <c r="J119" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K119" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L119" s="3" t="s">
-        <v>464</v>
+        <v>474</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="B120" s="3"/>
       <c r="C120" s="3" t="s">
-        <v>475</v>
+        <v>485</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>476</v>
+        <v>486</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>477</v>
+        <v>487</v>
       </c>
       <c r="F120" s="3" t="s">
-        <v>478</v>
+        <v>488</v>
       </c>
       <c r="G120" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H120" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="I120" s="3"/>
       <c r="J120" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K120" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L120" s="3" t="s">
-        <v>479</v>
+        <v>489</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="B121" s="3"/>
       <c r="C121" s="3" t="s">
-        <v>480</v>
+        <v>490</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>476</v>
+        <v>486</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>481</v>
+        <v>491</v>
       </c>
       <c r="F121" s="3" t="s">
-        <v>482</v>
+        <v>492</v>
       </c>
       <c r="G121" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H121" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="I121" s="3"/>
       <c r="J121" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K121" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L121" s="3" t="s">
-        <v>479</v>
+        <v>489</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="B122" s="3"/>
       <c r="C122" s="3" t="s">
-        <v>483</v>
+        <v>493</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>484</v>
+        <v>494</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>462</v>
+        <v>472</v>
       </c>
       <c r="F122" s="3" t="s">
-        <v>485</v>
+        <v>495</v>
       </c>
       <c r="G122" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H122" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="I122" s="3"/>
       <c r="J122" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K122" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L122" s="3" t="s">
-        <v>486</v>
+        <v>496</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A123" s="3" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="B123" s="3"/>
       <c r="C123" s="3" t="s">
-        <v>487</v>
+        <v>497</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>488</v>
+        <v>498</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>466</v>
+        <v>476</v>
       </c>
       <c r="F123" s="3" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
       <c r="G123" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H123" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="I123" s="3"/>
       <c r="J123" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K123" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L123" s="3" t="s">
-        <v>464</v>
+        <v>474</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="B124" s="3"/>
       <c r="C124" s="3" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>491</v>
+        <v>501</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>492</v>
+        <v>502</v>
       </c>
       <c r="F124" s="3"/>
       <c r="G124" s="3" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="H124" s="3" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="I124" s="3"/>
       <c r="J124" s="3" t="s">
-        <v>494</v>
+        <v>504</v>
       </c>
       <c r="K124" s="3" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="L124" s="3" t="s">
-        <v>495</v>
+        <v>505</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A125" s="3" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="B125" s="3"/>
       <c r="C125" s="3" t="s">
-        <v>496</v>
+        <v>506</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>498</v>
+        <v>508</v>
       </c>
       <c r="F125" s="3"/>
       <c r="G125" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H125" s="3" t="s">
-        <v>436</v>
+        <v>446</v>
       </c>
       <c r="I125" s="3"/>
       <c r="J125" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K125" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="L125" s="3" t="s">
-        <v>499</v>
+        <v>509</v>
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="B126" s="3"/>
       <c r="C126" s="3" t="s">
-        <v>500</v>
+        <v>510</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>501</v>
+        <v>511</v>
       </c>
       <c r="F126" s="3"/>
       <c r="G126" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H126" s="3" t="s">
-        <v>436</v>
+        <v>446</v>
       </c>
       <c r="I126" s="3"/>
       <c r="J126" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K126" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="L126" s="3" t="s">
-        <v>499</v>
+        <v>509</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="B127" s="3"/>
       <c r="C127" s="3" t="s">
-        <v>502</v>
+        <v>512</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>503</v>
+        <v>513</v>
       </c>
       <c r="F127" s="3"/>
       <c r="G127" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H127" s="3" t="s">
-        <v>436</v>
+        <v>446</v>
       </c>
       <c r="I127" s="3"/>
       <c r="J127" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K127" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="L127" s="3" t="s">
-        <v>499</v>
+        <v>509</v>
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="B128" s="3"/>
       <c r="C128" s="3" t="s">
-        <v>504</v>
+        <v>514</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>452</v>
+        <v>462</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>505</v>
+        <v>515</v>
       </c>
       <c r="F128" s="3"/>
       <c r="G128" s="3" t="s">
@@ -7192,594 +7204,594 @@
         <v>16</v>
       </c>
       <c r="L128" s="3" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A129" s="3" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="B129" s="3"/>
       <c r="C129" s="3" t="s">
-        <v>506</v>
+        <v>516</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>507</v>
+        <v>517</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>462</v>
+        <v>472</v>
       </c>
       <c r="F129" s="3" t="s">
-        <v>508</v>
+        <v>518</v>
       </c>
       <c r="G129" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H129" s="3" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I129" s="3"/>
       <c r="J129" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K129" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L129" s="3" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A130" s="3" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="B130" s="3"/>
       <c r="C130" s="3" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>507</v>
+        <v>517</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>511</v>
+        <v>521</v>
       </c>
       <c r="F130" s="3" t="s">
-        <v>512</v>
+        <v>522</v>
       </c>
       <c r="G130" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H130" s="3" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I130" s="3"/>
       <c r="J130" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K130" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L130" s="3" t="s">
-        <v>513</v>
+        <v>523</v>
       </c>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A131" s="3" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="B131" s="3"/>
       <c r="C131" s="3" t="s">
-        <v>514</v>
+        <v>524</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>515</v>
+        <v>525</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>516</v>
+        <v>526</v>
       </c>
       <c r="F131" s="3" t="s">
-        <v>517</v>
+        <v>527</v>
       </c>
       <c r="G131" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H131" s="3" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I131" s="3"/>
       <c r="J131" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K131" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L131" s="3" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="B132" s="3"/>
       <c r="C132" s="3" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>515</v>
+        <v>525</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>462</v>
+        <v>472</v>
       </c>
       <c r="F132" s="3" t="s">
-        <v>519</v>
+        <v>529</v>
       </c>
       <c r="G132" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H132" s="3" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I132" s="3"/>
       <c r="J132" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K132" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L132" s="3" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A133" s="3" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="B133" s="3"/>
       <c r="C133" s="3" t="s">
-        <v>520</v>
+        <v>530</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>515</v>
+        <v>525</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>521</v>
+        <v>531</v>
       </c>
       <c r="F133" s="3" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="G133" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H133" s="3" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I133" s="3"/>
       <c r="J133" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K133" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L133" s="3" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A134" s="3" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="B134" s="3"/>
       <c r="C134" s="3" t="s">
-        <v>523</v>
+        <v>533</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>524</v>
+        <v>534</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>525</v>
+        <v>535</v>
       </c>
       <c r="F134" s="3" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="G134" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H134" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="I134" s="3"/>
       <c r="J134" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K134" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L134" s="3" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="B135" s="3"/>
       <c r="C135" s="3" t="s">
-        <v>528</v>
+        <v>538</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>529</v>
+        <v>539</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>530</v>
+        <v>540</v>
       </c>
       <c r="F135" s="3" t="s">
-        <v>531</v>
+        <v>541</v>
       </c>
       <c r="G135" s="3" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="H135" s="3" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="I135" s="3"/>
       <c r="J135" s="3" t="s">
-        <v>532</v>
+        <v>542</v>
       </c>
       <c r="K135" s="3" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="L135" s="3" t="s">
-        <v>533</v>
+        <v>543</v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A136" s="3" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="B136" s="3"/>
       <c r="C136" s="3" t="s">
-        <v>534</v>
+        <v>544</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>535</v>
+        <v>545</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>536</v>
+        <v>546</v>
       </c>
       <c r="F136" s="3" t="s">
-        <v>537</v>
+        <v>547</v>
       </c>
       <c r="G136" s="3" t="s">
-        <v>538</v>
+        <v>548</v>
       </c>
       <c r="H136" s="3" t="s">
-        <v>539</v>
+        <v>549</v>
       </c>
       <c r="I136" s="3"/>
       <c r="J136" s="3" t="s">
-        <v>540</v>
+        <v>550</v>
       </c>
       <c r="K136" s="3" t="s">
-        <v>538</v>
+        <v>548</v>
       </c>
       <c r="L136" s="3" t="s">
-        <v>541</v>
+        <v>551</v>
       </c>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="B137" s="3"/>
       <c r="C137" s="3" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>535</v>
+        <v>545</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>543</v>
+        <v>553</v>
       </c>
       <c r="F137" s="3" t="s">
-        <v>544</v>
+        <v>554</v>
       </c>
       <c r="G137" s="3" t="s">
-        <v>545</v>
+        <v>555</v>
       </c>
       <c r="H137" s="3" t="s">
-        <v>539</v>
+        <v>549</v>
       </c>
       <c r="I137" s="3"/>
       <c r="J137" s="3" t="s">
-        <v>546</v>
+        <v>556</v>
       </c>
       <c r="K137" s="3" t="s">
-        <v>545</v>
+        <v>555</v>
       </c>
       <c r="L137" s="3" t="s">
-        <v>541</v>
+        <v>551</v>
       </c>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A138" s="3" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="B138" s="3"/>
       <c r="C138" s="3" t="s">
-        <v>547</v>
+        <v>557</v>
       </c>
       <c r="D138" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="E138" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="F138" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="G138" s="3" t="s">
         <v>548</v>
       </c>
-      <c r="E138" s="3" t="s">
-        <v>536</v>
-      </c>
-      <c r="F138" s="3" t="s">
+      <c r="H138" s="3" t="s">
         <v>549</v>
-      </c>
-      <c r="G138" s="3" t="s">
-        <v>538</v>
-      </c>
-      <c r="H138" s="3" t="s">
-        <v>539</v>
       </c>
       <c r="I138" s="3"/>
       <c r="J138" s="3" t="s">
-        <v>540</v>
+        <v>550</v>
       </c>
       <c r="K138" s="3" t="s">
-        <v>538</v>
+        <v>548</v>
       </c>
       <c r="L138" s="3" t="s">
-        <v>541</v>
+        <v>551</v>
       </c>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A139" s="3" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="B139" s="3"/>
       <c r="C139" s="3" t="s">
-        <v>550</v>
+        <v>560</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>548</v>
+        <v>558</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>543</v>
+        <v>553</v>
       </c>
       <c r="F139" s="3" t="s">
-        <v>551</v>
+        <v>561</v>
       </c>
       <c r="G139" s="3" t="s">
-        <v>545</v>
+        <v>555</v>
       </c>
       <c r="H139" s="3" t="s">
-        <v>539</v>
+        <v>549</v>
       </c>
       <c r="I139" s="3"/>
       <c r="J139" s="3" t="s">
-        <v>546</v>
+        <v>556</v>
       </c>
       <c r="K139" s="3" t="s">
-        <v>545</v>
+        <v>555</v>
       </c>
       <c r="L139" s="3" t="s">
-        <v>541</v>
+        <v>551</v>
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A140" s="3" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="B140" s="3"/>
       <c r="C140" s="3" t="s">
-        <v>552</v>
+        <v>562</v>
       </c>
       <c r="D140" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="E140" s="3" t="s">
         <v>553</v>
       </c>
-      <c r="E140" s="3" t="s">
-        <v>543</v>
-      </c>
       <c r="F140" s="3" t="s">
-        <v>554</v>
+        <v>564</v>
       </c>
       <c r="G140" s="3" t="s">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="H140" s="3" t="s">
-        <v>429</v>
+        <v>439</v>
       </c>
       <c r="I140" s="3"/>
       <c r="J140" s="3" t="s">
-        <v>555</v>
+        <v>565</v>
       </c>
       <c r="K140" s="3" t="s">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="L140" s="3" t="s">
-        <v>556</v>
+        <v>566</v>
       </c>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A141" s="3" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="B141" s="3"/>
       <c r="C141" s="3" t="s">
-        <v>557</v>
+        <v>567</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>553</v>
+        <v>563</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>501</v>
+        <v>511</v>
       </c>
       <c r="F141" s="3" t="s">
-        <v>558</v>
+        <v>568</v>
       </c>
       <c r="G141" s="3" t="s">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="H141" s="3" t="s">
-        <v>429</v>
+        <v>439</v>
       </c>
       <c r="I141" s="3"/>
       <c r="J141" s="3" t="s">
-        <v>555</v>
+        <v>565</v>
       </c>
       <c r="K141" s="3" t="s">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="L141" s="3" t="s">
-        <v>556</v>
+        <v>566</v>
       </c>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A142" s="3" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="B142" s="3"/>
       <c r="C142" s="3" t="s">
-        <v>559</v>
+        <v>569</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>560</v>
+        <v>570</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>561</v>
+        <v>571</v>
       </c>
       <c r="F142" s="3" t="s">
-        <v>562</v>
+        <v>572</v>
       </c>
       <c r="G142" s="3" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="H142" s="3" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I142" s="3"/>
       <c r="J142" s="3" t="s">
         <v>30</v>
       </c>
       <c r="K142" s="3" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="L142" s="3" t="s">
-        <v>563</v>
+        <v>573</v>
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A143" s="3" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="B143" s="3"/>
       <c r="C143" s="3" t="s">
-        <v>564</v>
+        <v>574</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>565</v>
+        <v>575</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>566</v>
+        <v>576</v>
       </c>
       <c r="F143" s="3"/>
       <c r="G143" s="3" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="H143" s="3" t="s">
-        <v>567</v>
+        <v>577</v>
       </c>
       <c r="I143" s="3"/>
       <c r="J143" s="3" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="K143" s="3" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="L143" s="3" t="s">
-        <v>568</v>
+        <v>578</v>
       </c>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A144" s="3" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="B144" s="3"/>
       <c r="C144" s="3" t="s">
-        <v>569</v>
+        <v>579</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>570</v>
+        <v>580</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>571</v>
+        <v>581</v>
       </c>
       <c r="F144" s="3"/>
       <c r="G144" s="3" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="H144" s="3" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="I144" s="3"/>
       <c r="J144" s="3" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="K144" s="3" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="L144" s="3" t="s">
-        <v>572</v>
+        <v>582</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A145" s="3" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="B145" s="3"/>
       <c r="C145" s="3" t="s">
-        <v>573</v>
+        <v>583</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>574</v>
+        <v>584</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>566</v>
+        <v>576</v>
       </c>
       <c r="F145" s="3"/>
       <c r="G145" s="3" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="H145" s="3" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="I145" s="3"/>
       <c r="J145" s="3" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="K145" s="3" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="L145" s="3" t="s">
-        <v>575</v>
+        <v>585</v>
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A146" s="3" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="B146" s="3"/>
       <c r="C146" s="3" t="s">
-        <v>576</v>
+        <v>586</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>452</v>
+        <v>462</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>577</v>
+        <v>587</v>
       </c>
       <c r="F146" s="3"/>
       <c r="G146" s="3" t="s">
@@ -7796,133 +7808,133 @@
         <v>16</v>
       </c>
       <c r="L146" s="3" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A147" s="3" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="B147" s="3"/>
       <c r="C147" s="3" t="s">
-        <v>578</v>
+        <v>588</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="E147" s="3" t="s">
-        <v>466</v>
+        <v>476</v>
       </c>
       <c r="F147" s="3" t="s">
-        <v>580</v>
+        <v>590</v>
       </c>
       <c r="G147" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H147" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="I147" s="3"/>
       <c r="J147" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K147" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L147" s="3" t="s">
-        <v>581</v>
+        <v>591</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A148" s="3" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="B148" s="3"/>
       <c r="C148" s="3" t="s">
-        <v>582</v>
+        <v>592</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>583</v>
+        <v>593</v>
       </c>
       <c r="F148" s="3" t="s">
-        <v>584</v>
+        <v>594</v>
       </c>
       <c r="G148" s="3" t="s">
-        <v>585</v>
+        <v>595</v>
       </c>
       <c r="H148" s="3" t="s">
-        <v>585</v>
+        <v>595</v>
       </c>
       <c r="I148" s="3"/>
       <c r="J148" s="3" t="s">
-        <v>470</v>
+        <v>480</v>
       </c>
       <c r="K148" s="3" t="s">
-        <v>585</v>
+        <v>595</v>
       </c>
       <c r="L148" s="3" t="s">
-        <v>586</v>
+        <v>596</v>
       </c>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A149" s="3" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="B149" s="3"/>
       <c r="C149" s="3" t="s">
-        <v>587</v>
+        <v>597</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="E149" s="3" t="s">
-        <v>588</v>
+        <v>598</v>
       </c>
       <c r="F149" s="3" t="s">
-        <v>589</v>
+        <v>599</v>
       </c>
       <c r="G149" s="3" t="s">
-        <v>585</v>
+        <v>595</v>
       </c>
       <c r="H149" s="3" t="s">
-        <v>585</v>
+        <v>595</v>
       </c>
       <c r="I149" s="3"/>
       <c r="J149" s="3" t="s">
-        <v>470</v>
+        <v>480</v>
       </c>
       <c r="K149" s="3" t="s">
-        <v>585</v>
+        <v>595</v>
       </c>
       <c r="L149" s="3" t="s">
-        <v>586</v>
+        <v>596</v>
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A150" s="3" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="B150" s="3"/>
       <c r="C150" s="3" t="s">
-        <v>590</v>
+        <v>600</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>591</v>
+        <v>601</v>
       </c>
       <c r="E150" s="3" t="s">
-        <v>592</v>
+        <v>602</v>
       </c>
       <c r="F150" s="3" t="s">
-        <v>593</v>
+        <v>603</v>
       </c>
       <c r="G150" s="3" t="s">
         <v>28</v>
       </c>
       <c r="H150" s="3" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="I150" s="3"/>
       <c r="J150" s="3" t="s">
@@ -7932,65 +7944,65 @@
         <v>28</v>
       </c>
       <c r="L150" s="3" t="s">
-        <v>594</v>
+        <v>604</v>
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A151" s="3" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="B151" s="3"/>
       <c r="C151" s="3" t="s">
-        <v>595</v>
+        <v>605</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>596</v>
+        <v>606</v>
       </c>
       <c r="E151" s="3" t="s">
-        <v>597</v>
+        <v>607</v>
       </c>
       <c r="F151" s="3" t="s">
-        <v>598</v>
+        <v>608</v>
       </c>
       <c r="G151" s="3" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="H151" s="3" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I151" s="3"/>
       <c r="J151" s="3" t="s">
-        <v>599</v>
+        <v>609</v>
       </c>
       <c r="K151" s="3" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="L151" s="3" t="s">
-        <v>600</v>
+        <v>610</v>
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A152" s="3" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="B152" s="3"/>
       <c r="C152" s="3" t="s">
-        <v>601</v>
+        <v>611</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>602</v>
+        <v>612</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>603</v>
+        <v>613</v>
       </c>
       <c r="F152" s="3" t="s">
-        <v>604</v>
+        <v>614</v>
       </c>
       <c r="G152" s="3" t="s">
         <v>28</v>
       </c>
       <c r="H152" s="3" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="I152" s="3"/>
       <c r="J152" s="3" t="s">
@@ -8000,31 +8012,31 @@
         <v>28</v>
       </c>
       <c r="L152" s="3" t="s">
-        <v>605</v>
+        <v>615</v>
       </c>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A153" s="3" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="B153" s="3"/>
       <c r="C153" s="3" t="s">
-        <v>606</v>
+        <v>616</v>
       </c>
       <c r="D153" s="3" t="s">
-        <v>602</v>
+        <v>612</v>
       </c>
       <c r="E153" s="3" t="s">
-        <v>607</v>
+        <v>617</v>
       </c>
       <c r="F153" s="3" t="s">
-        <v>608</v>
+        <v>618</v>
       </c>
       <c r="G153" s="3" t="s">
         <v>28</v>
       </c>
       <c r="H153" s="3" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="I153" s="3"/>
       <c r="J153" s="3" t="s">
@@ -8034,63 +8046,63 @@
         <v>28</v>
       </c>
       <c r="L153" s="3" t="s">
-        <v>609</v>
+        <v>619</v>
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A154" s="3" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="B154" s="3"/>
       <c r="C154" s="3" t="s">
-        <v>610</v>
+        <v>620</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>611</v>
+        <v>621</v>
       </c>
       <c r="E154" s="3" t="s">
-        <v>516</v>
+        <v>526</v>
       </c>
       <c r="F154" s="3" t="s">
-        <v>612</v>
+        <v>622</v>
       </c>
       <c r="G154" s="3" t="s">
-        <v>613</v>
+        <v>623</v>
       </c>
       <c r="H154" s="3" t="s">
-        <v>614</v>
+        <v>624</v>
       </c>
       <c r="I154" s="3"/>
       <c r="J154" s="3" t="s">
-        <v>615</v>
+        <v>625</v>
       </c>
       <c r="K154" s="3" t="s">
-        <v>613</v>
+        <v>623</v>
       </c>
       <c r="L154" s="3" t="s">
-        <v>616</v>
+        <v>626</v>
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A155" s="3" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="B155" s="3"/>
       <c r="C155" s="3" t="s">
-        <v>617</v>
+        <v>627</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>618</v>
+        <v>628</v>
       </c>
       <c r="E155" s="3" t="s">
-        <v>619</v>
+        <v>629</v>
       </c>
       <c r="F155" s="3"/>
       <c r="G155" s="3" t="s">
         <v>28</v>
       </c>
       <c r="H155" s="3" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="I155" s="3"/>
       <c r="J155" s="3" t="s">
@@ -8100,31 +8112,31 @@
         <v>28</v>
       </c>
       <c r="L155" s="3" t="s">
-        <v>620</v>
+        <v>630</v>
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A156" s="3" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="B156" s="3"/>
       <c r="C156" s="3" t="s">
+        <v>631</v>
+      </c>
+      <c r="D156" s="3" t="s">
         <v>621</v>
       </c>
-      <c r="D156" s="3" t="s">
-        <v>611</v>
-      </c>
       <c r="E156" s="3" t="s">
-        <v>462</v>
+        <v>472</v>
       </c>
       <c r="F156" s="3" t="s">
-        <v>622</v>
+        <v>632</v>
       </c>
       <c r="G156" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H156" s="3" t="s">
-        <v>443</v>
+        <v>453</v>
       </c>
       <c r="I156" s="3"/>
       <c r="J156" s="3" t="s">
@@ -8134,31 +8146,31 @@
         <v>17</v>
       </c>
       <c r="L156" s="3" t="s">
-        <v>623</v>
+        <v>633</v>
       </c>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A157" s="3" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="B157" s="3"/>
       <c r="C157" s="3" t="s">
-        <v>624</v>
+        <v>634</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>611</v>
+        <v>621</v>
       </c>
       <c r="E157" s="3" t="s">
-        <v>462</v>
+        <v>472</v>
       </c>
       <c r="F157" s="3" t="s">
-        <v>622</v>
+        <v>632</v>
       </c>
       <c r="G157" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H157" s="3" t="s">
-        <v>443</v>
+        <v>453</v>
       </c>
       <c r="I157" s="3"/>
       <c r="J157" s="3" t="s">
@@ -8168,22 +8180,22 @@
         <v>17</v>
       </c>
       <c r="L157" s="3" t="s">
-        <v>625</v>
+        <v>635</v>
       </c>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A158" s="3" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="B158" s="3"/>
       <c r="C158" s="3" t="s">
-        <v>626</v>
+        <v>636</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>452</v>
+        <v>462</v>
       </c>
       <c r="E158" s="3" t="s">
-        <v>627</v>
+        <v>637</v>
       </c>
       <c r="F158" s="3"/>
       <c r="G158" s="3" t="s">
@@ -8200,1147 +8212,1147 @@
         <v>16</v>
       </c>
       <c r="L158" s="3" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A159" s="3" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="B159" s="3"/>
       <c r="C159" s="3" t="s">
-        <v>628</v>
+        <v>638</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>629</v>
+        <v>639</v>
       </c>
       <c r="E159" s="3" t="s">
-        <v>607</v>
+        <v>617</v>
       </c>
       <c r="F159" s="3" t="s">
-        <v>630</v>
+        <v>640</v>
       </c>
       <c r="G159" s="3" t="s">
-        <v>631</v>
+        <v>641</v>
       </c>
       <c r="H159" s="3" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I159" s="3"/>
       <c r="J159" s="3" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="K159" s="3" t="s">
-        <v>631</v>
+        <v>641</v>
       </c>
       <c r="L159" s="3" t="s">
-        <v>632</v>
+        <v>642</v>
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A160" s="3" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="B160" s="3"/>
       <c r="C160" s="3" t="s">
-        <v>633</v>
+        <v>643</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>634</v>
+        <v>644</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>635</v>
+        <v>645</v>
       </c>
       <c r="F160" s="3"/>
       <c r="G160" s="3" t="s">
-        <v>636</v>
+        <v>646</v>
       </c>
       <c r="H160" s="3" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I160" s="3"/>
       <c r="J160" s="3" t="s">
-        <v>637</v>
+        <v>647</v>
       </c>
       <c r="K160" s="3" t="s">
-        <v>636</v>
+        <v>646</v>
       </c>
       <c r="L160" s="3" t="s">
-        <v>638</v>
+        <v>648</v>
       </c>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A161" s="3" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="B161" s="3"/>
       <c r="C161" s="3" t="s">
-        <v>639</v>
+        <v>649</v>
       </c>
       <c r="D161" s="3" t="s">
-        <v>634</v>
+        <v>644</v>
       </c>
       <c r="E161" s="3" t="s">
-        <v>640</v>
+        <v>650</v>
       </c>
       <c r="F161" s="3"/>
       <c r="G161" s="3" t="s">
-        <v>641</v>
+        <v>651</v>
       </c>
       <c r="H161" s="3" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I161" s="3"/>
       <c r="J161" s="3" t="s">
-        <v>642</v>
+        <v>652</v>
       </c>
       <c r="K161" s="3" t="s">
-        <v>641</v>
+        <v>651</v>
       </c>
       <c r="L161" s="3" t="s">
-        <v>643</v>
+        <v>653</v>
       </c>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A162" s="3" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="B162" s="3"/>
       <c r="C162" s="3" t="s">
-        <v>644</v>
+        <v>654</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>645</v>
+        <v>655</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="F162" s="3" t="s">
-        <v>646</v>
+        <v>656</v>
       </c>
       <c r="G162" s="3" t="s">
-        <v>647</v>
+        <v>657</v>
       </c>
       <c r="H162" s="3" t="s">
-        <v>648</v>
+        <v>658</v>
       </c>
       <c r="I162" s="3"/>
       <c r="J162" s="3" t="s">
-        <v>649</v>
+        <v>659</v>
       </c>
       <c r="K162" s="3" t="s">
-        <v>647</v>
+        <v>657</v>
       </c>
       <c r="L162" s="3" t="s">
-        <v>650</v>
+        <v>660</v>
       </c>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A163" s="3" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="B163" s="3"/>
       <c r="C163" s="3" t="s">
-        <v>651</v>
+        <v>661</v>
       </c>
       <c r="D163" s="3" t="s">
-        <v>652</v>
+        <v>662</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="F163" s="3" t="s">
-        <v>653</v>
+        <v>663</v>
       </c>
       <c r="G163" s="3" t="s">
-        <v>647</v>
+        <v>657</v>
       </c>
       <c r="H163" s="3" t="s">
-        <v>648</v>
+        <v>658</v>
       </c>
       <c r="I163" s="3"/>
       <c r="J163" s="3" t="s">
-        <v>649</v>
+        <v>659</v>
       </c>
       <c r="K163" s="3" t="s">
-        <v>647</v>
+        <v>657</v>
       </c>
       <c r="L163" s="3" t="s">
-        <v>654</v>
+        <v>664</v>
       </c>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A164" s="3" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="B164" s="3"/>
       <c r="C164" s="3" t="s">
-        <v>655</v>
+        <v>665</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>656</v>
+        <v>666</v>
       </c>
       <c r="E164" s="3" t="s">
-        <v>657</v>
+        <v>667</v>
       </c>
       <c r="F164" s="3" t="s">
-        <v>658</v>
+        <v>668</v>
       </c>
       <c r="G164" s="3" t="s">
-        <v>659</v>
+        <v>669</v>
       </c>
       <c r="H164" s="3" t="s">
-        <v>660</v>
+        <v>670</v>
       </c>
       <c r="I164" s="3"/>
       <c r="J164" s="3" t="s">
-        <v>661</v>
+        <v>671</v>
       </c>
       <c r="K164" s="3" t="s">
-        <v>659</v>
+        <v>669</v>
       </c>
       <c r="L164" s="3" t="s">
-        <v>662</v>
+        <v>672</v>
       </c>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A165" s="3" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="B165" s="3"/>
       <c r="C165" s="3" t="s">
-        <v>663</v>
+        <v>673</v>
       </c>
       <c r="D165" s="3" t="s">
-        <v>664</v>
+        <v>674</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>657</v>
+        <v>667</v>
       </c>
       <c r="F165" s="3" t="s">
-        <v>665</v>
+        <v>675</v>
       </c>
       <c r="G165" s="3" t="s">
-        <v>659</v>
+        <v>669</v>
       </c>
       <c r="H165" s="3" t="s">
-        <v>660</v>
+        <v>670</v>
       </c>
       <c r="I165" s="3"/>
       <c r="J165" s="3" t="s">
-        <v>661</v>
+        <v>671</v>
       </c>
       <c r="K165" s="3" t="s">
-        <v>659</v>
+        <v>669</v>
       </c>
       <c r="L165" s="3" t="s">
-        <v>662</v>
+        <v>672</v>
       </c>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A166" s="3" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="B166" s="3"/>
       <c r="C166" s="3" t="s">
-        <v>666</v>
+        <v>676</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>667</v>
+        <v>677</v>
       </c>
       <c r="E166" s="3" t="s">
-        <v>462</v>
+        <v>472</v>
       </c>
       <c r="F166" s="3" t="s">
-        <v>668</v>
+        <v>678</v>
       </c>
       <c r="G166" s="3" t="s">
-        <v>613</v>
+        <v>623</v>
       </c>
       <c r="H166" s="3" t="s">
-        <v>614</v>
+        <v>624</v>
       </c>
       <c r="I166" s="3"/>
       <c r="J166" s="3" t="s">
-        <v>615</v>
+        <v>625</v>
       </c>
       <c r="K166" s="3" t="s">
-        <v>613</v>
+        <v>623</v>
       </c>
       <c r="L166" s="3" t="s">
-        <v>669</v>
+        <v>679</v>
       </c>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A167" s="3" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="B167" s="3"/>
       <c r="C167" s="3" t="s">
-        <v>670</v>
+        <v>680</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>667</v>
+        <v>677</v>
       </c>
       <c r="E167" s="3" t="s">
-        <v>462</v>
+        <v>472</v>
       </c>
       <c r="F167" s="3" t="s">
-        <v>668</v>
+        <v>678</v>
       </c>
       <c r="G167" s="3" t="s">
-        <v>613</v>
+        <v>623</v>
       </c>
       <c r="H167" s="3" t="s">
-        <v>614</v>
+        <v>624</v>
       </c>
       <c r="I167" s="3"/>
       <c r="J167" s="3" t="s">
-        <v>615</v>
+        <v>625</v>
       </c>
       <c r="K167" s="3" t="s">
-        <v>613</v>
+        <v>623</v>
       </c>
       <c r="L167" s="3" t="s">
-        <v>669</v>
+        <v>679</v>
       </c>
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A168" s="3" t="s">
-        <v>671</v>
+        <v>681</v>
       </c>
       <c r="B168" s="3"/>
       <c r="C168" s="3" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
       <c r="E168" s="3" t="s">
-        <v>674</v>
+        <v>684</v>
       </c>
       <c r="F168" s="3"/>
       <c r="G168" s="3" t="s">
-        <v>675</v>
+        <v>685</v>
       </c>
       <c r="H168" s="3" t="s">
-        <v>675</v>
+        <v>685</v>
       </c>
       <c r="I168" s="3" t="s">
-        <v>676</v>
+        <v>686</v>
       </c>
       <c r="J168" s="3" t="s">
-        <v>677</v>
+        <v>687</v>
       </c>
       <c r="K168" s="3" t="s">
-        <v>675</v>
+        <v>685</v>
       </c>
       <c r="L168" s="3" t="s">
-        <v>678</v>
+        <v>688</v>
       </c>
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A169" s="3" t="s">
-        <v>671</v>
+        <v>681</v>
       </c>
       <c r="B169" s="3"/>
       <c r="C169" s="3" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>679</v>
+        <v>689</v>
       </c>
       <c r="E169" s="3" t="s">
-        <v>674</v>
+        <v>684</v>
       </c>
       <c r="F169" s="3"/>
       <c r="G169" s="3" t="s">
-        <v>675</v>
+        <v>685</v>
       </c>
       <c r="H169" s="3" t="s">
-        <v>675</v>
+        <v>685</v>
       </c>
       <c r="I169" s="3" t="s">
-        <v>676</v>
+        <v>686</v>
       </c>
       <c r="J169" s="3" t="s">
-        <v>677</v>
+        <v>687</v>
       </c>
       <c r="K169" s="3" t="s">
-        <v>675</v>
+        <v>685</v>
       </c>
       <c r="L169" s="3" t="s">
-        <v>678</v>
+        <v>688</v>
       </c>
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A170" s="3" t="s">
-        <v>671</v>
+        <v>681</v>
       </c>
       <c r="B170" s="3"/>
       <c r="C170" s="3" t="s">
-        <v>680</v>
+        <v>690</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>681</v>
+        <v>691</v>
       </c>
       <c r="E170" s="3" t="s">
-        <v>674</v>
+        <v>684</v>
       </c>
       <c r="F170" s="3"/>
       <c r="G170" s="3" t="s">
-        <v>675</v>
+        <v>685</v>
       </c>
       <c r="H170" s="3" t="s">
-        <v>675</v>
+        <v>685</v>
       </c>
       <c r="I170" s="3" t="s">
-        <v>682</v>
+        <v>692</v>
       </c>
       <c r="J170" s="3" t="s">
-        <v>677</v>
+        <v>687</v>
       </c>
       <c r="K170" s="3" t="s">
-        <v>675</v>
+        <v>685</v>
       </c>
       <c r="L170" s="3" t="s">
-        <v>683</v>
+        <v>693</v>
       </c>
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A171" s="3" t="s">
-        <v>671</v>
+        <v>681</v>
       </c>
       <c r="B171" s="3"/>
       <c r="C171" s="3" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="D171" s="3" t="s">
+        <v>694</v>
+      </c>
+      <c r="E171" s="3" t="s">
         <v>684</v>
-      </c>
-      <c r="E171" s="3" t="s">
-        <v>674</v>
       </c>
       <c r="F171" s="3"/>
       <c r="G171" s="3" t="s">
-        <v>675</v>
+        <v>685</v>
       </c>
       <c r="H171" s="3" t="s">
+        <v>695</v>
+      </c>
+      <c r="I171" s="3" t="s">
+        <v>686</v>
+      </c>
+      <c r="J171" s="3" t="s">
+        <v>687</v>
+      </c>
+      <c r="K171" s="3" t="s">
         <v>685</v>
       </c>
-      <c r="I171" s="3" t="s">
-        <v>676</v>
-      </c>
-      <c r="J171" s="3" t="s">
-        <v>677</v>
-      </c>
-      <c r="K171" s="3" t="s">
-        <v>675</v>
-      </c>
       <c r="L171" s="3" t="s">
-        <v>686</v>
+        <v>696</v>
       </c>
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A172" s="3" t="s">
-        <v>671</v>
+        <v>681</v>
       </c>
       <c r="B172" s="3"/>
       <c r="C172" s="3" t="s">
-        <v>680</v>
+        <v>690</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>687</v>
+        <v>697</v>
       </c>
       <c r="E172" s="3" t="s">
-        <v>674</v>
+        <v>684</v>
       </c>
       <c r="F172" s="3"/>
       <c r="G172" s="3" t="s">
-        <v>675</v>
+        <v>685</v>
       </c>
       <c r="H172" s="3" t="s">
-        <v>675</v>
+        <v>685</v>
       </c>
       <c r="I172" s="3" t="s">
-        <v>682</v>
+        <v>692</v>
       </c>
       <c r="J172" s="3" t="s">
-        <v>677</v>
+        <v>687</v>
       </c>
       <c r="K172" s="3" t="s">
-        <v>675</v>
+        <v>685</v>
       </c>
       <c r="L172" s="3" t="s">
-        <v>683</v>
+        <v>693</v>
       </c>
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A173" s="3" t="s">
-        <v>671</v>
+        <v>681</v>
       </c>
       <c r="B173" s="3"/>
       <c r="C173" s="3" t="s">
-        <v>680</v>
+        <v>690</v>
       </c>
       <c r="D173" s="3" t="s">
-        <v>688</v>
+        <v>698</v>
       </c>
       <c r="E173" s="3" t="s">
-        <v>674</v>
+        <v>684</v>
       </c>
       <c r="F173" s="3"/>
       <c r="G173" s="3" t="s">
-        <v>689</v>
+        <v>699</v>
       </c>
       <c r="H173" s="3" t="s">
-        <v>689</v>
+        <v>699</v>
       </c>
       <c r="I173" s="3" t="s">
-        <v>682</v>
+        <v>692</v>
       </c>
       <c r="J173" s="3" t="s">
-        <v>677</v>
+        <v>687</v>
       </c>
       <c r="K173" s="3" t="s">
-        <v>689</v>
+        <v>699</v>
       </c>
       <c r="L173" s="3" t="s">
-        <v>690</v>
+        <v>700</v>
       </c>
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A174" s="3" t="s">
-        <v>671</v>
+        <v>681</v>
       </c>
       <c r="B174" s="3"/>
       <c r="C174" s="3" t="s">
-        <v>680</v>
+        <v>690</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>691</v>
+        <v>701</v>
       </c>
       <c r="E174" s="3" t="s">
-        <v>692</v>
+        <v>702</v>
       </c>
       <c r="F174" s="3"/>
       <c r="G174" s="3" t="s">
-        <v>689</v>
+        <v>699</v>
       </c>
       <c r="H174" s="3" t="s">
-        <v>689</v>
+        <v>699</v>
       </c>
       <c r="I174" s="3" t="s">
-        <v>682</v>
+        <v>692</v>
       </c>
       <c r="J174" s="3" t="s">
-        <v>677</v>
+        <v>687</v>
       </c>
       <c r="K174" s="3" t="s">
-        <v>689</v>
+        <v>699</v>
       </c>
       <c r="L174" s="3" t="s">
-        <v>690</v>
+        <v>700</v>
       </c>
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A175" s="3" t="s">
-        <v>671</v>
+        <v>681</v>
       </c>
       <c r="B175" s="3"/>
       <c r="C175" s="3" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="D175" s="3" t="s">
-        <v>693</v>
+        <v>703</v>
       </c>
       <c r="E175" s="3" t="s">
-        <v>694</v>
+        <v>704</v>
       </c>
       <c r="F175" s="3"/>
       <c r="G175" s="3" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="H175" s="3" t="s">
-        <v>567</v>
+        <v>577</v>
       </c>
       <c r="I175" s="3" t="s">
-        <v>676</v>
+        <v>686</v>
       </c>
       <c r="J175" s="3" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="K175" s="3" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="L175" s="3" t="s">
-        <v>695</v>
+        <v>705</v>
       </c>
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A176" s="3" t="s">
-        <v>671</v>
+        <v>681</v>
       </c>
       <c r="B176" s="3"/>
       <c r="C176" s="3" t="s">
-        <v>680</v>
+        <v>690</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>696</v>
+        <v>706</v>
       </c>
       <c r="E176" s="3" t="s">
-        <v>697</v>
+        <v>707</v>
       </c>
       <c r="F176" s="3"/>
       <c r="G176" s="3" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="H176" s="3" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="I176" s="3" t="s">
-        <v>682</v>
+        <v>692</v>
       </c>
       <c r="J176" s="3" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="K176" s="3" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="L176" s="3" t="s">
-        <v>698</v>
+        <v>708</v>
       </c>
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A177" s="3" t="s">
-        <v>671</v>
+        <v>681</v>
       </c>
       <c r="B177" s="3"/>
       <c r="C177" s="3" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="D177" s="3" t="s">
-        <v>699</v>
+        <v>709</v>
       </c>
       <c r="E177" s="3" t="s">
-        <v>700</v>
+        <v>710</v>
       </c>
       <c r="F177" s="3"/>
       <c r="G177" s="3" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="H177" s="3" t="s">
-        <v>567</v>
+        <v>577</v>
       </c>
       <c r="I177" s="3" t="s">
-        <v>676</v>
+        <v>686</v>
       </c>
       <c r="J177" s="3" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="K177" s="3" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="L177" s="3" t="s">
-        <v>701</v>
+        <v>711</v>
       </c>
     </row>
     <row r="178" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A178" s="3" t="s">
-        <v>671</v>
+        <v>681</v>
       </c>
       <c r="B178" s="3"/>
       <c r="C178" s="3" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>702</v>
+        <v>712</v>
       </c>
       <c r="E178" s="3" t="s">
-        <v>674</v>
+        <v>684</v>
       </c>
       <c r="F178" s="3"/>
       <c r="G178" s="3" t="s">
-        <v>675</v>
+        <v>685</v>
       </c>
       <c r="H178" s="3" t="s">
-        <v>675</v>
+        <v>685</v>
       </c>
       <c r="I178" s="3" t="s">
-        <v>676</v>
+        <v>686</v>
       </c>
       <c r="J178" s="3" t="s">
-        <v>677</v>
+        <v>687</v>
       </c>
       <c r="K178" s="3" t="s">
-        <v>675</v>
+        <v>685</v>
       </c>
       <c r="L178" s="3" t="s">
-        <v>703</v>
+        <v>713</v>
       </c>
     </row>
     <row r="179" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A179" s="3" t="s">
-        <v>671</v>
+        <v>681</v>
       </c>
       <c r="B179" s="3"/>
       <c r="C179" s="3" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="D179" s="3" t="s">
-        <v>704</v>
+        <v>714</v>
       </c>
       <c r="E179" s="3" t="s">
-        <v>705</v>
+        <v>715</v>
       </c>
       <c r="F179" s="3"/>
       <c r="G179" s="3" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="H179" s="3" t="s">
-        <v>706</v>
+        <v>716</v>
       </c>
       <c r="I179" s="3" t="s">
-        <v>676</v>
+        <v>686</v>
       </c>
       <c r="J179" s="3" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="K179" s="3" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="L179" s="3" t="s">
-        <v>707</v>
+        <v>717</v>
       </c>
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A180" s="3" t="s">
-        <v>671</v>
+        <v>681</v>
       </c>
       <c r="B180" s="3"/>
       <c r="C180" s="3" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>708</v>
+        <v>718</v>
       </c>
       <c r="E180" s="3" t="s">
-        <v>709</v>
+        <v>719</v>
       </c>
       <c r="F180" s="3"/>
       <c r="G180" s="3" t="s">
-        <v>710</v>
+        <v>720</v>
       </c>
       <c r="H180" s="3" t="s">
-        <v>711</v>
+        <v>721</v>
       </c>
       <c r="I180" s="3" t="s">
-        <v>676</v>
+        <v>686</v>
       </c>
       <c r="J180" s="3" t="s">
-        <v>712</v>
+        <v>722</v>
       </c>
       <c r="K180" s="3" t="s">
-        <v>710</v>
+        <v>720</v>
       </c>
       <c r="L180" s="3" t="s">
-        <v>713</v>
+        <v>723</v>
       </c>
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A181" s="3" t="s">
-        <v>671</v>
+        <v>681</v>
       </c>
       <c r="B181" s="3"/>
       <c r="C181" s="3" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>714</v>
+        <v>724</v>
       </c>
       <c r="E181" s="3" t="s">
-        <v>709</v>
+        <v>719</v>
       </c>
       <c r="F181" s="3"/>
       <c r="G181" s="3" t="s">
-        <v>710</v>
+        <v>720</v>
       </c>
       <c r="H181" s="3" t="s">
-        <v>711</v>
+        <v>721</v>
       </c>
       <c r="I181" s="3" t="s">
-        <v>676</v>
+        <v>686</v>
       </c>
       <c r="J181" s="3" t="s">
-        <v>712</v>
+        <v>722</v>
       </c>
       <c r="K181" s="3" t="s">
-        <v>710</v>
+        <v>720</v>
       </c>
       <c r="L181" s="3" t="s">
-        <v>713</v>
+        <v>723</v>
       </c>
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A182" s="3" t="s">
-        <v>671</v>
+        <v>681</v>
       </c>
       <c r="B182" s="3"/>
       <c r="C182" s="3" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>715</v>
+        <v>725</v>
       </c>
       <c r="E182" s="3" t="s">
-        <v>674</v>
+        <v>684</v>
       </c>
       <c r="F182" s="3"/>
       <c r="G182" s="3" t="s">
-        <v>675</v>
+        <v>685</v>
       </c>
       <c r="H182" s="3" t="s">
-        <v>675</v>
+        <v>685</v>
       </c>
       <c r="I182" s="3" t="s">
-        <v>676</v>
+        <v>686</v>
       </c>
       <c r="J182" s="3" t="s">
-        <v>677</v>
+        <v>687</v>
       </c>
       <c r="K182" s="3" t="s">
-        <v>675</v>
+        <v>685</v>
       </c>
       <c r="L182" s="3" t="s">
-        <v>703</v>
+        <v>713</v>
       </c>
     </row>
     <row r="183" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A183" s="3" t="s">
-        <v>671</v>
+        <v>681</v>
       </c>
       <c r="B183" s="3"/>
       <c r="C183" s="3" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="D183" s="3" t="s">
-        <v>716</v>
+        <v>726</v>
       </c>
       <c r="E183" s="3" t="s">
-        <v>717</v>
+        <v>727</v>
       </c>
       <c r="F183" s="3"/>
       <c r="G183" s="3" t="s">
-        <v>718</v>
+        <v>728</v>
       </c>
       <c r="H183" s="3" t="s">
-        <v>719</v>
+        <v>729</v>
       </c>
       <c r="I183" s="3" t="s">
-        <v>676</v>
+        <v>686</v>
       </c>
       <c r="J183" s="3" t="s">
-        <v>720</v>
+        <v>730</v>
       </c>
       <c r="K183" s="3" t="s">
-        <v>718</v>
+        <v>728</v>
       </c>
       <c r="L183" s="3" t="s">
-        <v>721</v>
+        <v>731</v>
       </c>
     </row>
     <row r="184" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A184" s="3" t="s">
-        <v>722</v>
+        <v>732</v>
       </c>
       <c r="B184" s="3"/>
       <c r="C184" s="3" t="s">
-        <v>723</v>
+        <v>733</v>
       </c>
       <c r="D184" s="3" t="s">
-        <v>724</v>
+        <v>734</v>
       </c>
       <c r="E184" s="3" t="s">
-        <v>725</v>
+        <v>735</v>
       </c>
       <c r="F184" s="3" t="s">
-        <v>726</v>
+        <v>736</v>
       </c>
       <c r="G184" s="3" t="s">
-        <v>727</v>
+        <v>737</v>
       </c>
       <c r="H184" s="3" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I184" s="3"/>
       <c r="J184" s="3" t="s">
-        <v>728</v>
+        <v>738</v>
       </c>
       <c r="K184" s="3" t="s">
-        <v>727</v>
+        <v>737</v>
       </c>
       <c r="L184" s="3" t="s">
-        <v>729</v>
+        <v>739</v>
       </c>
     </row>
     <row r="185" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A185" s="3" t="s">
-        <v>722</v>
+        <v>732</v>
       </c>
       <c r="B185" s="3"/>
       <c r="C185" s="3" t="s">
-        <v>730</v>
+        <v>740</v>
       </c>
       <c r="D185" s="3" t="s">
-        <v>731</v>
+        <v>741</v>
       </c>
       <c r="E185" s="3" t="s">
-        <v>732</v>
+        <v>742</v>
       </c>
       <c r="F185" s="3" t="s">
-        <v>733</v>
+        <v>743</v>
       </c>
       <c r="G185" s="3" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="H185" s="3" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="I185" s="3"/>
       <c r="J185" s="3" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="K185" s="3" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="L185" s="3" t="s">
-        <v>734</v>
+        <v>744</v>
       </c>
     </row>
     <row r="186" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A186" s="3" t="s">
-        <v>722</v>
+        <v>732</v>
       </c>
       <c r="B186" s="3"/>
       <c r="C186" s="3" t="s">
-        <v>735</v>
+        <v>745</v>
       </c>
       <c r="D186" s="3" t="s">
-        <v>736</v>
+        <v>746</v>
       </c>
       <c r="E186" s="3" t="s">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="F186" s="3" t="s">
-        <v>737</v>
+        <v>747</v>
       </c>
       <c r="G186" s="3" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="H186" s="3" t="s">
-        <v>706</v>
+        <v>716</v>
       </c>
       <c r="I186" s="3"/>
       <c r="J186" s="3" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="K186" s="3" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="L186" s="3" t="s">
-        <v>738</v>
+        <v>748</v>
       </c>
     </row>
     <row r="187" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A187" s="3" t="s">
-        <v>722</v>
+        <v>732</v>
       </c>
       <c r="B187" s="3"/>
       <c r="C187" s="3" t="s">
-        <v>739</v>
+        <v>749</v>
       </c>
       <c r="D187" s="3" t="s">
-        <v>740</v>
+        <v>750</v>
       </c>
       <c r="E187" s="3" t="s">
-        <v>741</v>
+        <v>751</v>
       </c>
       <c r="F187" s="3" t="s">
-        <v>742</v>
+        <v>752</v>
       </c>
       <c r="G187" s="3" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="H187" s="3" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I187" s="3"/>
       <c r="J187" s="3" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="K187" s="3" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="L187" s="3" t="s">
-        <v>743</v>
+        <v>753</v>
       </c>
     </row>
     <row r="188" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A188" s="3" t="s">
-        <v>722</v>
+        <v>732</v>
       </c>
       <c r="B188" s="3"/>
       <c r="C188" s="3" t="s">
-        <v>744</v>
+        <v>754</v>
       </c>
       <c r="D188" s="3" t="s">
-        <v>745</v>
+        <v>755</v>
       </c>
       <c r="E188" s="3" t="s">
-        <v>746</v>
+        <v>756</v>
       </c>
       <c r="F188" s="3" t="s">
-        <v>746</v>
+        <v>756</v>
       </c>
       <c r="G188" s="3" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="H188" s="3" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I188" s="3"/>
       <c r="J188" s="3" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="K188" s="3" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="L188" s="3" t="s">
-        <v>747</v>
+        <v>757</v>
       </c>
     </row>
     <row r="189" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A189" s="3" t="s">
-        <v>722</v>
+        <v>732</v>
       </c>
       <c r="B189" s="3"/>
       <c r="C189" s="3" t="s">
-        <v>748</v>
+        <v>758</v>
       </c>
       <c r="D189" s="3" t="s">
-        <v>745</v>
+        <v>755</v>
       </c>
       <c r="E189" s="3" t="s">
-        <v>749</v>
+        <v>759</v>
       </c>
       <c r="F189" s="3" t="s">
-        <v>749</v>
+        <v>759</v>
       </c>
       <c r="G189" s="3" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="H189" s="3" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I189" s="3"/>
       <c r="J189" s="3" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="K189" s="3" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="L189" s="3" t="s">
-        <v>747</v>
+        <v>757</v>
       </c>
     </row>
     <row r="190" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A190" s="3" t="s">
-        <v>722</v>
+        <v>732</v>
       </c>
       <c r="B190" s="3"/>
       <c r="C190" s="3" t="s">
-        <v>750</v>
+        <v>760</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>751</v>
+        <v>761</v>
       </c>
       <c r="E190" s="3"/>
       <c r="F190" s="3" t="s">
-        <v>752</v>
+        <v>762</v>
       </c>
       <c r="G190" s="3" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="H190" s="3" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="I190" s="3"/>
       <c r="J190" s="3" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="K190" s="3" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="L190" s="3" t="s">
-        <v>753</v>
+        <v>763</v>
       </c>
     </row>
     <row r="191" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A191" s="3" t="s">
-        <v>754</v>
+        <v>764</v>
       </c>
       <c r="B191" s="3"/>
       <c r="C191" s="3" t="s">
-        <v>755</v>
+        <v>765</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>756</v>
+        <v>766</v>
       </c>
       <c r="E191" s="3" t="s">
-        <v>757</v>
+        <v>767</v>
       </c>
       <c r="F191" s="3" t="s">
-        <v>758</v>
+        <v>768</v>
       </c>
       <c r="G191" s="3" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="H191" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="I191" s="3"/>
       <c r="J191" s="3" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="K191" s="3" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="L191" s="3" t="s">
-        <v>759</v>
+        <v>769</v>
       </c>
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A192" s="3" t="s">
-        <v>754</v>
+        <v>764</v>
       </c>
       <c r="B192" s="3"/>
       <c r="C192" s="3" t="s">
-        <v>760</v>
+        <v>770</v>
       </c>
       <c r="D192" s="3" t="s">
-        <v>761</v>
+        <v>771</v>
       </c>
       <c r="E192" s="3" t="s">
-        <v>762</v>
+        <v>772</v>
       </c>
       <c r="F192" s="3" t="s">
-        <v>763</v>
+        <v>773</v>
       </c>
       <c r="G192" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H192" s="3" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I192" s="3"/>
       <c r="J192" s="3" t="s">
@@ -9350,31 +9362,31 @@
         <v>17</v>
       </c>
       <c r="L192" s="3" t="s">
-        <v>759</v>
+        <v>769</v>
       </c>
     </row>
     <row r="193" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A193" s="3" t="s">
-        <v>754</v>
+        <v>764</v>
       </c>
       <c r="B193" s="3"/>
       <c r="C193" s="3" t="s">
-        <v>764</v>
+        <v>774</v>
       </c>
       <c r="D193" s="3" t="s">
-        <v>765</v>
+        <v>775</v>
       </c>
       <c r="E193" s="3" t="s">
-        <v>766</v>
+        <v>776</v>
       </c>
       <c r="F193" s="3" t="s">
-        <v>767</v>
+        <v>777</v>
       </c>
       <c r="G193" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H193" s="3" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I193" s="3"/>
       <c r="J193" s="3" t="s">
@@ -9384,747 +9396,747 @@
         <v>17</v>
       </c>
       <c r="L193" s="3" t="s">
-        <v>759</v>
+        <v>769</v>
       </c>
     </row>
     <row r="194" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A194" s="3" t="s">
-        <v>754</v>
+        <v>764</v>
       </c>
       <c r="B194" s="3"/>
       <c r="C194" s="3" t="s">
-        <v>768</v>
+        <v>778</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>769</v>
+        <v>779</v>
       </c>
       <c r="E194" s="3" t="s">
-        <v>770</v>
+        <v>780</v>
       </c>
       <c r="F194" s="3" t="s">
-        <v>771</v>
+        <v>781</v>
       </c>
       <c r="G194" s="3" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="H194" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="I194" s="3"/>
       <c r="J194" s="3" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="K194" s="3" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="L194" s="3" t="s">
-        <v>759</v>
+        <v>769</v>
       </c>
     </row>
     <row r="195" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A195" s="3" t="s">
-        <v>754</v>
+        <v>764</v>
       </c>
       <c r="B195" s="3"/>
       <c r="C195" s="3" t="s">
-        <v>772</v>
+        <v>782</v>
       </c>
       <c r="D195" s="3" t="s">
-        <v>773</v>
+        <v>783</v>
       </c>
       <c r="E195" s="3" t="s">
-        <v>770</v>
+        <v>780</v>
       </c>
       <c r="F195" s="3" t="s">
-        <v>774</v>
+        <v>784</v>
       </c>
       <c r="G195" s="3" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="H195" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="I195" s="3"/>
       <c r="J195" s="3" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="K195" s="3" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="L195" s="3" t="s">
-        <v>759</v>
+        <v>769</v>
       </c>
     </row>
     <row r="196" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A196" s="3" t="s">
-        <v>754</v>
+        <v>764</v>
       </c>
       <c r="B196" s="3"/>
       <c r="C196" s="3" t="s">
-        <v>775</v>
+        <v>785</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>776</v>
+        <v>786</v>
       </c>
       <c r="E196" s="3" t="s">
-        <v>777</v>
+        <v>787</v>
       </c>
       <c r="F196" s="3" t="s">
-        <v>778</v>
+        <v>788</v>
       </c>
       <c r="G196" s="3" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="H196" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="I196" s="3"/>
       <c r="J196" s="3" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="K196" s="3" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="L196" s="3" t="s">
-        <v>759</v>
+        <v>769</v>
       </c>
     </row>
     <row r="197" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A197" s="3" t="s">
-        <v>754</v>
+        <v>764</v>
       </c>
       <c r="B197" s="3"/>
       <c r="C197" s="3" t="s">
-        <v>779</v>
+        <v>789</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>780</v>
+        <v>790</v>
       </c>
       <c r="E197" s="3" t="s">
-        <v>781</v>
+        <v>791</v>
       </c>
       <c r="F197" s="3" t="s">
-        <v>782</v>
+        <v>792</v>
       </c>
       <c r="G197" s="3" t="s">
-        <v>783</v>
+        <v>793</v>
       </c>
       <c r="H197" s="3" t="s">
-        <v>784</v>
+        <v>794</v>
       </c>
       <c r="I197" s="3"/>
       <c r="J197" s="3" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="K197" s="3" t="s">
-        <v>783</v>
+        <v>793</v>
       </c>
       <c r="L197" s="3" t="s">
-        <v>785</v>
+        <v>795</v>
       </c>
     </row>
     <row r="198" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A198" s="3" t="s">
-        <v>754</v>
+        <v>764</v>
       </c>
       <c r="B198" s="3"/>
       <c r="C198" s="3" t="s">
-        <v>786</v>
+        <v>796</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>787</v>
+        <v>797</v>
       </c>
       <c r="E198" s="3" t="s">
-        <v>788</v>
+        <v>798</v>
       </c>
       <c r="F198" s="3" t="s">
-        <v>789</v>
+        <v>799</v>
       </c>
       <c r="G198" s="3" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="H198" s="3" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="I198" s="3"/>
       <c r="J198" s="3" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="K198" s="3" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="L198" s="3" t="s">
-        <v>790</v>
+        <v>800</v>
       </c>
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A199" s="3" t="s">
-        <v>754</v>
+        <v>764</v>
       </c>
       <c r="B199" s="3"/>
       <c r="C199" s="3" t="s">
-        <v>791</v>
+        <v>801</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>787</v>
+        <v>797</v>
       </c>
       <c r="E199" s="3" t="s">
-        <v>577</v>
+        <v>587</v>
       </c>
       <c r="F199" s="3" t="s">
-        <v>792</v>
+        <v>802</v>
       </c>
       <c r="G199" s="3" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="H199" s="3" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="I199" s="3"/>
       <c r="J199" s="3" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="K199" s="3" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="L199" s="3" t="s">
-        <v>790</v>
+        <v>800</v>
       </c>
     </row>
     <row r="200" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A200" s="3" t="s">
-        <v>754</v>
+        <v>764</v>
       </c>
       <c r="B200" s="3"/>
       <c r="C200" s="3" t="s">
-        <v>793</v>
+        <v>803</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>794</v>
+        <v>804</v>
       </c>
       <c r="E200" s="3"/>
       <c r="F200" s="3" t="s">
-        <v>795</v>
+        <v>805</v>
       </c>
       <c r="G200" s="3" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="H200" s="3" t="s">
-        <v>436</v>
+        <v>446</v>
       </c>
       <c r="I200" s="3"/>
       <c r="J200" s="3" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="K200" s="3" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="L200" s="3" t="s">
-        <v>796</v>
+        <v>806</v>
       </c>
     </row>
     <row r="201" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A201" s="3" t="s">
-        <v>754</v>
+        <v>764</v>
       </c>
       <c r="B201" s="3"/>
       <c r="C201" s="3" t="s">
-        <v>797</v>
+        <v>807</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>798</v>
+        <v>808</v>
       </c>
       <c r="E201" s="3" t="s">
-        <v>799</v>
+        <v>809</v>
       </c>
       <c r="F201" s="3" t="s">
-        <v>800</v>
+        <v>810</v>
       </c>
       <c r="G201" s="3" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="H201" s="3" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="I201" s="3"/>
       <c r="J201" s="3" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="K201" s="3" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="L201" s="3" t="s">
-        <v>801</v>
+        <v>811</v>
       </c>
     </row>
     <row r="202" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A202" s="3" t="s">
-        <v>754</v>
+        <v>764</v>
       </c>
       <c r="B202" s="3"/>
       <c r="C202" s="3" t="s">
-        <v>802</v>
+        <v>812</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>803</v>
+        <v>813</v>
       </c>
       <c r="E202" s="3" t="s">
-        <v>804</v>
+        <v>814</v>
       </c>
       <c r="F202" s="3" t="s">
-        <v>805</v>
+        <v>815</v>
       </c>
       <c r="G202" s="3" t="s">
-        <v>806</v>
+        <v>816</v>
       </c>
       <c r="H202" s="3" t="s">
-        <v>807</v>
+        <v>817</v>
       </c>
       <c r="I202" s="3"/>
       <c r="J202" s="3" t="s">
-        <v>808</v>
+        <v>818</v>
       </c>
       <c r="K202" s="3" t="s">
-        <v>806</v>
+        <v>816</v>
       </c>
       <c r="L202" s="3" t="s">
-        <v>809</v>
+        <v>819</v>
       </c>
     </row>
     <row r="203" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A203" s="3" t="s">
-        <v>754</v>
+        <v>764</v>
       </c>
       <c r="B203" s="3"/>
       <c r="C203" s="3" t="s">
-        <v>810</v>
+        <v>820</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>811</v>
+        <v>821</v>
       </c>
       <c r="E203" s="3" t="s">
-        <v>812</v>
+        <v>822</v>
       </c>
       <c r="F203" s="3" t="s">
-        <v>813</v>
+        <v>823</v>
       </c>
       <c r="G203" s="3" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="H203" s="3" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="I203" s="3"/>
       <c r="J203" s="3" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="K203" s="3" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="L203" s="3" t="s">
-        <v>814</v>
+        <v>824</v>
       </c>
     </row>
     <row r="204" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A204" s="3" t="s">
-        <v>754</v>
+        <v>764</v>
       </c>
       <c r="B204" s="3"/>
       <c r="C204" s="3" t="s">
-        <v>815</v>
+        <v>825</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>811</v>
+        <v>821</v>
       </c>
       <c r="E204" s="3" t="s">
-        <v>816</v>
+        <v>826</v>
       </c>
       <c r="F204" s="3" t="s">
-        <v>817</v>
+        <v>827</v>
       </c>
       <c r="G204" s="3" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="H204" s="3" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="I204" s="3"/>
       <c r="J204" s="3" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="K204" s="3" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="L204" s="3" t="s">
-        <v>814</v>
+        <v>824</v>
       </c>
     </row>
     <row r="205" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A205" s="3" t="s">
-        <v>754</v>
+        <v>764</v>
       </c>
       <c r="B205" s="3"/>
       <c r="C205" s="3" t="s">
-        <v>818</v>
+        <v>828</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>819</v>
+        <v>829</v>
       </c>
       <c r="E205" s="3" t="s">
-        <v>820</v>
+        <v>830</v>
       </c>
       <c r="F205" s="3" t="s">
-        <v>821</v>
+        <v>831</v>
       </c>
       <c r="G205" s="3" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="H205" s="3" t="s">
-        <v>436</v>
+        <v>446</v>
       </c>
       <c r="I205" s="3"/>
       <c r="J205" s="3" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="K205" s="3" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="L205" s="3" t="s">
-        <v>822</v>
+        <v>832</v>
       </c>
     </row>
     <row r="206" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A206" s="3" t="s">
-        <v>754</v>
+        <v>764</v>
       </c>
       <c r="B206" s="3"/>
       <c r="C206" s="3" t="s">
-        <v>823</v>
+        <v>833</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>819</v>
+        <v>829</v>
       </c>
       <c r="E206" s="3" t="s">
-        <v>820</v>
+        <v>830</v>
       </c>
       <c r="F206" s="3" t="s">
-        <v>824</v>
+        <v>834</v>
       </c>
       <c r="G206" s="3" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="H206" s="3" t="s">
-        <v>436</v>
+        <v>446</v>
       </c>
       <c r="I206" s="3"/>
       <c r="J206" s="3" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="K206" s="3" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="L206" s="3" t="s">
-        <v>822</v>
+        <v>832</v>
       </c>
     </row>
     <row r="207" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A207" s="3" t="s">
-        <v>754</v>
+        <v>764</v>
       </c>
       <c r="B207" s="3"/>
       <c r="C207" s="3" t="s">
-        <v>825</v>
+        <v>835</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>826</v>
+        <v>836</v>
       </c>
       <c r="E207" s="3" t="s">
-        <v>827</v>
+        <v>837</v>
       </c>
       <c r="F207" s="3" t="s">
-        <v>828</v>
+        <v>838</v>
       </c>
       <c r="G207" s="3" t="s">
-        <v>806</v>
+        <v>816</v>
       </c>
       <c r="H207" s="3" t="s">
-        <v>807</v>
+        <v>817</v>
       </c>
       <c r="I207" s="3"/>
       <c r="J207" s="3" t="s">
-        <v>808</v>
+        <v>818</v>
       </c>
       <c r="K207" s="3" t="s">
-        <v>806</v>
+        <v>816</v>
       </c>
       <c r="L207" s="3" t="s">
-        <v>809</v>
+        <v>819</v>
       </c>
     </row>
     <row r="208" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A208" s="3" t="s">
-        <v>754</v>
+        <v>764</v>
       </c>
       <c r="B208" s="3"/>
       <c r="C208" s="3" t="s">
-        <v>829</v>
+        <v>839</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>830</v>
+        <v>840</v>
       </c>
       <c r="E208" s="3"/>
       <c r="F208" s="3" t="s">
-        <v>831</v>
+        <v>841</v>
       </c>
       <c r="G208" s="3" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="H208" s="3" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="I208" s="3"/>
       <c r="J208" s="3" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="K208" s="3" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="L208" s="3" t="s">
-        <v>832</v>
+        <v>842</v>
       </c>
     </row>
     <row r="209" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A209" s="3" t="s">
-        <v>754</v>
+        <v>764</v>
       </c>
       <c r="B209" s="3"/>
       <c r="C209" s="3" t="s">
-        <v>833</v>
+        <v>843</v>
       </c>
       <c r="D209" s="3" t="s">
-        <v>830</v>
+        <v>840</v>
       </c>
       <c r="E209" s="3"/>
       <c r="F209" s="3" t="s">
-        <v>834</v>
+        <v>844</v>
       </c>
       <c r="G209" s="3" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="H209" s="3" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="I209" s="3"/>
       <c r="J209" s="3" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="K209" s="3" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="L209" s="3" t="s">
-        <v>832</v>
+        <v>842</v>
       </c>
     </row>
     <row r="210" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A210" s="3" t="s">
-        <v>754</v>
+        <v>764</v>
       </c>
       <c r="B210" s="3"/>
       <c r="C210" s="3" t="s">
-        <v>835</v>
+        <v>845</v>
       </c>
       <c r="D210" s="3" t="s">
-        <v>836</v>
+        <v>846</v>
       </c>
       <c r="E210" s="3" t="s">
-        <v>837</v>
+        <v>847</v>
       </c>
       <c r="F210" s="3"/>
       <c r="G210" s="3" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="H210" s="3" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="I210" s="3"/>
       <c r="J210" s="3" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="K210" s="3" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="L210" s="3" t="s">
-        <v>838</v>
+        <v>848</v>
       </c>
     </row>
     <row r="211" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A211" s="3" t="s">
-        <v>754</v>
+        <v>764</v>
       </c>
       <c r="B211" s="3"/>
       <c r="C211" s="3" t="s">
-        <v>839</v>
+        <v>849</v>
       </c>
       <c r="D211" s="3" t="s">
-        <v>840</v>
+        <v>850</v>
       </c>
       <c r="E211" s="3" t="s">
-        <v>841</v>
+        <v>851</v>
       </c>
       <c r="F211" s="3" t="s">
-        <v>842</v>
+        <v>852</v>
       </c>
       <c r="G211" s="3" t="s">
-        <v>843</v>
+        <v>853</v>
       </c>
       <c r="H211" s="3" t="s">
-        <v>807</v>
+        <v>817</v>
       </c>
       <c r="I211" s="3"/>
       <c r="J211" s="3" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="K211" s="3" t="s">
-        <v>843</v>
+        <v>853</v>
       </c>
       <c r="L211" s="3" t="s">
-        <v>845</v>
+        <v>855</v>
       </c>
     </row>
     <row r="212" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A212" s="3" t="s">
-        <v>754</v>
+        <v>764</v>
       </c>
       <c r="B212" s="3"/>
       <c r="C212" s="3" t="s">
-        <v>839</v>
+        <v>849</v>
       </c>
       <c r="D212" s="3" t="s">
-        <v>840</v>
+        <v>850</v>
       </c>
       <c r="E212" s="3" t="s">
-        <v>846</v>
+        <v>856</v>
       </c>
       <c r="F212" s="3" t="s">
-        <v>847</v>
+        <v>857</v>
       </c>
       <c r="G212" s="3" t="s">
-        <v>843</v>
+        <v>853</v>
       </c>
       <c r="H212" s="3" t="s">
-        <v>807</v>
+        <v>817</v>
       </c>
       <c r="I212" s="3"/>
       <c r="J212" s="3" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="K212" s="3" t="s">
-        <v>843</v>
+        <v>853</v>
       </c>
       <c r="L212" s="3" t="s">
-        <v>845</v>
+        <v>855</v>
       </c>
     </row>
     <row r="213" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A213" s="3" t="s">
-        <v>754</v>
+        <v>764</v>
       </c>
       <c r="B213" s="3"/>
       <c r="C213" s="3" t="s">
-        <v>848</v>
+        <v>858</v>
       </c>
       <c r="D213" s="3" t="s">
-        <v>849</v>
+        <v>859</v>
       </c>
       <c r="E213" s="3" t="s">
-        <v>841</v>
+        <v>851</v>
       </c>
       <c r="F213" s="3" t="s">
-        <v>850</v>
+        <v>860</v>
       </c>
       <c r="G213" s="3" t="s">
-        <v>843</v>
+        <v>853</v>
       </c>
       <c r="H213" s="3" t="s">
-        <v>807</v>
+        <v>817</v>
       </c>
       <c r="I213" s="3"/>
       <c r="J213" s="3" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="K213" s="3" t="s">
-        <v>843</v>
+        <v>853</v>
       </c>
       <c r="L213" s="3" t="s">
-        <v>851</v>
+        <v>861</v>
       </c>
     </row>
     <row r="214" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A214" s="3" t="s">
-        <v>754</v>
+        <v>764</v>
       </c>
       <c r="B214" s="3"/>
       <c r="C214" s="3" t="s">
-        <v>848</v>
+        <v>858</v>
       </c>
       <c r="D214" s="3" t="s">
-        <v>849</v>
+        <v>859</v>
       </c>
       <c r="E214" s="3" t="s">
-        <v>846</v>
+        <v>856</v>
       </c>
       <c r="F214" s="3" t="s">
-        <v>852</v>
+        <v>862</v>
       </c>
       <c r="G214" s="3" t="s">
-        <v>843</v>
+        <v>853</v>
       </c>
       <c r="H214" s="3" t="s">
-        <v>807</v>
+        <v>817</v>
       </c>
       <c r="I214" s="3"/>
       <c r="J214" s="3" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="K214" s="3" t="s">
-        <v>843</v>
+        <v>853</v>
       </c>
       <c r="L214" s="3" t="s">
-        <v>851</v>
+        <v>861</v>
       </c>
     </row>
     <row r="215" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A215" s="3" t="s">
-        <v>754</v>
+        <v>764</v>
       </c>
       <c r="B215" s="3"/>
       <c r="C215" s="3" t="s">
-        <v>853</v>
+        <v>863</v>
       </c>
       <c r="D215" s="3" t="s">
-        <v>854</v>
+        <v>864</v>
       </c>
       <c r="E215" s="3" t="s">
-        <v>841</v>
+        <v>851</v>
       </c>
       <c r="F215" s="3" t="s">
-        <v>855</v>
+        <v>865</v>
       </c>
       <c r="G215" s="3" t="s">
-        <v>856</v>
+        <v>866</v>
       </c>
       <c r="H215" s="3" t="s">
-        <v>856</v>
+        <v>866</v>
       </c>
       <c r="I215" s="3"/>
       <c r="J215" s="3" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="K215" s="3" t="s">
-        <v>856</v>
+        <v>866</v>
       </c>
       <c r="L215" s="3" t="s">
-        <v>845</v>
+        <v>855</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dvagov-my.sharepoint.com/personal/bernard_chan_va_gov/Documents/Microsoft Teams Chat Files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="41" documentId="11_87A73CECC8785890643FEBC9776139824E07390D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1DC67227-D43E-4D83-9019-D21FCC478F9F}"/>
+  <xr:revisionPtr revIDLastSave="47" documentId="11_87A73CECC8785890643FEBC9776139824E07390D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BBDFB50C-05FA-4165-95BE-D76492117E0F}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2046" uniqueCount="869">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2056" uniqueCount="873">
   <si>
     <t>category</t>
   </si>
@@ -2643,6 +2643,18 @@
   </si>
   <si>
     <t>Washed and reused ~3 days, so one per day.</t>
+  </si>
+  <si>
+    <t>Male External Catheter BD UltraFlex</t>
+  </si>
+  <si>
+    <t>Medium 29mm</t>
+  </si>
+  <si>
+    <t>6530-01-451-7669</t>
+  </si>
+  <si>
+    <t>U 21</t>
   </si>
 </sst>
 </file>
@@ -2719,9 +2731,13 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Items" displayName="Items" ref="A1:L215">
-  <autoFilter ref="A1:L215" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Items" displayName="Items" ref="A1:L216">
+  <autoFilter ref="A1:L216" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="category"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="shelf"/>
@@ -3025,7 +3041,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L215"/>
+  <dimension ref="A1:L216"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" style="1" customWidth="1"/>
@@ -9442,13 +9458,13 @@
         <v>782</v>
       </c>
       <c r="D195" s="3" t="s">
-        <v>783</v>
+        <v>869</v>
       </c>
       <c r="E195" s="3" t="s">
-        <v>780</v>
+        <v>870</v>
       </c>
       <c r="F195" s="3" t="s">
-        <v>784</v>
+        <v>871</v>
       </c>
       <c r="G195" s="3" t="s">
         <v>129</v>
@@ -9476,13 +9492,13 @@
         <v>785</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="E196" s="3" t="s">
-        <v>787</v>
+        <v>780</v>
       </c>
       <c r="F196" s="3" t="s">
-        <v>788</v>
+        <v>784</v>
       </c>
       <c r="G196" s="3" t="s">
         <v>129</v>
@@ -9510,29 +9526,29 @@
         <v>789</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>790</v>
+        <v>786</v>
       </c>
       <c r="E197" s="3" t="s">
-        <v>791</v>
+        <v>787</v>
       </c>
       <c r="F197" s="3" t="s">
-        <v>792</v>
+        <v>788</v>
       </c>
       <c r="G197" s="3" t="s">
-        <v>793</v>
+        <v>129</v>
       </c>
       <c r="H197" s="3" t="s">
-        <v>794</v>
+        <v>130</v>
       </c>
       <c r="I197" s="3"/>
       <c r="J197" s="3" t="s">
         <v>131</v>
       </c>
       <c r="K197" s="3" t="s">
-        <v>793</v>
+        <v>129</v>
       </c>
       <c r="L197" s="3" t="s">
-        <v>795</v>
+        <v>769</v>
       </c>
     </row>
     <row r="198" spans="1:12" x14ac:dyDescent="0.25">
@@ -9544,29 +9560,29 @@
         <v>796</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>797</v>
+        <v>790</v>
       </c>
       <c r="E198" s="3" t="s">
-        <v>798</v>
+        <v>791</v>
       </c>
       <c r="F198" s="3" t="s">
-        <v>799</v>
+        <v>792</v>
       </c>
       <c r="G198" s="3" t="s">
-        <v>264</v>
+        <v>793</v>
       </c>
       <c r="H198" s="3" t="s">
-        <v>263</v>
+        <v>794</v>
       </c>
       <c r="I198" s="3"/>
       <c r="J198" s="3" t="s">
-        <v>82</v>
+        <v>131</v>
       </c>
       <c r="K198" s="3" t="s">
-        <v>264</v>
+        <v>793</v>
       </c>
       <c r="L198" s="3" t="s">
-        <v>800</v>
+        <v>795</v>
       </c>
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.25">
@@ -9581,10 +9597,10 @@
         <v>797</v>
       </c>
       <c r="E199" s="3" t="s">
-        <v>587</v>
+        <v>798</v>
       </c>
       <c r="F199" s="3" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="G199" s="3" t="s">
         <v>264</v>
@@ -9612,17 +9628,19 @@
         <v>803</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>804</v>
-      </c>
-      <c r="E200" s="3"/>
+        <v>797</v>
+      </c>
+      <c r="E200" s="3" t="s">
+        <v>587</v>
+      </c>
       <c r="F200" s="3" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="G200" s="3" t="s">
         <v>264</v>
       </c>
       <c r="H200" s="3" t="s">
-        <v>446</v>
+        <v>263</v>
       </c>
       <c r="I200" s="3"/>
       <c r="J200" s="3" t="s">
@@ -9632,7 +9650,7 @@
         <v>264</v>
       </c>
       <c r="L200" s="3" t="s">
-        <v>806</v>
+        <v>800</v>
       </c>
     </row>
     <row r="201" spans="1:12" x14ac:dyDescent="0.25">
@@ -9644,29 +9662,27 @@
         <v>807</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>808</v>
-      </c>
-      <c r="E201" s="3" t="s">
-        <v>809</v>
-      </c>
+        <v>804</v>
+      </c>
+      <c r="E201" s="3"/>
       <c r="F201" s="3" t="s">
-        <v>810</v>
+        <v>805</v>
       </c>
       <c r="G201" s="3" t="s">
-        <v>202</v>
+        <v>264</v>
       </c>
       <c r="H201" s="3" t="s">
-        <v>121</v>
+        <v>446</v>
       </c>
       <c r="I201" s="3"/>
       <c r="J201" s="3" t="s">
-        <v>203</v>
+        <v>82</v>
       </c>
       <c r="K201" s="3" t="s">
-        <v>202</v>
+        <v>264</v>
       </c>
       <c r="L201" s="3" t="s">
-        <v>811</v>
+        <v>806</v>
       </c>
     </row>
     <row r="202" spans="1:12" x14ac:dyDescent="0.25">
@@ -9678,29 +9694,29 @@
         <v>812</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>813</v>
+        <v>808</v>
       </c>
       <c r="E202" s="3" t="s">
-        <v>814</v>
+        <v>809</v>
       </c>
       <c r="F202" s="3" t="s">
-        <v>815</v>
+        <v>810</v>
       </c>
       <c r="G202" s="3" t="s">
-        <v>816</v>
+        <v>202</v>
       </c>
       <c r="H202" s="3" t="s">
-        <v>817</v>
+        <v>121</v>
       </c>
       <c r="I202" s="3"/>
       <c r="J202" s="3" t="s">
-        <v>818</v>
+        <v>203</v>
       </c>
       <c r="K202" s="3" t="s">
-        <v>816</v>
+        <v>202</v>
       </c>
       <c r="L202" s="3" t="s">
-        <v>819</v>
+        <v>811</v>
       </c>
     </row>
     <row r="203" spans="1:12" x14ac:dyDescent="0.25">
@@ -9712,29 +9728,29 @@
         <v>820</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>821</v>
+        <v>813</v>
       </c>
       <c r="E203" s="3" t="s">
-        <v>822</v>
+        <v>814</v>
       </c>
       <c r="F203" s="3" t="s">
-        <v>823</v>
+        <v>815</v>
       </c>
       <c r="G203" s="3" t="s">
-        <v>121</v>
+        <v>816</v>
       </c>
       <c r="H203" s="3" t="s">
-        <v>121</v>
+        <v>817</v>
       </c>
       <c r="I203" s="3"/>
       <c r="J203" s="3" t="s">
-        <v>82</v>
+        <v>818</v>
       </c>
       <c r="K203" s="3" t="s">
-        <v>121</v>
+        <v>816</v>
       </c>
       <c r="L203" s="3" t="s">
-        <v>824</v>
+        <v>819</v>
       </c>
     </row>
     <row r="204" spans="1:12" x14ac:dyDescent="0.25">
@@ -9749,10 +9765,10 @@
         <v>821</v>
       </c>
       <c r="E204" s="3" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
       <c r="F204" s="3" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="G204" s="3" t="s">
         <v>121</v>
@@ -9780,29 +9796,29 @@
         <v>828</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>829</v>
+        <v>821</v>
       </c>
       <c r="E205" s="3" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="F205" s="3" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="G205" s="3" t="s">
-        <v>264</v>
+        <v>121</v>
       </c>
       <c r="H205" s="3" t="s">
-        <v>446</v>
+        <v>121</v>
       </c>
       <c r="I205" s="3"/>
       <c r="J205" s="3" t="s">
         <v>82</v>
       </c>
       <c r="K205" s="3" t="s">
-        <v>264</v>
+        <v>121</v>
       </c>
       <c r="L205" s="3" t="s">
-        <v>832</v>
+        <v>824</v>
       </c>
     </row>
     <row r="206" spans="1:12" x14ac:dyDescent="0.25">
@@ -9820,7 +9836,7 @@
         <v>830</v>
       </c>
       <c r="F206" s="3" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="G206" s="3" t="s">
         <v>264</v>
@@ -9848,29 +9864,29 @@
         <v>835</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>836</v>
+        <v>829</v>
       </c>
       <c r="E207" s="3" t="s">
-        <v>837</v>
+        <v>830</v>
       </c>
       <c r="F207" s="3" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
       <c r="G207" s="3" t="s">
-        <v>816</v>
+        <v>264</v>
       </c>
       <c r="H207" s="3" t="s">
-        <v>817</v>
+        <v>446</v>
       </c>
       <c r="I207" s="3"/>
       <c r="J207" s="3" t="s">
-        <v>818</v>
+        <v>82</v>
       </c>
       <c r="K207" s="3" t="s">
-        <v>816</v>
+        <v>264</v>
       </c>
       <c r="L207" s="3" t="s">
-        <v>819</v>
+        <v>832</v>
       </c>
     </row>
     <row r="208" spans="1:12" x14ac:dyDescent="0.25">
@@ -9882,27 +9898,29 @@
         <v>839</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>840</v>
-      </c>
-      <c r="E208" s="3"/>
+        <v>836</v>
+      </c>
+      <c r="E208" s="3" t="s">
+        <v>837</v>
+      </c>
       <c r="F208" s="3" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="G208" s="3" t="s">
-        <v>264</v>
+        <v>816</v>
       </c>
       <c r="H208" s="3" t="s">
-        <v>263</v>
+        <v>817</v>
       </c>
       <c r="I208" s="3"/>
       <c r="J208" s="3" t="s">
-        <v>82</v>
+        <v>818</v>
       </c>
       <c r="K208" s="3" t="s">
-        <v>264</v>
+        <v>816</v>
       </c>
       <c r="L208" s="3" t="s">
-        <v>842</v>
+        <v>819</v>
       </c>
     </row>
     <row r="209" spans="1:12" x14ac:dyDescent="0.25">
@@ -9918,7 +9936,7 @@
       </c>
       <c r="E209" s="3"/>
       <c r="F209" s="3" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="G209" s="3" t="s">
         <v>264</v>
@@ -9946,27 +9964,27 @@
         <v>845</v>
       </c>
       <c r="D210" s="3" t="s">
-        <v>846</v>
-      </c>
-      <c r="E210" s="3" t="s">
-        <v>847</v>
-      </c>
-      <c r="F210" s="3"/>
+        <v>840</v>
+      </c>
+      <c r="E210" s="3"/>
+      <c r="F210" s="3" t="s">
+        <v>844</v>
+      </c>
       <c r="G210" s="3" t="s">
-        <v>246</v>
+        <v>264</v>
       </c>
       <c r="H210" s="3" t="s">
-        <v>244</v>
+        <v>263</v>
       </c>
       <c r="I210" s="3"/>
       <c r="J210" s="3" t="s">
-        <v>245</v>
+        <v>82</v>
       </c>
       <c r="K210" s="3" t="s">
-        <v>246</v>
+        <v>264</v>
       </c>
       <c r="L210" s="3" t="s">
-        <v>848</v>
+        <v>842</v>
       </c>
     </row>
     <row r="211" spans="1:12" x14ac:dyDescent="0.25">
@@ -9975,32 +9993,30 @@
       </c>
       <c r="B211" s="3"/>
       <c r="C211" s="3" t="s">
-        <v>849</v>
+        <v>872</v>
       </c>
       <c r="D211" s="3" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
       <c r="E211" s="3" t="s">
-        <v>851</v>
-      </c>
-      <c r="F211" s="3" t="s">
-        <v>852</v>
-      </c>
+        <v>847</v>
+      </c>
+      <c r="F211" s="3"/>
       <c r="G211" s="3" t="s">
-        <v>853</v>
+        <v>246</v>
       </c>
       <c r="H211" s="3" t="s">
-        <v>817</v>
+        <v>244</v>
       </c>
       <c r="I211" s="3"/>
       <c r="J211" s="3" t="s">
-        <v>854</v>
+        <v>245</v>
       </c>
       <c r="K211" s="3" t="s">
-        <v>853</v>
+        <v>246</v>
       </c>
       <c r="L211" s="3" t="s">
-        <v>855</v>
+        <v>848</v>
       </c>
     </row>
     <row r="212" spans="1:12" x14ac:dyDescent="0.25">
@@ -10015,10 +10031,10 @@
         <v>850</v>
       </c>
       <c r="E212" s="3" t="s">
-        <v>856</v>
+        <v>851</v>
       </c>
       <c r="F212" s="3" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="G212" s="3" t="s">
         <v>853</v>
@@ -10043,16 +10059,16 @@
       </c>
       <c r="B213" s="3"/>
       <c r="C213" s="3" t="s">
-        <v>858</v>
+        <v>849</v>
       </c>
       <c r="D213" s="3" t="s">
-        <v>859</v>
+        <v>850</v>
       </c>
       <c r="E213" s="3" t="s">
-        <v>851</v>
+        <v>856</v>
       </c>
       <c r="F213" s="3" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="G213" s="3" t="s">
         <v>853</v>
@@ -10068,7 +10084,7 @@
         <v>853</v>
       </c>
       <c r="L213" s="3" t="s">
-        <v>861</v>
+        <v>855</v>
       </c>
     </row>
     <row r="214" spans="1:12" x14ac:dyDescent="0.25">
@@ -10083,10 +10099,10 @@
         <v>859</v>
       </c>
       <c r="E214" s="3" t="s">
-        <v>856</v>
+        <v>851</v>
       </c>
       <c r="F214" s="3" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="G214" s="3" t="s">
         <v>853</v>
@@ -10111,31 +10127,65 @@
       </c>
       <c r="B215" s="3"/>
       <c r="C215" s="3" t="s">
-        <v>863</v>
+        <v>858</v>
       </c>
       <c r="D215" s="3" t="s">
-        <v>864</v>
+        <v>859</v>
       </c>
       <c r="E215" s="3" t="s">
-        <v>851</v>
+        <v>856</v>
       </c>
       <c r="F215" s="3" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="G215" s="3" t="s">
-        <v>866</v>
+        <v>853</v>
       </c>
       <c r="H215" s="3" t="s">
-        <v>866</v>
+        <v>817</v>
       </c>
       <c r="I215" s="3"/>
       <c r="J215" s="3" t="s">
+        <v>854</v>
+      </c>
+      <c r="K215" s="3" t="s">
+        <v>853</v>
+      </c>
+      <c r="L215" s="3" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="216" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A216" s="3" t="s">
+        <v>764</v>
+      </c>
+      <c r="B216" s="3"/>
+      <c r="C216" s="3" t="s">
+        <v>863</v>
+      </c>
+      <c r="D216" s="3" t="s">
+        <v>864</v>
+      </c>
+      <c r="E216" s="3" t="s">
+        <v>851</v>
+      </c>
+      <c r="F216" s="3" t="s">
+        <v>865</v>
+      </c>
+      <c r="G216" s="3" t="s">
+        <v>866</v>
+      </c>
+      <c r="H216" s="3" t="s">
+        <v>866</v>
+      </c>
+      <c r="I216" s="3"/>
+      <c r="J216" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="K215" s="3" t="s">
+      <c r="K216" s="3" t="s">
         <v>866</v>
       </c>
-      <c r="L215" s="3" t="s">
+      <c r="L216" s="3" t="s">
         <v>855</v>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dvagov-my.sharepoint.com/personal/bernard_chan_va_gov/Documents/Microsoft Teams Chat Files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="47" documentId="11_87A73CECC8785890643FEBC9776139824E07390D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BBDFB50C-05FA-4165-95BE-D76492117E0F}"/>
+  <xr:revisionPtr revIDLastSave="50" documentId="11_87A73CECC8785890643FEBC9776139824E07390D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C7C0600-0369-45DC-AD5C-D29C9D536A08}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9458,13 +9458,13 @@
         <v>782</v>
       </c>
       <c r="D195" s="3" t="s">
-        <v>869</v>
+        <v>783</v>
       </c>
       <c r="E195" s="3" t="s">
-        <v>870</v>
+        <v>780</v>
       </c>
       <c r="F195" s="3" t="s">
-        <v>871</v>
+        <v>784</v>
       </c>
       <c r="G195" s="3" t="s">
         <v>129</v>
@@ -9492,13 +9492,13 @@
         <v>785</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>783</v>
+        <v>869</v>
       </c>
       <c r="E196" s="3" t="s">
-        <v>780</v>
+        <v>870</v>
       </c>
       <c r="F196" s="3" t="s">
-        <v>784</v>
+        <v>871</v>
       </c>
       <c r="G196" s="3" t="s">
         <v>129</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dvagov-my.sharepoint.com/personal/bernard_chan_va_gov/Documents/Microsoft Teams Chat Files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="50" documentId="11_87A73CECC8785890643FEBC9776139824E07390D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C7C0600-0369-45DC-AD5C-D29C9D536A08}"/>
+  <xr:revisionPtr revIDLastSave="63" documentId="11_87A73CECC8785890643FEBC9776139824E07390D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4742EE64-3A2A-4E53-BCDD-E223680C7C31}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2056" uniqueCount="873">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2066" uniqueCount="875">
   <si>
     <t>category</t>
   </si>
@@ -2655,6 +2655,12 @@
   </si>
   <si>
     <t>U 21</t>
+  </si>
+  <si>
+    <t>Glucerna Rich Chocolate</t>
+  </si>
+  <si>
+    <t>24 x 240 mL</t>
   </si>
 </sst>
 </file>
@@ -2736,8 +2742,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Items" displayName="Items" ref="A1:L216">
-  <autoFilter ref="A1:L216" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Items" displayName="Items" ref="A1:L217">
+  <autoFilter ref="A1:L217" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="category"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="shelf"/>
@@ -3041,7 +3047,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L216"/>
+  <dimension ref="A1:L217"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" style="1" customWidth="1"/>
@@ -8712,17 +8718,17 @@
         <v>690</v>
       </c>
       <c r="D173" s="3" t="s">
-        <v>698</v>
+        <v>873</v>
       </c>
       <c r="E173" s="3" t="s">
-        <v>684</v>
+        <v>874</v>
       </c>
       <c r="F173" s="3"/>
       <c r="G173" s="3" t="s">
         <v>699</v>
       </c>
       <c r="H173" s="3" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="I173" s="3" t="s">
         <v>692</v>
@@ -8731,10 +8737,10 @@
         <v>687</v>
       </c>
       <c r="K173" s="3" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="L173" s="3" t="s">
-        <v>700</v>
+        <v>693</v>
       </c>
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.25">
@@ -8746,10 +8752,10 @@
         <v>690</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="E174" s="3" t="s">
-        <v>702</v>
+        <v>684</v>
       </c>
       <c r="F174" s="3"/>
       <c r="G174" s="3" t="s">
@@ -8777,32 +8783,32 @@
       </c>
       <c r="B175" s="3"/>
       <c r="C175" s="3" t="s">
-        <v>682</v>
+        <v>690</v>
       </c>
       <c r="D175" s="3" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="E175" s="3" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="F175" s="3"/>
       <c r="G175" s="3" t="s">
-        <v>101</v>
+        <v>699</v>
       </c>
       <c r="H175" s="3" t="s">
-        <v>577</v>
+        <v>699</v>
       </c>
       <c r="I175" s="3" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
       <c r="J175" s="3" t="s">
-        <v>103</v>
+        <v>687</v>
       </c>
       <c r="K175" s="3" t="s">
-        <v>101</v>
+        <v>699</v>
       </c>
       <c r="L175" s="3" t="s">
-        <v>705</v>
+        <v>700</v>
       </c>
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.25">
@@ -8811,23 +8817,23 @@
       </c>
       <c r="B176" s="3"/>
       <c r="C176" s="3" t="s">
-        <v>690</v>
+        <v>682</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="E176" s="3" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="F176" s="3"/>
       <c r="G176" s="3" t="s">
         <v>101</v>
       </c>
       <c r="H176" s="3" t="s">
-        <v>102</v>
+        <v>577</v>
       </c>
       <c r="I176" s="3" t="s">
-        <v>692</v>
+        <v>686</v>
       </c>
       <c r="J176" s="3" t="s">
         <v>103</v>
@@ -8836,7 +8842,7 @@
         <v>101</v>
       </c>
       <c r="L176" s="3" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.25">
@@ -8845,23 +8851,23 @@
       </c>
       <c r="B177" s="3"/>
       <c r="C177" s="3" t="s">
-        <v>682</v>
+        <v>690</v>
       </c>
       <c r="D177" s="3" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="E177" s="3" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="F177" s="3"/>
       <c r="G177" s="3" t="s">
         <v>101</v>
       </c>
       <c r="H177" s="3" t="s">
-        <v>577</v>
+        <v>102</v>
       </c>
       <c r="I177" s="3" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
       <c r="J177" s="3" t="s">
         <v>103</v>
@@ -8870,7 +8876,7 @@
         <v>101</v>
       </c>
       <c r="L177" s="3" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
     </row>
     <row r="178" spans="1:12" x14ac:dyDescent="0.25">
@@ -8882,29 +8888,29 @@
         <v>682</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="E178" s="3" t="s">
-        <v>684</v>
+        <v>710</v>
       </c>
       <c r="F178" s="3"/>
       <c r="G178" s="3" t="s">
-        <v>685</v>
+        <v>101</v>
       </c>
       <c r="H178" s="3" t="s">
-        <v>685</v>
+        <v>577</v>
       </c>
       <c r="I178" s="3" t="s">
         <v>686</v>
       </c>
       <c r="J178" s="3" t="s">
-        <v>687</v>
+        <v>103</v>
       </c>
       <c r="K178" s="3" t="s">
-        <v>685</v>
+        <v>101</v>
       </c>
       <c r="L178" s="3" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
     </row>
     <row r="179" spans="1:12" x14ac:dyDescent="0.25">
@@ -8916,29 +8922,29 @@
         <v>682</v>
       </c>
       <c r="D179" s="3" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="E179" s="3" t="s">
-        <v>715</v>
+        <v>684</v>
       </c>
       <c r="F179" s="3"/>
       <c r="G179" s="3" t="s">
-        <v>129</v>
+        <v>685</v>
       </c>
       <c r="H179" s="3" t="s">
-        <v>716</v>
+        <v>685</v>
       </c>
       <c r="I179" s="3" t="s">
         <v>686</v>
       </c>
       <c r="J179" s="3" t="s">
-        <v>131</v>
+        <v>687</v>
       </c>
       <c r="K179" s="3" t="s">
-        <v>129</v>
+        <v>685</v>
       </c>
       <c r="L179" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.25">
@@ -8950,29 +8956,29 @@
         <v>682</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="E180" s="3" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="F180" s="3"/>
       <c r="G180" s="3" t="s">
-        <v>720</v>
+        <v>129</v>
       </c>
       <c r="H180" s="3" t="s">
-        <v>721</v>
+        <v>716</v>
       </c>
       <c r="I180" s="3" t="s">
         <v>686</v>
       </c>
       <c r="J180" s="3" t="s">
-        <v>722</v>
+        <v>131</v>
       </c>
       <c r="K180" s="3" t="s">
-        <v>720</v>
+        <v>129</v>
       </c>
       <c r="L180" s="3" t="s">
-        <v>723</v>
+        <v>717</v>
       </c>
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.25">
@@ -8984,7 +8990,7 @@
         <v>682</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>724</v>
+        <v>718</v>
       </c>
       <c r="E181" s="3" t="s">
         <v>719</v>
@@ -9018,29 +9024,29 @@
         <v>682</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E182" s="3" t="s">
-        <v>684</v>
+        <v>719</v>
       </c>
       <c r="F182" s="3"/>
       <c r="G182" s="3" t="s">
-        <v>685</v>
+        <v>720</v>
       </c>
       <c r="H182" s="3" t="s">
-        <v>685</v>
+        <v>721</v>
       </c>
       <c r="I182" s="3" t="s">
         <v>686</v>
       </c>
       <c r="J182" s="3" t="s">
-        <v>687</v>
+        <v>722</v>
       </c>
       <c r="K182" s="3" t="s">
-        <v>685</v>
+        <v>720</v>
       </c>
       <c r="L182" s="3" t="s">
-        <v>713</v>
+        <v>723</v>
       </c>
     </row>
     <row r="183" spans="1:12" x14ac:dyDescent="0.25">
@@ -9052,63 +9058,63 @@
         <v>682</v>
       </c>
       <c r="D183" s="3" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E183" s="3" t="s">
-        <v>727</v>
+        <v>684</v>
       </c>
       <c r="F183" s="3"/>
       <c r="G183" s="3" t="s">
-        <v>728</v>
+        <v>685</v>
       </c>
       <c r="H183" s="3" t="s">
-        <v>729</v>
+        <v>685</v>
       </c>
       <c r="I183" s="3" t="s">
         <v>686</v>
       </c>
       <c r="J183" s="3" t="s">
-        <v>730</v>
+        <v>687</v>
       </c>
       <c r="K183" s="3" t="s">
-        <v>728</v>
+        <v>685</v>
       </c>
       <c r="L183" s="3" t="s">
-        <v>731</v>
+        <v>713</v>
       </c>
     </row>
     <row r="184" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A184" s="3" t="s">
-        <v>732</v>
+        <v>681</v>
       </c>
       <c r="B184" s="3"/>
       <c r="C184" s="3" t="s">
-        <v>733</v>
+        <v>682</v>
       </c>
       <c r="D184" s="3" t="s">
-        <v>734</v>
+        <v>726</v>
       </c>
       <c r="E184" s="3" t="s">
-        <v>735</v>
-      </c>
-      <c r="F184" s="3" t="s">
-        <v>736</v>
-      </c>
+        <v>727</v>
+      </c>
+      <c r="F184" s="3"/>
       <c r="G184" s="3" t="s">
-        <v>737</v>
+        <v>728</v>
       </c>
       <c r="H184" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="I184" s="3"/>
+        <v>729</v>
+      </c>
+      <c r="I184" s="3" t="s">
+        <v>686</v>
+      </c>
       <c r="J184" s="3" t="s">
-        <v>738</v>
+        <v>730</v>
       </c>
       <c r="K184" s="3" t="s">
-        <v>737</v>
+        <v>728</v>
       </c>
       <c r="L184" s="3" t="s">
-        <v>739</v>
+        <v>731</v>
       </c>
     </row>
     <row r="185" spans="1:12" x14ac:dyDescent="0.25">
@@ -9117,32 +9123,32 @@
       </c>
       <c r="B185" s="3"/>
       <c r="C185" s="3" t="s">
-        <v>740</v>
+        <v>733</v>
       </c>
       <c r="D185" s="3" t="s">
-        <v>741</v>
+        <v>734</v>
       </c>
       <c r="E185" s="3" t="s">
-        <v>742</v>
+        <v>735</v>
       </c>
       <c r="F185" s="3" t="s">
-        <v>743</v>
+        <v>736</v>
       </c>
       <c r="G185" s="3" t="s">
-        <v>121</v>
+        <v>737</v>
       </c>
       <c r="H185" s="3" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="I185" s="3"/>
       <c r="J185" s="3" t="s">
-        <v>82</v>
+        <v>738</v>
       </c>
       <c r="K185" s="3" t="s">
-        <v>121</v>
+        <v>737</v>
       </c>
       <c r="L185" s="3" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
     </row>
     <row r="186" spans="1:12" x14ac:dyDescent="0.25">
@@ -9151,32 +9157,32 @@
       </c>
       <c r="B186" s="3"/>
       <c r="C186" s="3" t="s">
-        <v>745</v>
+        <v>740</v>
       </c>
       <c r="D186" s="3" t="s">
-        <v>746</v>
+        <v>741</v>
       </c>
       <c r="E186" s="3" t="s">
-        <v>319</v>
+        <v>742</v>
       </c>
       <c r="F186" s="3" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="G186" s="3" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="H186" s="3" t="s">
-        <v>716</v>
+        <v>121</v>
       </c>
       <c r="I186" s="3"/>
       <c r="J186" s="3" t="s">
-        <v>131</v>
+        <v>82</v>
       </c>
       <c r="K186" s="3" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="L186" s="3" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
     </row>
     <row r="187" spans="1:12" x14ac:dyDescent="0.25">
@@ -9185,32 +9191,32 @@
       </c>
       <c r="B187" s="3"/>
       <c r="C187" s="3" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="D187" s="3" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="E187" s="3" t="s">
-        <v>751</v>
+        <v>319</v>
       </c>
       <c r="F187" s="3" t="s">
-        <v>752</v>
+        <v>747</v>
       </c>
       <c r="G187" s="3" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="H187" s="3" t="s">
-        <v>135</v>
+        <v>716</v>
       </c>
       <c r="I187" s="3"/>
       <c r="J187" s="3" t="s">
-        <v>82</v>
+        <v>131</v>
       </c>
       <c r="K187" s="3" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="L187" s="3" t="s">
-        <v>753</v>
+        <v>748</v>
       </c>
     </row>
     <row r="188" spans="1:12" x14ac:dyDescent="0.25">
@@ -9219,16 +9225,16 @@
       </c>
       <c r="B188" s="3"/>
       <c r="C188" s="3" t="s">
-        <v>754</v>
+        <v>749</v>
       </c>
       <c r="D188" s="3" t="s">
-        <v>755</v>
+        <v>750</v>
       </c>
       <c r="E188" s="3" t="s">
-        <v>756</v>
+        <v>751</v>
       </c>
       <c r="F188" s="3" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="G188" s="3" t="s">
         <v>135</v>
@@ -9244,7 +9250,7 @@
         <v>135</v>
       </c>
       <c r="L188" s="3" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
     </row>
     <row r="189" spans="1:12" x14ac:dyDescent="0.25">
@@ -9253,16 +9259,16 @@
       </c>
       <c r="B189" s="3"/>
       <c r="C189" s="3" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="D189" s="3" t="s">
         <v>755</v>
       </c>
       <c r="E189" s="3" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="F189" s="3" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="G189" s="3" t="s">
         <v>135</v>
@@ -9287,64 +9293,64 @@
       </c>
       <c r="B190" s="3"/>
       <c r="C190" s="3" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>761</v>
-      </c>
-      <c r="E190" s="3"/>
+        <v>755</v>
+      </c>
+      <c r="E190" s="3" t="s">
+        <v>759</v>
+      </c>
       <c r="F190" s="3" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="G190" s="3" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="H190" s="3" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="I190" s="3"/>
       <c r="J190" s="3" t="s">
         <v>82</v>
       </c>
       <c r="K190" s="3" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="L190" s="3" t="s">
-        <v>763</v>
+        <v>757</v>
       </c>
     </row>
     <row r="191" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A191" s="3" t="s">
-        <v>764</v>
+        <v>732</v>
       </c>
       <c r="B191" s="3"/>
       <c r="C191" s="3" t="s">
-        <v>765</v>
+        <v>760</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>766</v>
-      </c>
-      <c r="E191" s="3" t="s">
-        <v>767</v>
-      </c>
+        <v>761</v>
+      </c>
+      <c r="E191" s="3"/>
       <c r="F191" s="3" t="s">
-        <v>768</v>
+        <v>762</v>
       </c>
       <c r="G191" s="3" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="H191" s="3" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="I191" s="3"/>
       <c r="J191" s="3" t="s">
-        <v>131</v>
+        <v>82</v>
       </c>
       <c r="K191" s="3" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="L191" s="3" t="s">
-        <v>769</v>
+        <v>763</v>
       </c>
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.25">
@@ -9353,29 +9359,29 @@
       </c>
       <c r="B192" s="3"/>
       <c r="C192" s="3" t="s">
-        <v>770</v>
+        <v>765</v>
       </c>
       <c r="D192" s="3" t="s">
-        <v>771</v>
+        <v>766</v>
       </c>
       <c r="E192" s="3" t="s">
-        <v>772</v>
+        <v>767</v>
       </c>
       <c r="F192" s="3" t="s">
-        <v>773</v>
+        <v>768</v>
       </c>
       <c r="G192" s="3" t="s">
-        <v>17</v>
+        <v>129</v>
       </c>
       <c r="H192" s="3" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="I192" s="3"/>
       <c r="J192" s="3" t="s">
-        <v>18</v>
+        <v>131</v>
       </c>
       <c r="K192" s="3" t="s">
-        <v>17</v>
+        <v>129</v>
       </c>
       <c r="L192" s="3" t="s">
         <v>769</v>
@@ -9387,16 +9393,16 @@
       </c>
       <c r="B193" s="3"/>
       <c r="C193" s="3" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="D193" s="3" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="E193" s="3" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="F193" s="3" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="G193" s="3" t="s">
         <v>17</v>
@@ -9421,29 +9427,29 @@
       </c>
       <c r="B194" s="3"/>
       <c r="C194" s="3" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="E194" s="3" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="F194" s="3" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="G194" s="3" t="s">
-        <v>129</v>
+        <v>17</v>
       </c>
       <c r="H194" s="3" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="I194" s="3"/>
       <c r="J194" s="3" t="s">
-        <v>131</v>
+        <v>18</v>
       </c>
       <c r="K194" s="3" t="s">
-        <v>129</v>
+        <v>17</v>
       </c>
       <c r="L194" s="3" t="s">
         <v>769</v>
@@ -9455,16 +9461,16 @@
       </c>
       <c r="B195" s="3"/>
       <c r="C195" s="3" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="D195" s="3" t="s">
-        <v>783</v>
+        <v>869</v>
       </c>
       <c r="E195" s="3" t="s">
-        <v>780</v>
+        <v>870</v>
       </c>
       <c r="F195" s="3" t="s">
-        <v>784</v>
+        <v>871</v>
       </c>
       <c r="G195" s="3" t="s">
         <v>129</v>
@@ -9489,16 +9495,16 @@
       </c>
       <c r="B196" s="3"/>
       <c r="C196" s="3" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>869</v>
+        <v>779</v>
       </c>
       <c r="E196" s="3" t="s">
-        <v>870</v>
+        <v>780</v>
       </c>
       <c r="F196" s="3" t="s">
-        <v>871</v>
+        <v>781</v>
       </c>
       <c r="G196" s="3" t="s">
         <v>129</v>
@@ -9523,16 +9529,16 @@
       </c>
       <c r="B197" s="3"/>
       <c r="C197" s="3" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="E197" s="3" t="s">
-        <v>787</v>
+        <v>780</v>
       </c>
       <c r="F197" s="3" t="s">
-        <v>788</v>
+        <v>784</v>
       </c>
       <c r="G197" s="3" t="s">
         <v>129</v>
@@ -9557,32 +9563,32 @@
       </c>
       <c r="B198" s="3"/>
       <c r="C198" s="3" t="s">
-        <v>796</v>
+        <v>789</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>790</v>
+        <v>786</v>
       </c>
       <c r="E198" s="3" t="s">
-        <v>791</v>
+        <v>787</v>
       </c>
       <c r="F198" s="3" t="s">
-        <v>792</v>
+        <v>788</v>
       </c>
       <c r="G198" s="3" t="s">
-        <v>793</v>
+        <v>129</v>
       </c>
       <c r="H198" s="3" t="s">
-        <v>794</v>
+        <v>130</v>
       </c>
       <c r="I198" s="3"/>
       <c r="J198" s="3" t="s">
         <v>131</v>
       </c>
       <c r="K198" s="3" t="s">
-        <v>793</v>
+        <v>129</v>
       </c>
       <c r="L198" s="3" t="s">
-        <v>795</v>
+        <v>769</v>
       </c>
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.25">
@@ -9591,32 +9597,32 @@
       </c>
       <c r="B199" s="3"/>
       <c r="C199" s="3" t="s">
-        <v>801</v>
+        <v>796</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>797</v>
+        <v>790</v>
       </c>
       <c r="E199" s="3" t="s">
-        <v>798</v>
+        <v>791</v>
       </c>
       <c r="F199" s="3" t="s">
-        <v>799</v>
+        <v>792</v>
       </c>
       <c r="G199" s="3" t="s">
-        <v>264</v>
+        <v>793</v>
       </c>
       <c r="H199" s="3" t="s">
-        <v>263</v>
+        <v>794</v>
       </c>
       <c r="I199" s="3"/>
       <c r="J199" s="3" t="s">
-        <v>82</v>
+        <v>131</v>
       </c>
       <c r="K199" s="3" t="s">
-        <v>264</v>
+        <v>793</v>
       </c>
       <c r="L199" s="3" t="s">
-        <v>800</v>
+        <v>795</v>
       </c>
     </row>
     <row r="200" spans="1:12" x14ac:dyDescent="0.25">
@@ -9625,16 +9631,16 @@
       </c>
       <c r="B200" s="3"/>
       <c r="C200" s="3" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="D200" s="3" t="s">
         <v>797</v>
       </c>
       <c r="E200" s="3" t="s">
-        <v>587</v>
+        <v>798</v>
       </c>
       <c r="F200" s="3" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="G200" s="3" t="s">
         <v>264</v>
@@ -9659,20 +9665,22 @@
       </c>
       <c r="B201" s="3"/>
       <c r="C201" s="3" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>804</v>
-      </c>
-      <c r="E201" s="3"/>
+        <v>797</v>
+      </c>
+      <c r="E201" s="3" t="s">
+        <v>587</v>
+      </c>
       <c r="F201" s="3" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="G201" s="3" t="s">
         <v>264</v>
       </c>
       <c r="H201" s="3" t="s">
-        <v>446</v>
+        <v>263</v>
       </c>
       <c r="I201" s="3"/>
       <c r="J201" s="3" t="s">
@@ -9682,7 +9690,7 @@
         <v>264</v>
       </c>
       <c r="L201" s="3" t="s">
-        <v>806</v>
+        <v>800</v>
       </c>
     </row>
     <row r="202" spans="1:12" x14ac:dyDescent="0.25">
@@ -9691,32 +9699,30 @@
       </c>
       <c r="B202" s="3"/>
       <c r="C202" s="3" t="s">
-        <v>812</v>
+        <v>807</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>808</v>
-      </c>
-      <c r="E202" s="3" t="s">
-        <v>809</v>
-      </c>
+        <v>804</v>
+      </c>
+      <c r="E202" s="3"/>
       <c r="F202" s="3" t="s">
-        <v>810</v>
+        <v>805</v>
       </c>
       <c r="G202" s="3" t="s">
-        <v>202</v>
+        <v>264</v>
       </c>
       <c r="H202" s="3" t="s">
-        <v>121</v>
+        <v>446</v>
       </c>
       <c r="I202" s="3"/>
       <c r="J202" s="3" t="s">
-        <v>203</v>
+        <v>82</v>
       </c>
       <c r="K202" s="3" t="s">
-        <v>202</v>
+        <v>264</v>
       </c>
       <c r="L202" s="3" t="s">
-        <v>811</v>
+        <v>806</v>
       </c>
     </row>
     <row r="203" spans="1:12" x14ac:dyDescent="0.25">
@@ -9725,32 +9731,32 @@
       </c>
       <c r="B203" s="3"/>
       <c r="C203" s="3" t="s">
-        <v>820</v>
+        <v>812</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>813</v>
+        <v>808</v>
       </c>
       <c r="E203" s="3" t="s">
-        <v>814</v>
+        <v>809</v>
       </c>
       <c r="F203" s="3" t="s">
-        <v>815</v>
+        <v>810</v>
       </c>
       <c r="G203" s="3" t="s">
-        <v>816</v>
+        <v>202</v>
       </c>
       <c r="H203" s="3" t="s">
-        <v>817</v>
+        <v>121</v>
       </c>
       <c r="I203" s="3"/>
       <c r="J203" s="3" t="s">
-        <v>818</v>
+        <v>203</v>
       </c>
       <c r="K203" s="3" t="s">
-        <v>816</v>
+        <v>202</v>
       </c>
       <c r="L203" s="3" t="s">
-        <v>819</v>
+        <v>811</v>
       </c>
     </row>
     <row r="204" spans="1:12" x14ac:dyDescent="0.25">
@@ -9759,32 +9765,32 @@
       </c>
       <c r="B204" s="3"/>
       <c r="C204" s="3" t="s">
-        <v>825</v>
+        <v>820</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>821</v>
+        <v>813</v>
       </c>
       <c r="E204" s="3" t="s">
-        <v>822</v>
+        <v>814</v>
       </c>
       <c r="F204" s="3" t="s">
-        <v>823</v>
+        <v>815</v>
       </c>
       <c r="G204" s="3" t="s">
-        <v>121</v>
+        <v>816</v>
       </c>
       <c r="H204" s="3" t="s">
-        <v>121</v>
+        <v>817</v>
       </c>
       <c r="I204" s="3"/>
       <c r="J204" s="3" t="s">
-        <v>82</v>
+        <v>818</v>
       </c>
       <c r="K204" s="3" t="s">
-        <v>121</v>
+        <v>816</v>
       </c>
       <c r="L204" s="3" t="s">
-        <v>824</v>
+        <v>819</v>
       </c>
     </row>
     <row r="205" spans="1:12" x14ac:dyDescent="0.25">
@@ -9793,16 +9799,16 @@
       </c>
       <c r="B205" s="3"/>
       <c r="C205" s="3" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="D205" s="3" t="s">
         <v>821</v>
       </c>
       <c r="E205" s="3" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
       <c r="F205" s="3" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="G205" s="3" t="s">
         <v>121</v>
@@ -9827,32 +9833,32 @@
       </c>
       <c r="B206" s="3"/>
       <c r="C206" s="3" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>829</v>
+        <v>821</v>
       </c>
       <c r="E206" s="3" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="F206" s="3" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="G206" s="3" t="s">
-        <v>264</v>
+        <v>121</v>
       </c>
       <c r="H206" s="3" t="s">
-        <v>446</v>
+        <v>121</v>
       </c>
       <c r="I206" s="3"/>
       <c r="J206" s="3" t="s">
         <v>82</v>
       </c>
       <c r="K206" s="3" t="s">
-        <v>264</v>
+        <v>121</v>
       </c>
       <c r="L206" s="3" t="s">
-        <v>832</v>
+        <v>824</v>
       </c>
     </row>
     <row r="207" spans="1:12" x14ac:dyDescent="0.25">
@@ -9861,7 +9867,7 @@
       </c>
       <c r="B207" s="3"/>
       <c r="C207" s="3" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="D207" s="3" t="s">
         <v>829</v>
@@ -9870,7 +9876,7 @@
         <v>830</v>
       </c>
       <c r="F207" s="3" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="G207" s="3" t="s">
         <v>264</v>
@@ -9895,32 +9901,32 @@
       </c>
       <c r="B208" s="3"/>
       <c r="C208" s="3" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>836</v>
+        <v>829</v>
       </c>
       <c r="E208" s="3" t="s">
-        <v>837</v>
+        <v>830</v>
       </c>
       <c r="F208" s="3" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
       <c r="G208" s="3" t="s">
-        <v>816</v>
+        <v>264</v>
       </c>
       <c r="H208" s="3" t="s">
-        <v>817</v>
+        <v>446</v>
       </c>
       <c r="I208" s="3"/>
       <c r="J208" s="3" t="s">
-        <v>818</v>
+        <v>82</v>
       </c>
       <c r="K208" s="3" t="s">
-        <v>816</v>
+        <v>264</v>
       </c>
       <c r="L208" s="3" t="s">
-        <v>819</v>
+        <v>832</v>
       </c>
     </row>
     <row r="209" spans="1:12" x14ac:dyDescent="0.25">
@@ -9929,30 +9935,32 @@
       </c>
       <c r="B209" s="3"/>
       <c r="C209" s="3" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="D209" s="3" t="s">
-        <v>840</v>
-      </c>
-      <c r="E209" s="3"/>
+        <v>836</v>
+      </c>
+      <c r="E209" s="3" t="s">
+        <v>837</v>
+      </c>
       <c r="F209" s="3" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="G209" s="3" t="s">
-        <v>264</v>
+        <v>816</v>
       </c>
       <c r="H209" s="3" t="s">
-        <v>263</v>
+        <v>817</v>
       </c>
       <c r="I209" s="3"/>
       <c r="J209" s="3" t="s">
-        <v>82</v>
+        <v>818</v>
       </c>
       <c r="K209" s="3" t="s">
-        <v>264</v>
+        <v>816</v>
       </c>
       <c r="L209" s="3" t="s">
-        <v>842</v>
+        <v>819</v>
       </c>
     </row>
     <row r="210" spans="1:12" x14ac:dyDescent="0.25">
@@ -9961,14 +9969,14 @@
       </c>
       <c r="B210" s="3"/>
       <c r="C210" s="3" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="D210" s="3" t="s">
         <v>840</v>
       </c>
       <c r="E210" s="3"/>
       <c r="F210" s="3" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="G210" s="3" t="s">
         <v>264</v>
@@ -9993,30 +10001,30 @@
       </c>
       <c r="B211" s="3"/>
       <c r="C211" s="3" t="s">
-        <v>872</v>
+        <v>845</v>
       </c>
       <c r="D211" s="3" t="s">
-        <v>846</v>
-      </c>
-      <c r="E211" s="3" t="s">
-        <v>847</v>
-      </c>
-      <c r="F211" s="3"/>
+        <v>840</v>
+      </c>
+      <c r="E211" s="3"/>
+      <c r="F211" s="3" t="s">
+        <v>844</v>
+      </c>
       <c r="G211" s="3" t="s">
-        <v>246</v>
+        <v>264</v>
       </c>
       <c r="H211" s="3" t="s">
-        <v>244</v>
+        <v>263</v>
       </c>
       <c r="I211" s="3"/>
       <c r="J211" s="3" t="s">
-        <v>245</v>
+        <v>82</v>
       </c>
       <c r="K211" s="3" t="s">
-        <v>246</v>
+        <v>264</v>
       </c>
       <c r="L211" s="3" t="s">
-        <v>848</v>
+        <v>842</v>
       </c>
     </row>
     <row r="212" spans="1:12" x14ac:dyDescent="0.25">
@@ -10025,32 +10033,30 @@
       </c>
       <c r="B212" s="3"/>
       <c r="C212" s="3" t="s">
-        <v>849</v>
+        <v>872</v>
       </c>
       <c r="D212" s="3" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
       <c r="E212" s="3" t="s">
-        <v>851</v>
-      </c>
-      <c r="F212" s="3" t="s">
-        <v>852</v>
-      </c>
+        <v>847</v>
+      </c>
+      <c r="F212" s="3"/>
       <c r="G212" s="3" t="s">
-        <v>853</v>
+        <v>246</v>
       </c>
       <c r="H212" s="3" t="s">
-        <v>817</v>
+        <v>244</v>
       </c>
       <c r="I212" s="3"/>
       <c r="J212" s="3" t="s">
-        <v>854</v>
+        <v>245</v>
       </c>
       <c r="K212" s="3" t="s">
-        <v>853</v>
+        <v>246</v>
       </c>
       <c r="L212" s="3" t="s">
-        <v>855</v>
+        <v>848</v>
       </c>
     </row>
     <row r="213" spans="1:12" x14ac:dyDescent="0.25">
@@ -10065,10 +10071,10 @@
         <v>850</v>
       </c>
       <c r="E213" s="3" t="s">
-        <v>856</v>
+        <v>851</v>
       </c>
       <c r="F213" s="3" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="G213" s="3" t="s">
         <v>853</v>
@@ -10093,16 +10099,16 @@
       </c>
       <c r="B214" s="3"/>
       <c r="C214" s="3" t="s">
-        <v>858</v>
+        <v>849</v>
       </c>
       <c r="D214" s="3" t="s">
-        <v>859</v>
+        <v>850</v>
       </c>
       <c r="E214" s="3" t="s">
-        <v>851</v>
+        <v>856</v>
       </c>
       <c r="F214" s="3" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="G214" s="3" t="s">
         <v>853</v>
@@ -10118,7 +10124,7 @@
         <v>853</v>
       </c>
       <c r="L214" s="3" t="s">
-        <v>861</v>
+        <v>855</v>
       </c>
     </row>
     <row r="215" spans="1:12" x14ac:dyDescent="0.25">
@@ -10133,10 +10139,10 @@
         <v>859</v>
       </c>
       <c r="E215" s="3" t="s">
-        <v>856</v>
+        <v>851</v>
       </c>
       <c r="F215" s="3" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="G215" s="3" t="s">
         <v>853</v>
@@ -10161,31 +10167,65 @@
       </c>
       <c r="B216" s="3"/>
       <c r="C216" s="3" t="s">
-        <v>863</v>
+        <v>858</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>864</v>
+        <v>859</v>
       </c>
       <c r="E216" s="3" t="s">
-        <v>851</v>
+        <v>856</v>
       </c>
       <c r="F216" s="3" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="G216" s="3" t="s">
-        <v>866</v>
+        <v>853</v>
       </c>
       <c r="H216" s="3" t="s">
-        <v>866</v>
+        <v>817</v>
       </c>
       <c r="I216" s="3"/>
       <c r="J216" s="3" t="s">
+        <v>854</v>
+      </c>
+      <c r="K216" s="3" t="s">
+        <v>853</v>
+      </c>
+      <c r="L216" s="3" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="217" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A217" s="3" t="s">
+        <v>764</v>
+      </c>
+      <c r="B217" s="3"/>
+      <c r="C217" s="3" t="s">
+        <v>863</v>
+      </c>
+      <c r="D217" s="3" t="s">
+        <v>864</v>
+      </c>
+      <c r="E217" s="3" t="s">
+        <v>851</v>
+      </c>
+      <c r="F217" s="3" t="s">
+        <v>865</v>
+      </c>
+      <c r="G217" s="3" t="s">
+        <v>866</v>
+      </c>
+      <c r="H217" s="3" t="s">
+        <v>866</v>
+      </c>
+      <c r="I217" s="3"/>
+      <c r="J217" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="K216" s="3" t="s">
+      <c r="K217" s="3" t="s">
         <v>866</v>
       </c>
-      <c r="L216" s="3" t="s">
+      <c r="L217" s="3" t="s">
         <v>855</v>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dvagov-my.sharepoint.com/personal/bernard_chan_va_gov/Documents/Microsoft Teams Chat Files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="63" documentId="11_87A73CECC8785890643FEBC9776139824E07390D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4742EE64-3A2A-4E53-BCDD-E223680C7C31}"/>
+  <xr:revisionPtr revIDLastSave="77" documentId="11_87A73CECC8785890643FEBC9776139824E07390D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{07D158D4-1413-4ECE-AE74-B10956DAE3D1}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2066" uniqueCount="875">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2070" uniqueCount="878">
   <si>
     <t>category</t>
   </si>
@@ -1172,9 +1172,6 @@
     <t>S 28</t>
   </si>
   <si>
-    <t>Catheter Tip Syringe</t>
-  </si>
-  <si>
     <t>50mL</t>
   </si>
   <si>
@@ -1199,9 +1196,6 @@
     <t>3mL 25G 5/8"</t>
   </si>
   <si>
-    <t>S 32</t>
-  </si>
-  <si>
     <t>3mL 25G 1"</t>
   </si>
   <si>
@@ -2661,6 +2655,21 @@
   </si>
   <si>
     <t>24 x 240 mL</t>
+  </si>
+  <si>
+    <t>U 22</t>
+  </si>
+  <si>
+    <t>309620</t>
+  </si>
+  <si>
+    <t>U 23</t>
+  </si>
+  <si>
+    <t>Gentamicin</t>
+  </si>
+  <si>
+    <t>Catheter Tip Syringe (Adapter Tips Available)</t>
   </si>
 </sst>
 </file>
@@ -2742,8 +2751,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Items" displayName="Items" ref="A1:L217">
-  <autoFilter ref="A1:L217" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Items" displayName="Items" ref="A1:L218">
+  <autoFilter ref="A1:L218" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="category"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="shelf"/>
@@ -3047,7 +3056,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L217"/>
+  <dimension ref="A1:L218"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" style="1" customWidth="1"/>
@@ -3894,7 +3903,7 @@
         <v>129</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="I26" s="3"/>
       <c r="J26" s="3" t="s">
@@ -3904,7 +3913,7 @@
         <v>129</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
@@ -3928,7 +3937,7 @@
         <v>17</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="I27" s="3"/>
       <c r="J27" s="3" t="s">
@@ -3938,7 +3947,7 @@
         <v>17</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
@@ -6152,27 +6161,27 @@
         <v>377</v>
       </c>
       <c r="D96" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="E96" s="3" t="s">
         <v>378</v>
-      </c>
-      <c r="E96" s="3" t="s">
-        <v>379</v>
       </c>
       <c r="F96" s="3"/>
       <c r="G96" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="I96" s="3"/>
       <c r="J96" s="3" t="s">
         <v>131</v>
       </c>
       <c r="K96" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L96" s="3" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
@@ -6181,30 +6190,28 @@
       </c>
       <c r="B97" s="3"/>
       <c r="C97" s="3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>317</v>
+        <v>365</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="F97" s="3"/>
       <c r="G97" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="H97" s="3" t="s">
-        <v>135</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="H97" s="3"/>
       <c r="I97" s="3"/>
       <c r="J97" s="3" t="s">
-        <v>131</v>
+        <v>18</v>
       </c>
       <c r="K97" s="3" t="s">
-        <v>130</v>
+        <v>17</v>
       </c>
       <c r="L97" s="3" t="s">
-        <v>382</v>
+        <v>338</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
@@ -6213,13 +6220,13 @@
       </c>
       <c r="B98" s="3"/>
       <c r="C98" s="3" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D98" s="3" t="s">
         <v>365</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F98" s="3"/>
       <c r="G98" s="3" t="s">
@@ -6243,7 +6250,7 @@
       </c>
       <c r="B99" s="3"/>
       <c r="C99" s="3" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D99" s="3" t="s">
         <v>365</v>
@@ -6269,250 +6276,254 @@
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
-        <v>312</v>
+        <v>387</v>
       </c>
       <c r="B100" s="3"/>
       <c r="C100" s="3" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>365</v>
+        <v>389</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="F100" s="3"/>
+        <v>390</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>391</v>
+      </c>
       <c r="G100" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H100" s="3"/>
+        <v>57</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>57</v>
+      </c>
       <c r="I100" s="3"/>
       <c r="J100" s="3" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="K100" s="3" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="L100" s="3" t="s">
-        <v>338</v>
+        <v>392</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B101" s="3"/>
       <c r="C101" s="3" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F101" s="3" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="G101" s="3" t="s">
-        <v>57</v>
+        <v>264</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>57</v>
+        <v>263</v>
       </c>
       <c r="I101" s="3"/>
       <c r="J101" s="3" t="s">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="K101" s="3" t="s">
-        <v>57</v>
+        <v>264</v>
       </c>
       <c r="L101" s="3" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B102" s="3"/>
       <c r="C102" s="3" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>391</v>
-      </c>
-      <c r="E102" s="3" t="s">
-        <v>396</v>
-      </c>
+        <v>398</v>
+      </c>
+      <c r="E102" s="3"/>
       <c r="F102" s="3" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="G102" s="3" t="s">
-        <v>264</v>
+        <v>400</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>263</v>
+        <v>400</v>
       </c>
       <c r="I102" s="3"/>
       <c r="J102" s="3" t="s">
         <v>82</v>
       </c>
       <c r="K102" s="3" t="s">
-        <v>264</v>
+        <v>400</v>
       </c>
       <c r="L102" s="3" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B103" s="3"/>
       <c r="C103" s="3" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="E103" s="3"/>
+        <v>403</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>404</v>
+      </c>
       <c r="F103" s="3" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="G103" s="3" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="I103" s="3"/>
       <c r="J103" s="3" t="s">
-        <v>82</v>
+        <v>408</v>
       </c>
       <c r="K103" s="3" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="L103" s="3" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B104" s="3"/>
       <c r="C104" s="3" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="E104" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="F104" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="G104" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="F104" s="3" t="s">
+      <c r="H104" s="3" t="s">
         <v>407</v>
-      </c>
-      <c r="G104" s="3" t="s">
-        <v>408</v>
-      </c>
-      <c r="H104" s="3" t="s">
-        <v>409</v>
       </c>
       <c r="I104" s="3"/>
       <c r="J104" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="K104" s="3" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="L104" s="3" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B105" s="3"/>
       <c r="C105" s="3" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>405</v>
-      </c>
-      <c r="E105" s="3" t="s">
-        <v>413</v>
-      </c>
+        <v>414</v>
+      </c>
+      <c r="E105" s="3"/>
       <c r="F105" s="3" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G105" s="3" t="s">
-        <v>408</v>
+        <v>109</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>409</v>
+        <v>110</v>
       </c>
       <c r="I105" s="3"/>
       <c r="J105" s="3" t="s">
-        <v>410</v>
+        <v>111</v>
       </c>
       <c r="K105" s="3" t="s">
-        <v>408</v>
+        <v>109</v>
       </c>
       <c r="L105" s="3" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B106" s="3"/>
       <c r="C106" s="3" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>416</v>
-      </c>
-      <c r="E106" s="3"/>
+        <v>418</v>
+      </c>
+      <c r="E106" s="3" t="s">
+        <v>419</v>
+      </c>
       <c r="F106" s="3" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="G106" s="3" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="I106" s="3"/>
       <c r="J106" s="3" t="s">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="K106" s="3" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="L106" s="3" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B107" s="3"/>
       <c r="C107" s="3" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="F107" s="3" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="G107" s="3" t="s">
         <v>121</v>
@@ -6528,25 +6539,25 @@
         <v>121</v>
       </c>
       <c r="L107" s="3" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B108" s="3"/>
       <c r="C108" s="3" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="F108" s="3" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="G108" s="3" t="s">
         <v>121</v>
@@ -6562,25 +6573,23 @@
         <v>121</v>
       </c>
       <c r="L108" s="3" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B109" s="3"/>
       <c r="C109" s="3" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>428</v>
-      </c>
-      <c r="E109" s="3" t="s">
-        <v>429</v>
-      </c>
+        <v>430</v>
+      </c>
+      <c r="E109" s="3"/>
       <c r="F109" s="3" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="G109" s="3" t="s">
         <v>121</v>
@@ -6596,223 +6605,225 @@
         <v>121</v>
       </c>
       <c r="L109" s="3" t="s">
-        <v>423</v>
+        <v>432</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B110" s="3"/>
       <c r="C110" s="3" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="E110" s="3"/>
       <c r="F110" s="3" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="G110" s="3" t="s">
-        <v>121</v>
+        <v>436</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>121</v>
+        <v>437</v>
       </c>
       <c r="I110" s="3"/>
       <c r="J110" s="3" t="s">
-        <v>82</v>
+        <v>438</v>
       </c>
       <c r="K110" s="3" t="s">
-        <v>121</v>
+        <v>436</v>
       </c>
       <c r="L110" s="3" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B111" s="3"/>
       <c r="C111" s="3" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>436</v>
-      </c>
-      <c r="E111" s="3"/>
+        <v>441</v>
+      </c>
+      <c r="E111" s="3" t="s">
+        <v>442</v>
+      </c>
       <c r="F111" s="3" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="G111" s="3" t="s">
-        <v>438</v>
+        <v>264</v>
       </c>
       <c r="H111" s="3" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="I111" s="3"/>
       <c r="J111" s="3" t="s">
-        <v>440</v>
+        <v>82</v>
       </c>
       <c r="K111" s="3" t="s">
-        <v>438</v>
+        <v>264</v>
       </c>
       <c r="L111" s="3" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B112" s="3"/>
       <c r="C112" s="3" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="F112" s="3" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="G112" s="3" t="s">
-        <v>264</v>
+        <v>450</v>
       </c>
       <c r="H112" s="3" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="I112" s="3"/>
       <c r="J112" s="3" t="s">
-        <v>82</v>
+        <v>452</v>
       </c>
       <c r="K112" s="3" t="s">
-        <v>264</v>
+        <v>450</v>
       </c>
       <c r="L112" s="3" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B113" s="3"/>
       <c r="C113" s="3" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="E113" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="F113" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="G113" s="3" t="s">
         <v>450</v>
       </c>
-      <c r="F113" s="3" t="s">
+      <c r="H113" s="3" t="s">
         <v>451</v>
-      </c>
-      <c r="G113" s="3" t="s">
-        <v>452</v>
-      </c>
-      <c r="H113" s="3" t="s">
-        <v>453</v>
       </c>
       <c r="I113" s="3"/>
       <c r="J113" s="3" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="K113" s="3" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="L113" s="3" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
-        <v>389</v>
+        <v>458</v>
       </c>
       <c r="B114" s="3"/>
       <c r="C114" s="3" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>449</v>
+        <v>460</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>457</v>
-      </c>
-      <c r="F114" s="3" t="s">
-        <v>458</v>
-      </c>
+        <v>461</v>
+      </c>
+      <c r="F114" s="3"/>
       <c r="G114" s="3" t="s">
-        <v>452</v>
+        <v>16</v>
       </c>
       <c r="H114" s="3" t="s">
-        <v>453</v>
+        <v>17</v>
       </c>
       <c r="I114" s="3"/>
       <c r="J114" s="3" t="s">
-        <v>454</v>
+        <v>18</v>
       </c>
       <c r="K114" s="3" t="s">
-        <v>452</v>
+        <v>16</v>
       </c>
       <c r="L114" s="3" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B115" s="3"/>
       <c r="C115" s="3" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>463</v>
-      </c>
-      <c r="F115" s="3"/>
+        <v>465</v>
+      </c>
+      <c r="F115" s="3" t="s">
+        <v>466</v>
+      </c>
       <c r="G115" s="3" t="s">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="H115" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="I115" s="3"/>
       <c r="J115" s="3" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="K115" s="3" t="s">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="L115" s="3" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B116" s="3"/>
       <c r="C116" s="3" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="F116" s="3" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="G116" s="3" t="s">
         <v>57</v>
@@ -6828,93 +6839,93 @@
         <v>57</v>
       </c>
       <c r="L116" s="3" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B117" s="3"/>
       <c r="C117" s="3" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="F117" s="3" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="G117" s="3" t="s">
-        <v>57</v>
+        <v>476</v>
       </c>
       <c r="H117" s="3" t="s">
-        <v>58</v>
+        <v>477</v>
       </c>
       <c r="I117" s="3"/>
       <c r="J117" s="3" t="s">
-        <v>59</v>
+        <v>478</v>
       </c>
       <c r="K117" s="3" t="s">
-        <v>57</v>
+        <v>476</v>
       </c>
       <c r="L117" s="3" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B118" s="3"/>
       <c r="C118" s="3" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="F118" s="3" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="G118" s="3" t="s">
-        <v>478</v>
+        <v>57</v>
       </c>
       <c r="H118" s="3" t="s">
-        <v>479</v>
+        <v>58</v>
       </c>
       <c r="I118" s="3"/>
       <c r="J118" s="3" t="s">
-        <v>480</v>
+        <v>59</v>
       </c>
       <c r="K118" s="3" t="s">
-        <v>478</v>
+        <v>57</v>
       </c>
       <c r="L118" s="3" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B119" s="3"/>
       <c r="C119" s="3" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="F119" s="3" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="G119" s="3" t="s">
         <v>57</v>
@@ -6930,25 +6941,25 @@
         <v>57</v>
       </c>
       <c r="L119" s="3" t="s">
-        <v>474</v>
+        <v>487</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B120" s="3"/>
       <c r="C120" s="3" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="F120" s="3" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G120" s="3" t="s">
         <v>57</v>
@@ -6964,25 +6975,25 @@
         <v>57</v>
       </c>
       <c r="L120" s="3" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B121" s="3"/>
       <c r="C121" s="3" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>491</v>
+        <v>470</v>
       </c>
       <c r="F121" s="3" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="G121" s="3" t="s">
         <v>57</v>
@@ -6998,25 +7009,25 @@
         <v>57</v>
       </c>
       <c r="L121" s="3" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B122" s="3"/>
       <c r="C122" s="3" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="F122" s="3" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="G122" s="3" t="s">
         <v>57</v>
@@ -7032,95 +7043,93 @@
         <v>57</v>
       </c>
       <c r="L122" s="3" t="s">
-        <v>496</v>
+        <v>472</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A123" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B123" s="3"/>
       <c r="C123" s="3" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>476</v>
-      </c>
-      <c r="F123" s="3" t="s">
-        <v>499</v>
-      </c>
+        <v>500</v>
+      </c>
+      <c r="F123" s="3"/>
       <c r="G123" s="3" t="s">
-        <v>57</v>
+        <v>501</v>
       </c>
       <c r="H123" s="3" t="s">
-        <v>58</v>
+        <v>450</v>
       </c>
       <c r="I123" s="3"/>
       <c r="J123" s="3" t="s">
-        <v>59</v>
+        <v>502</v>
       </c>
       <c r="K123" s="3" t="s">
-        <v>57</v>
+        <v>501</v>
       </c>
       <c r="L123" s="3" t="s">
-        <v>474</v>
+        <v>503</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B124" s="3"/>
       <c r="C124" s="3" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="F124" s="3"/>
       <c r="G124" s="3" t="s">
-        <v>503</v>
+        <v>58</v>
       </c>
       <c r="H124" s="3" t="s">
-        <v>452</v>
+        <v>444</v>
       </c>
       <c r="I124" s="3"/>
       <c r="J124" s="3" t="s">
-        <v>504</v>
+        <v>59</v>
       </c>
       <c r="K124" s="3" t="s">
-        <v>503</v>
+        <v>58</v>
       </c>
       <c r="L124" s="3" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A125" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B125" s="3"/>
       <c r="C125" s="3" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="F125" s="3"/>
       <c r="G125" s="3" t="s">
         <v>58</v>
       </c>
       <c r="H125" s="3" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="I125" s="3"/>
       <c r="J125" s="3" t="s">
@@ -7130,19 +7139,19 @@
         <v>58</v>
       </c>
       <c r="L125" s="3" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B126" s="3"/>
       <c r="C126" s="3" t="s">
         <v>510</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="E126" s="3" t="s">
         <v>511</v>
@@ -7152,7 +7161,7 @@
         <v>58</v>
       </c>
       <c r="H126" s="3" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="I126" s="3"/>
       <c r="J126" s="3" t="s">
@@ -7162,89 +7171,91 @@
         <v>58</v>
       </c>
       <c r="L126" s="3" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B127" s="3"/>
       <c r="C127" s="3" t="s">
         <v>512</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>507</v>
+        <v>460</v>
       </c>
       <c r="E127" s="3" t="s">
         <v>513</v>
       </c>
       <c r="F127" s="3"/>
       <c r="G127" s="3" t="s">
-        <v>58</v>
+        <v>16</v>
       </c>
       <c r="H127" s="3" t="s">
-        <v>446</v>
+        <v>17</v>
       </c>
       <c r="I127" s="3"/>
       <c r="J127" s="3" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="K127" s="3" t="s">
-        <v>58</v>
+        <v>16</v>
       </c>
       <c r="L127" s="3" t="s">
-        <v>509</v>
+        <v>462</v>
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B128" s="3"/>
       <c r="C128" s="3" t="s">
         <v>514</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>462</v>
+        <v>515</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>515</v>
-      </c>
-      <c r="F128" s="3"/>
+        <v>470</v>
+      </c>
+      <c r="F128" s="3" t="s">
+        <v>516</v>
+      </c>
       <c r="G128" s="3" t="s">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="H128" s="3" t="s">
-        <v>17</v>
+        <v>95</v>
       </c>
       <c r="I128" s="3"/>
       <c r="J128" s="3" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="K128" s="3" t="s">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="L128" s="3" t="s">
-        <v>464</v>
+        <v>517</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A129" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B129" s="3"/>
       <c r="C129" s="3" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>472</v>
+        <v>519</v>
       </c>
       <c r="F129" s="3" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="G129" s="3" t="s">
         <v>57</v>
@@ -7260,25 +7271,25 @@
         <v>57</v>
       </c>
       <c r="L129" s="3" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A130" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B130" s="3"/>
       <c r="C130" s="3" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="F130" s="3" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="G130" s="3" t="s">
         <v>57</v>
@@ -7294,22 +7305,22 @@
         <v>57</v>
       </c>
       <c r="L130" s="3" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A131" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B131" s="3"/>
       <c r="C131" s="3" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>526</v>
+        <v>470</v>
       </c>
       <c r="F131" s="3" t="s">
         <v>527</v>
@@ -7328,25 +7339,25 @@
         <v>57</v>
       </c>
       <c r="L131" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B132" s="3"/>
       <c r="C132" s="3" t="s">
         <v>528</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>472</v>
+        <v>529</v>
       </c>
       <c r="F132" s="3" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="G132" s="3" t="s">
         <v>57</v>
@@ -7362,31 +7373,31 @@
         <v>57</v>
       </c>
       <c r="L132" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A133" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B133" s="3"/>
       <c r="C133" s="3" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>525</v>
+        <v>532</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="F133" s="3" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="G133" s="3" t="s">
         <v>57</v>
       </c>
       <c r="H133" s="3" t="s">
-        <v>95</v>
+        <v>58</v>
       </c>
       <c r="I133" s="3"/>
       <c r="J133" s="3" t="s">
@@ -7396,335 +7407,333 @@
         <v>57</v>
       </c>
       <c r="L133" s="3" t="s">
-        <v>519</v>
+        <v>535</v>
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A134" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B134" s="3"/>
       <c r="C134" s="3" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="F134" s="3" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="G134" s="3" t="s">
-        <v>57</v>
+        <v>501</v>
       </c>
       <c r="H134" s="3" t="s">
-        <v>58</v>
+        <v>450</v>
       </c>
       <c r="I134" s="3"/>
       <c r="J134" s="3" t="s">
-        <v>59</v>
+        <v>540</v>
       </c>
       <c r="K134" s="3" t="s">
-        <v>57</v>
+        <v>501</v>
       </c>
       <c r="L134" s="3" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B135" s="3"/>
       <c r="C135" s="3" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="F135" s="3" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="G135" s="3" t="s">
-        <v>503</v>
+        <v>546</v>
       </c>
       <c r="H135" s="3" t="s">
-        <v>452</v>
+        <v>547</v>
       </c>
       <c r="I135" s="3"/>
       <c r="J135" s="3" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="K135" s="3" t="s">
-        <v>503</v>
+        <v>546</v>
       </c>
       <c r="L135" s="3" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A136" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B136" s="3"/>
       <c r="C136" s="3" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="F136" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="G136" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="H136" s="3" t="s">
         <v>547</v>
-      </c>
-      <c r="G136" s="3" t="s">
-        <v>548</v>
-      </c>
-      <c r="H136" s="3" t="s">
-        <v>549</v>
       </c>
       <c r="I136" s="3"/>
       <c r="J136" s="3" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="K136" s="3" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="L136" s="3" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B137" s="3"/>
       <c r="C137" s="3" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>545</v>
+        <v>556</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>553</v>
+        <v>544</v>
       </c>
       <c r="F137" s="3" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="G137" s="3" t="s">
-        <v>555</v>
+        <v>546</v>
       </c>
       <c r="H137" s="3" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="I137" s="3"/>
       <c r="J137" s="3" t="s">
-        <v>556</v>
+        <v>548</v>
       </c>
       <c r="K137" s="3" t="s">
-        <v>555</v>
+        <v>546</v>
       </c>
       <c r="L137" s="3" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A138" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B138" s="3"/>
       <c r="C138" s="3" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="F138" s="3" t="s">
         <v>559</v>
       </c>
       <c r="G138" s="3" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="H138" s="3" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="I138" s="3"/>
       <c r="J138" s="3" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="K138" s="3" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="L138" s="3" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A139" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B139" s="3"/>
       <c r="C139" s="3" t="s">
         <v>560</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="F139" s="3" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="G139" s="3" t="s">
-        <v>555</v>
+        <v>436</v>
       </c>
       <c r="H139" s="3" t="s">
-        <v>549</v>
+        <v>437</v>
       </c>
       <c r="I139" s="3"/>
       <c r="J139" s="3" t="s">
-        <v>556</v>
+        <v>563</v>
       </c>
       <c r="K139" s="3" t="s">
-        <v>555</v>
+        <v>436</v>
       </c>
       <c r="L139" s="3" t="s">
-        <v>551</v>
+        <v>564</v>
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A140" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B140" s="3"/>
       <c r="C140" s="3" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>553</v>
+        <v>509</v>
       </c>
       <c r="F140" s="3" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="G140" s="3" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="H140" s="3" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="I140" s="3"/>
       <c r="J140" s="3" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="K140" s="3" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="L140" s="3" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A141" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B141" s="3"/>
       <c r="C141" s="3" t="s">
         <v>567</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>511</v>
+        <v>569</v>
       </c>
       <c r="F141" s="3" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="G141" s="3" t="s">
-        <v>438</v>
+        <v>332</v>
       </c>
       <c r="H141" s="3" t="s">
-        <v>439</v>
+        <v>135</v>
       </c>
       <c r="I141" s="3"/>
       <c r="J141" s="3" t="s">
-        <v>565</v>
+        <v>30</v>
       </c>
       <c r="K141" s="3" t="s">
-        <v>438</v>
+        <v>332</v>
       </c>
       <c r="L141" s="3" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A142" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B142" s="3"/>
       <c r="C142" s="3" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>571</v>
-      </c>
-      <c r="F142" s="3" t="s">
-        <v>572</v>
-      </c>
+        <v>574</v>
+      </c>
+      <c r="F142" s="3"/>
       <c r="G142" s="3" t="s">
-        <v>332</v>
+        <v>101</v>
       </c>
       <c r="H142" s="3" t="s">
-        <v>135</v>
+        <v>575</v>
       </c>
       <c r="I142" s="3"/>
       <c r="J142" s="3" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="K142" s="3" t="s">
-        <v>332</v>
+        <v>101</v>
       </c>
       <c r="L142" s="3" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A143" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B143" s="3"/>
       <c r="C143" s="3" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="F143" s="3"/>
       <c r="G143" s="3" t="s">
         <v>101</v>
       </c>
       <c r="H143" s="3" t="s">
-        <v>577</v>
+        <v>102</v>
       </c>
       <c r="I143" s="3"/>
       <c r="J143" s="3" t="s">
@@ -7734,22 +7743,22 @@
         <v>101</v>
       </c>
       <c r="L143" s="3" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A144" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B144" s="3"/>
       <c r="C144" s="3" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>581</v>
+        <v>574</v>
       </c>
       <c r="F144" s="3"/>
       <c r="G144" s="3" t="s">
@@ -7766,259 +7775,261 @@
         <v>101</v>
       </c>
       <c r="L144" s="3" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A145" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B145" s="3"/>
       <c r="C145" s="3" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>584</v>
+        <v>460</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>576</v>
+        <v>585</v>
       </c>
       <c r="F145" s="3"/>
       <c r="G145" s="3" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
       <c r="H145" s="3" t="s">
-        <v>102</v>
+        <v>17</v>
       </c>
       <c r="I145" s="3"/>
       <c r="J145" s="3" t="s">
-        <v>103</v>
+        <v>18</v>
       </c>
       <c r="K145" s="3" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
       <c r="L145" s="3" t="s">
-        <v>585</v>
+        <v>462</v>
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A146" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B146" s="3"/>
       <c r="C146" s="3" t="s">
         <v>586</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>462</v>
+        <v>587</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>587</v>
-      </c>
-      <c r="F146" s="3"/>
+        <v>474</v>
+      </c>
+      <c r="F146" s="3" t="s">
+        <v>588</v>
+      </c>
       <c r="G146" s="3" t="s">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="H146" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="I146" s="3"/>
       <c r="J146" s="3" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="K146" s="3" t="s">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="L146" s="3" t="s">
-        <v>464</v>
+        <v>589</v>
       </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A147" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B147" s="3"/>
       <c r="C147" s="3" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E147" s="3" t="s">
-        <v>476</v>
+        <v>591</v>
       </c>
       <c r="F147" s="3" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="G147" s="3" t="s">
-        <v>57</v>
+        <v>593</v>
       </c>
       <c r="H147" s="3" t="s">
-        <v>58</v>
+        <v>593</v>
       </c>
       <c r="I147" s="3"/>
       <c r="J147" s="3" t="s">
-        <v>59</v>
+        <v>478</v>
       </c>
       <c r="K147" s="3" t="s">
-        <v>57</v>
+        <v>593</v>
       </c>
       <c r="L147" s="3" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A148" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B148" s="3"/>
       <c r="C148" s="3" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E148" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="F148" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="G148" s="3" t="s">
         <v>593</v>
       </c>
-      <c r="F148" s="3" t="s">
-        <v>594</v>
-      </c>
-      <c r="G148" s="3" t="s">
-        <v>595</v>
-      </c>
       <c r="H148" s="3" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="I148" s="3"/>
       <c r="J148" s="3" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="K148" s="3" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="L148" s="3" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A149" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B149" s="3"/>
       <c r="C149" s="3" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>589</v>
+        <v>599</v>
       </c>
       <c r="E149" s="3" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="F149" s="3" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="G149" s="3" t="s">
-        <v>595</v>
+        <v>28</v>
       </c>
       <c r="H149" s="3" t="s">
-        <v>595</v>
+        <v>332</v>
       </c>
       <c r="I149" s="3"/>
       <c r="J149" s="3" t="s">
-        <v>480</v>
+        <v>30</v>
       </c>
       <c r="K149" s="3" t="s">
-        <v>595</v>
+        <v>28</v>
       </c>
       <c r="L149" s="3" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A150" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B150" s="3"/>
       <c r="C150" s="3" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="E150" s="3" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="F150" s="3" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="G150" s="3" t="s">
-        <v>28</v>
+        <v>450</v>
       </c>
       <c r="H150" s="3" t="s">
-        <v>332</v>
+        <v>135</v>
       </c>
       <c r="I150" s="3"/>
       <c r="J150" s="3" t="s">
-        <v>30</v>
+        <v>607</v>
       </c>
       <c r="K150" s="3" t="s">
-        <v>28</v>
+        <v>450</v>
       </c>
       <c r="L150" s="3" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A151" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B151" s="3"/>
       <c r="C151" s="3" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="E151" s="3" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="F151" s="3" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="G151" s="3" t="s">
-        <v>452</v>
+        <v>28</v>
       </c>
       <c r="H151" s="3" t="s">
-        <v>135</v>
+        <v>332</v>
       </c>
       <c r="I151" s="3"/>
       <c r="J151" s="3" t="s">
-        <v>609</v>
+        <v>30</v>
       </c>
       <c r="K151" s="3" t="s">
-        <v>452</v>
+        <v>28</v>
       </c>
       <c r="L151" s="3" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A152" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B152" s="3"/>
       <c r="C152" s="3" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="F152" s="3" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="G152" s="3" t="s">
         <v>28</v>
@@ -8034,131 +8045,131 @@
         <v>28</v>
       </c>
       <c r="L152" s="3" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A153" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B153" s="3"/>
       <c r="C153" s="3" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="D153" s="3" t="s">
-        <v>612</v>
+        <v>619</v>
       </c>
       <c r="E153" s="3" t="s">
-        <v>617</v>
+        <v>524</v>
       </c>
       <c r="F153" s="3" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="G153" s="3" t="s">
-        <v>28</v>
+        <v>621</v>
       </c>
       <c r="H153" s="3" t="s">
-        <v>332</v>
+        <v>622</v>
       </c>
       <c r="I153" s="3"/>
       <c r="J153" s="3" t="s">
-        <v>30</v>
+        <v>623</v>
       </c>
       <c r="K153" s="3" t="s">
-        <v>28</v>
+        <v>621</v>
       </c>
       <c r="L153" s="3" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A154" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B154" s="3"/>
       <c r="C154" s="3" t="s">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="E154" s="3" t="s">
-        <v>526</v>
-      </c>
-      <c r="F154" s="3" t="s">
-        <v>622</v>
-      </c>
+        <v>627</v>
+      </c>
+      <c r="F154" s="3"/>
       <c r="G154" s="3" t="s">
-        <v>623</v>
+        <v>28</v>
       </c>
       <c r="H154" s="3" t="s">
-        <v>624</v>
+        <v>332</v>
       </c>
       <c r="I154" s="3"/>
       <c r="J154" s="3" t="s">
-        <v>625</v>
+        <v>30</v>
       </c>
       <c r="K154" s="3" t="s">
-        <v>623</v>
+        <v>28</v>
       </c>
       <c r="L154" s="3" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A155" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B155" s="3"/>
       <c r="C155" s="3" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>628</v>
+        <v>619</v>
       </c>
       <c r="E155" s="3" t="s">
-        <v>629</v>
-      </c>
-      <c r="F155" s="3"/>
+        <v>470</v>
+      </c>
+      <c r="F155" s="3" t="s">
+        <v>630</v>
+      </c>
       <c r="G155" s="3" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H155" s="3" t="s">
-        <v>332</v>
+        <v>451</v>
       </c>
       <c r="I155" s="3"/>
       <c r="J155" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="K155" s="3" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="L155" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A156" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B156" s="3"/>
       <c r="C156" s="3" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="E156" s="3" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="F156" s="3" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="G156" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H156" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I156" s="3"/>
       <c r="J156" s="3" t="s">
@@ -8173,617 +8184,617 @@
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A157" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B157" s="3"/>
       <c r="C157" s="3" t="s">
         <v>634</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>621</v>
+        <v>460</v>
       </c>
       <c r="E157" s="3" t="s">
-        <v>472</v>
-      </c>
-      <c r="F157" s="3" t="s">
-        <v>632</v>
-      </c>
+        <v>635</v>
+      </c>
+      <c r="F157" s="3"/>
       <c r="G157" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H157" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="H157" s="3" t="s">
-        <v>453</v>
       </c>
       <c r="I157" s="3"/>
       <c r="J157" s="3" t="s">
         <v>18</v>
       </c>
       <c r="K157" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L157" s="3" t="s">
-        <v>635</v>
+        <v>462</v>
       </c>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A158" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B158" s="3"/>
       <c r="C158" s="3" t="s">
         <v>636</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>462</v>
+        <v>637</v>
       </c>
       <c r="E158" s="3" t="s">
-        <v>637</v>
-      </c>
-      <c r="F158" s="3"/>
+        <v>615</v>
+      </c>
+      <c r="F158" s="3" t="s">
+        <v>638</v>
+      </c>
       <c r="G158" s="3" t="s">
-        <v>16</v>
+        <v>639</v>
       </c>
       <c r="H158" s="3" t="s">
-        <v>17</v>
+        <v>135</v>
       </c>
       <c r="I158" s="3"/>
       <c r="J158" s="3" t="s">
-        <v>18</v>
+        <v>203</v>
       </c>
       <c r="K158" s="3" t="s">
-        <v>16</v>
+        <v>639</v>
       </c>
       <c r="L158" s="3" t="s">
-        <v>464</v>
+        <v>640</v>
       </c>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A159" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B159" s="3"/>
       <c r="C159" s="3" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="E159" s="3" t="s">
-        <v>617</v>
-      </c>
-      <c r="F159" s="3" t="s">
-        <v>640</v>
-      </c>
+        <v>643</v>
+      </c>
+      <c r="F159" s="3"/>
       <c r="G159" s="3" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="H159" s="3" t="s">
         <v>135</v>
       </c>
       <c r="I159" s="3"/>
       <c r="J159" s="3" t="s">
-        <v>203</v>
+        <v>645</v>
       </c>
       <c r="K159" s="3" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="L159" s="3" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A160" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B160" s="3"/>
       <c r="C160" s="3" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="F160" s="3"/>
       <c r="G160" s="3" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="H160" s="3" t="s">
         <v>135</v>
       </c>
       <c r="I160" s="3"/>
       <c r="J160" s="3" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="K160" s="3" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="L160" s="3" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A161" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B161" s="3"/>
       <c r="C161" s="3" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="D161" s="3" t="s">
-        <v>644</v>
+        <v>653</v>
       </c>
       <c r="E161" s="3" t="s">
-        <v>650</v>
-      </c>
-      <c r="F161" s="3"/>
+        <v>115</v>
+      </c>
+      <c r="F161" s="3" t="s">
+        <v>654</v>
+      </c>
       <c r="G161" s="3" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="H161" s="3" t="s">
-        <v>135</v>
+        <v>656</v>
       </c>
       <c r="I161" s="3"/>
       <c r="J161" s="3" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="K161" s="3" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="L161" s="3" t="s">
-        <v>653</v>
+        <v>658</v>
       </c>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A162" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B162" s="3"/>
       <c r="C162" s="3" t="s">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="E162" s="3" t="s">
         <v>115</v>
       </c>
       <c r="F162" s="3" t="s">
+        <v>661</v>
+      </c>
+      <c r="G162" s="3" t="s">
+        <v>655</v>
+      </c>
+      <c r="H162" s="3" t="s">
         <v>656</v>
-      </c>
-      <c r="G162" s="3" t="s">
-        <v>657</v>
-      </c>
-      <c r="H162" s="3" t="s">
-        <v>658</v>
       </c>
       <c r="I162" s="3"/>
       <c r="J162" s="3" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="K162" s="3" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="L162" s="3" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A163" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B163" s="3"/>
       <c r="C163" s="3" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="D163" s="3" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>115</v>
+        <v>665</v>
       </c>
       <c r="F163" s="3" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="G163" s="3" t="s">
-        <v>657</v>
+        <v>667</v>
       </c>
       <c r="H163" s="3" t="s">
-        <v>658</v>
+        <v>668</v>
       </c>
       <c r="I163" s="3"/>
       <c r="J163" s="3" t="s">
-        <v>659</v>
+        <v>669</v>
       </c>
       <c r="K163" s="3" t="s">
-        <v>657</v>
+        <v>667</v>
       </c>
       <c r="L163" s="3" t="s">
-        <v>664</v>
+        <v>670</v>
       </c>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A164" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B164" s="3"/>
       <c r="C164" s="3" t="s">
+        <v>671</v>
+      </c>
+      <c r="D164" s="3" t="s">
+        <v>672</v>
+      </c>
+      <c r="E164" s="3" t="s">
         <v>665</v>
       </c>
-      <c r="D164" s="3" t="s">
-        <v>666</v>
-      </c>
-      <c r="E164" s="3" t="s">
+      <c r="F164" s="3" t="s">
+        <v>673</v>
+      </c>
+      <c r="G164" s="3" t="s">
         <v>667</v>
       </c>
-      <c r="F164" s="3" t="s">
+      <c r="H164" s="3" t="s">
         <v>668</v>
-      </c>
-      <c r="G164" s="3" t="s">
-        <v>669</v>
-      </c>
-      <c r="H164" s="3" t="s">
-        <v>670</v>
       </c>
       <c r="I164" s="3"/>
       <c r="J164" s="3" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="K164" s="3" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="L164" s="3" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A165" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B165" s="3"/>
       <c r="C165" s="3" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="D165" s="3" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>667</v>
+        <v>470</v>
       </c>
       <c r="F165" s="3" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="G165" s="3" t="s">
-        <v>669</v>
+        <v>621</v>
       </c>
       <c r="H165" s="3" t="s">
-        <v>670</v>
+        <v>622</v>
       </c>
       <c r="I165" s="3"/>
       <c r="J165" s="3" t="s">
-        <v>671</v>
+        <v>623</v>
       </c>
       <c r="K165" s="3" t="s">
-        <v>669</v>
+        <v>621</v>
       </c>
       <c r="L165" s="3" t="s">
-        <v>672</v>
+        <v>677</v>
       </c>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A166" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B166" s="3"/>
       <c r="C166" s="3" t="s">
+        <v>678</v>
+      </c>
+      <c r="D166" s="3" t="s">
+        <v>675</v>
+      </c>
+      <c r="E166" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="F166" s="3" t="s">
         <v>676</v>
       </c>
-      <c r="D166" s="3" t="s">
-        <v>677</v>
-      </c>
-      <c r="E166" s="3" t="s">
-        <v>472</v>
-      </c>
-      <c r="F166" s="3" t="s">
-        <v>678</v>
-      </c>
       <c r="G166" s="3" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="H166" s="3" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="I166" s="3"/>
       <c r="J166" s="3" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="K166" s="3" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="L166" s="3" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A167" s="3" t="s">
-        <v>460</v>
+        <v>679</v>
       </c>
       <c r="B167" s="3"/>
       <c r="C167" s="3" t="s">
         <v>680</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="E167" s="3" t="s">
-        <v>472</v>
-      </c>
-      <c r="F167" s="3" t="s">
-        <v>678</v>
-      </c>
+        <v>682</v>
+      </c>
+      <c r="F167" s="3"/>
       <c r="G167" s="3" t="s">
-        <v>623</v>
+        <v>683</v>
       </c>
       <c r="H167" s="3" t="s">
-        <v>624</v>
-      </c>
-      <c r="I167" s="3"/>
+        <v>683</v>
+      </c>
+      <c r="I167" s="3" t="s">
+        <v>684</v>
+      </c>
       <c r="J167" s="3" t="s">
-        <v>625</v>
+        <v>685</v>
       </c>
       <c r="K167" s="3" t="s">
-        <v>623</v>
+        <v>683</v>
       </c>
       <c r="L167" s="3" t="s">
-        <v>679</v>
+        <v>686</v>
       </c>
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A168" s="3" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B168" s="3"/>
       <c r="C168" s="3" t="s">
+        <v>680</v>
+      </c>
+      <c r="D168" s="3" t="s">
+        <v>687</v>
+      </c>
+      <c r="E168" s="3" t="s">
         <v>682</v>
-      </c>
-      <c r="D168" s="3" t="s">
-        <v>683</v>
-      </c>
-      <c r="E168" s="3" t="s">
-        <v>684</v>
       </c>
       <c r="F168" s="3"/>
       <c r="G168" s="3" t="s">
+        <v>683</v>
+      </c>
+      <c r="H168" s="3" t="s">
+        <v>683</v>
+      </c>
+      <c r="I168" s="3" t="s">
+        <v>684</v>
+      </c>
+      <c r="J168" s="3" t="s">
         <v>685</v>
       </c>
-      <c r="H168" s="3" t="s">
-        <v>685</v>
-      </c>
-      <c r="I168" s="3" t="s">
+      <c r="K168" s="3" t="s">
+        <v>683</v>
+      </c>
+      <c r="L168" s="3" t="s">
         <v>686</v>
-      </c>
-      <c r="J168" s="3" t="s">
-        <v>687</v>
-      </c>
-      <c r="K168" s="3" t="s">
-        <v>685</v>
-      </c>
-      <c r="L168" s="3" t="s">
-        <v>688</v>
       </c>
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A169" s="3" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B169" s="3"/>
       <c r="C169" s="3" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="D169" s="3" t="s">
         <v>689</v>
       </c>
       <c r="E169" s="3" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="F169" s="3"/>
       <c r="G169" s="3" t="s">
+        <v>683</v>
+      </c>
+      <c r="H169" s="3" t="s">
+        <v>683</v>
+      </c>
+      <c r="I169" s="3" t="s">
+        <v>690</v>
+      </c>
+      <c r="J169" s="3" t="s">
         <v>685</v>
       </c>
-      <c r="H169" s="3" t="s">
-        <v>685</v>
-      </c>
-      <c r="I169" s="3" t="s">
-        <v>686</v>
-      </c>
-      <c r="J169" s="3" t="s">
-        <v>687</v>
-      </c>
       <c r="K169" s="3" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="L169" s="3" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A170" s="3" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B170" s="3"/>
       <c r="C170" s="3" t="s">
-        <v>690</v>
+        <v>680</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="E170" s="3" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="F170" s="3"/>
       <c r="G170" s="3" t="s">
+        <v>683</v>
+      </c>
+      <c r="H170" s="3" t="s">
+        <v>693</v>
+      </c>
+      <c r="I170" s="3" t="s">
+        <v>684</v>
+      </c>
+      <c r="J170" s="3" t="s">
         <v>685</v>
       </c>
-      <c r="H170" s="3" t="s">
-        <v>685</v>
-      </c>
-      <c r="I170" s="3" t="s">
-        <v>692</v>
-      </c>
-      <c r="J170" s="3" t="s">
-        <v>687</v>
-      </c>
       <c r="K170" s="3" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="L170" s="3" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A171" s="3" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B171" s="3"/>
       <c r="C171" s="3" t="s">
+        <v>688</v>
+      </c>
+      <c r="D171" s="3" t="s">
+        <v>695</v>
+      </c>
+      <c r="E171" s="3" t="s">
         <v>682</v>
-      </c>
-      <c r="D171" s="3" t="s">
-        <v>694</v>
-      </c>
-      <c r="E171" s="3" t="s">
-        <v>684</v>
       </c>
       <c r="F171" s="3"/>
       <c r="G171" s="3" t="s">
+        <v>683</v>
+      </c>
+      <c r="H171" s="3" t="s">
+        <v>683</v>
+      </c>
+      <c r="I171" s="3" t="s">
+        <v>690</v>
+      </c>
+      <c r="J171" s="3" t="s">
         <v>685</v>
       </c>
-      <c r="H171" s="3" t="s">
-        <v>695</v>
-      </c>
-      <c r="I171" s="3" t="s">
-        <v>686</v>
-      </c>
-      <c r="J171" s="3" t="s">
-        <v>687</v>
-      </c>
       <c r="K171" s="3" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="L171" s="3" t="s">
-        <v>696</v>
+        <v>691</v>
       </c>
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A172" s="3" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B172" s="3"/>
       <c r="C172" s="3" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>697</v>
+        <v>871</v>
       </c>
       <c r="E172" s="3" t="s">
-        <v>684</v>
+        <v>872</v>
       </c>
       <c r="F172" s="3"/>
       <c r="G172" s="3" t="s">
+        <v>697</v>
+      </c>
+      <c r="H172" s="3" t="s">
+        <v>683</v>
+      </c>
+      <c r="I172" s="3" t="s">
+        <v>690</v>
+      </c>
+      <c r="J172" s="3" t="s">
         <v>685</v>
       </c>
-      <c r="H172" s="3" t="s">
-        <v>685</v>
-      </c>
-      <c r="I172" s="3" t="s">
-        <v>692</v>
-      </c>
-      <c r="J172" s="3" t="s">
-        <v>687</v>
-      </c>
       <c r="K172" s="3" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="L172" s="3" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A173" s="3" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B173" s="3"/>
       <c r="C173" s="3" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="D173" s="3" t="s">
-        <v>873</v>
+        <v>696</v>
       </c>
       <c r="E173" s="3" t="s">
-        <v>874</v>
+        <v>682</v>
       </c>
       <c r="F173" s="3"/>
       <c r="G173" s="3" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="H173" s="3" t="s">
+        <v>697</v>
+      </c>
+      <c r="I173" s="3" t="s">
+        <v>690</v>
+      </c>
+      <c r="J173" s="3" t="s">
         <v>685</v>
       </c>
-      <c r="I173" s="3" t="s">
-        <v>692</v>
-      </c>
-      <c r="J173" s="3" t="s">
-        <v>687</v>
-      </c>
       <c r="K173" s="3" t="s">
-        <v>685</v>
+        <v>697</v>
       </c>
       <c r="L173" s="3" t="s">
-        <v>693</v>
+        <v>698</v>
       </c>
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A174" s="3" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B174" s="3"/>
       <c r="C174" s="3" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="E174" s="3" t="s">
-        <v>684</v>
+        <v>700</v>
       </c>
       <c r="F174" s="3"/>
       <c r="G174" s="3" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="H174" s="3" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="I174" s="3" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="J174" s="3" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="K174" s="3" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="L174" s="3" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A175" s="3" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B175" s="3"/>
       <c r="C175" s="3" t="s">
-        <v>690</v>
+        <v>680</v>
       </c>
       <c r="D175" s="3" t="s">
         <v>701</v>
@@ -8793,47 +8804,47 @@
       </c>
       <c r="F175" s="3"/>
       <c r="G175" s="3" t="s">
-        <v>699</v>
+        <v>101</v>
       </c>
       <c r="H175" s="3" t="s">
-        <v>699</v>
+        <v>575</v>
       </c>
       <c r="I175" s="3" t="s">
-        <v>692</v>
+        <v>684</v>
       </c>
       <c r="J175" s="3" t="s">
-        <v>687</v>
+        <v>103</v>
       </c>
       <c r="K175" s="3" t="s">
-        <v>699</v>
+        <v>101</v>
       </c>
       <c r="L175" s="3" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A176" s="3" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B176" s="3"/>
       <c r="C176" s="3" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="E176" s="3" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="F176" s="3"/>
       <c r="G176" s="3" t="s">
         <v>101</v>
       </c>
       <c r="H176" s="3" t="s">
-        <v>577</v>
+        <v>102</v>
       </c>
       <c r="I176" s="3" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="J176" s="3" t="s">
         <v>103</v>
@@ -8842,32 +8853,32 @@
         <v>101</v>
       </c>
       <c r="L176" s="3" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A177" s="3" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B177" s="3"/>
       <c r="C177" s="3" t="s">
-        <v>690</v>
+        <v>680</v>
       </c>
       <c r="D177" s="3" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="E177" s="3" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="F177" s="3"/>
       <c r="G177" s="3" t="s">
         <v>101</v>
       </c>
       <c r="H177" s="3" t="s">
-        <v>102</v>
+        <v>575</v>
       </c>
       <c r="I177" s="3" t="s">
-        <v>692</v>
+        <v>684</v>
       </c>
       <c r="J177" s="3" t="s">
         <v>103</v>
@@ -8876,38 +8887,38 @@
         <v>101</v>
       </c>
       <c r="L177" s="3" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
     </row>
     <row r="178" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A178" s="3" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B178" s="3"/>
       <c r="C178" s="3" t="s">
+        <v>680</v>
+      </c>
+      <c r="D178" s="3" t="s">
+        <v>710</v>
+      </c>
+      <c r="E178" s="3" t="s">
         <v>682</v>
-      </c>
-      <c r="D178" s="3" t="s">
-        <v>709</v>
-      </c>
-      <c r="E178" s="3" t="s">
-        <v>710</v>
       </c>
       <c r="F178" s="3"/>
       <c r="G178" s="3" t="s">
-        <v>101</v>
+        <v>683</v>
       </c>
       <c r="H178" s="3" t="s">
-        <v>577</v>
+        <v>683</v>
       </c>
       <c r="I178" s="3" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="J178" s="3" t="s">
-        <v>103</v>
+        <v>685</v>
       </c>
       <c r="K178" s="3" t="s">
-        <v>101</v>
+        <v>683</v>
       </c>
       <c r="L178" s="3" t="s">
         <v>711</v>
@@ -8915,326 +8926,326 @@
     </row>
     <row r="179" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A179" s="3" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B179" s="3"/>
       <c r="C179" s="3" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="D179" s="3" t="s">
         <v>712</v>
       </c>
       <c r="E179" s="3" t="s">
-        <v>684</v>
+        <v>713</v>
       </c>
       <c r="F179" s="3"/>
       <c r="G179" s="3" t="s">
-        <v>685</v>
+        <v>129</v>
       </c>
       <c r="H179" s="3" t="s">
-        <v>685</v>
+        <v>714</v>
       </c>
       <c r="I179" s="3" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="J179" s="3" t="s">
-        <v>687</v>
+        <v>131</v>
       </c>
       <c r="K179" s="3" t="s">
-        <v>685</v>
+        <v>129</v>
       </c>
       <c r="L179" s="3" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A180" s="3" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B180" s="3"/>
       <c r="C180" s="3" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="E180" s="3" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="F180" s="3"/>
       <c r="G180" s="3" t="s">
-        <v>129</v>
+        <v>718</v>
       </c>
       <c r="H180" s="3" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="I180" s="3" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="J180" s="3" t="s">
-        <v>131</v>
+        <v>720</v>
       </c>
       <c r="K180" s="3" t="s">
-        <v>129</v>
+        <v>718</v>
       </c>
       <c r="L180" s="3" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A181" s="3" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B181" s="3"/>
       <c r="C181" s="3" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="E181" s="3" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="F181" s="3"/>
       <c r="G181" s="3" t="s">
+        <v>718</v>
+      </c>
+      <c r="H181" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="I181" s="3" t="s">
+        <v>684</v>
+      </c>
+      <c r="J181" s="3" t="s">
         <v>720</v>
       </c>
-      <c r="H181" s="3" t="s">
+      <c r="K181" s="3" t="s">
+        <v>718</v>
+      </c>
+      <c r="L181" s="3" t="s">
         <v>721</v>
-      </c>
-      <c r="I181" s="3" t="s">
-        <v>686</v>
-      </c>
-      <c r="J181" s="3" t="s">
-        <v>722</v>
-      </c>
-      <c r="K181" s="3" t="s">
-        <v>720</v>
-      </c>
-      <c r="L181" s="3" t="s">
-        <v>723</v>
       </c>
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A182" s="3" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B182" s="3"/>
       <c r="C182" s="3" t="s">
+        <v>680</v>
+      </c>
+      <c r="D182" s="3" t="s">
+        <v>723</v>
+      </c>
+      <c r="E182" s="3" t="s">
         <v>682</v>
-      </c>
-      <c r="D182" s="3" t="s">
-        <v>724</v>
-      </c>
-      <c r="E182" s="3" t="s">
-        <v>719</v>
       </c>
       <c r="F182" s="3"/>
       <c r="G182" s="3" t="s">
-        <v>720</v>
+        <v>683</v>
       </c>
       <c r="H182" s="3" t="s">
-        <v>721</v>
+        <v>683</v>
       </c>
       <c r="I182" s="3" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="J182" s="3" t="s">
-        <v>722</v>
+        <v>685</v>
       </c>
       <c r="K182" s="3" t="s">
-        <v>720</v>
+        <v>683</v>
       </c>
       <c r="L182" s="3" t="s">
-        <v>723</v>
+        <v>711</v>
       </c>
     </row>
     <row r="183" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A183" s="3" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B183" s="3"/>
       <c r="C183" s="3" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="D183" s="3" t="s">
+        <v>724</v>
+      </c>
+      <c r="E183" s="3" t="s">
         <v>725</v>
-      </c>
-      <c r="E183" s="3" t="s">
-        <v>684</v>
       </c>
       <c r="F183" s="3"/>
       <c r="G183" s="3" t="s">
-        <v>685</v>
+        <v>726</v>
       </c>
       <c r="H183" s="3" t="s">
-        <v>685</v>
+        <v>727</v>
       </c>
       <c r="I183" s="3" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="J183" s="3" t="s">
-        <v>687</v>
+        <v>728</v>
       </c>
       <c r="K183" s="3" t="s">
-        <v>685</v>
+        <v>726</v>
       </c>
       <c r="L183" s="3" t="s">
-        <v>713</v>
+        <v>729</v>
       </c>
     </row>
     <row r="184" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A184" s="3" t="s">
-        <v>681</v>
+        <v>730</v>
       </c>
       <c r="B184" s="3"/>
       <c r="C184" s="3" t="s">
-        <v>682</v>
+        <v>731</v>
       </c>
       <c r="D184" s="3" t="s">
-        <v>726</v>
+        <v>732</v>
       </c>
       <c r="E184" s="3" t="s">
-        <v>727</v>
-      </c>
-      <c r="F184" s="3"/>
+        <v>733</v>
+      </c>
+      <c r="F184" s="3" t="s">
+        <v>734</v>
+      </c>
       <c r="G184" s="3" t="s">
-        <v>728</v>
+        <v>735</v>
       </c>
       <c r="H184" s="3" t="s">
-        <v>729</v>
-      </c>
-      <c r="I184" s="3" t="s">
-        <v>686</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="I184" s="3"/>
       <c r="J184" s="3" t="s">
-        <v>730</v>
+        <v>736</v>
       </c>
       <c r="K184" s="3" t="s">
-        <v>728</v>
+        <v>735</v>
       </c>
       <c r="L184" s="3" t="s">
-        <v>731</v>
+        <v>737</v>
       </c>
     </row>
     <row r="185" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A185" s="3" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="B185" s="3"/>
       <c r="C185" s="3" t="s">
-        <v>733</v>
+        <v>738</v>
       </c>
       <c r="D185" s="3" t="s">
-        <v>734</v>
+        <v>739</v>
       </c>
       <c r="E185" s="3" t="s">
-        <v>735</v>
+        <v>740</v>
       </c>
       <c r="F185" s="3" t="s">
-        <v>736</v>
+        <v>741</v>
       </c>
       <c r="G185" s="3" t="s">
-        <v>737</v>
+        <v>121</v>
       </c>
       <c r="H185" s="3" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="I185" s="3"/>
       <c r="J185" s="3" t="s">
-        <v>738</v>
+        <v>82</v>
       </c>
       <c r="K185" s="3" t="s">
-        <v>737</v>
+        <v>121</v>
       </c>
       <c r="L185" s="3" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
     </row>
     <row r="186" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A186" s="3" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="B186" s="3"/>
       <c r="C186" s="3" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="D186" s="3" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="E186" s="3" t="s">
-        <v>742</v>
+        <v>319</v>
       </c>
       <c r="F186" s="3" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="G186" s="3" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="H186" s="3" t="s">
-        <v>121</v>
+        <v>714</v>
       </c>
       <c r="I186" s="3"/>
       <c r="J186" s="3" t="s">
-        <v>82</v>
+        <v>131</v>
       </c>
       <c r="K186" s="3" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="L186" s="3" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
     </row>
     <row r="187" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A187" s="3" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="B187" s="3"/>
       <c r="C187" s="3" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="D187" s="3" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="E187" s="3" t="s">
-        <v>319</v>
+        <v>749</v>
       </c>
       <c r="F187" s="3" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="G187" s="3" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="H187" s="3" t="s">
-        <v>716</v>
+        <v>135</v>
       </c>
       <c r="I187" s="3"/>
       <c r="J187" s="3" t="s">
-        <v>131</v>
+        <v>82</v>
       </c>
       <c r="K187" s="3" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="L187" s="3" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
     </row>
     <row r="188" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A188" s="3" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="B188" s="3"/>
       <c r="C188" s="3" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="D188" s="3" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="E188" s="3" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="F188" s="3" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="G188" s="3" t="s">
         <v>135</v>
@@ -9250,25 +9261,25 @@
         <v>135</v>
       </c>
       <c r="L188" s="3" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
     </row>
     <row r="189" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A189" s="3" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="B189" s="3"/>
       <c r="C189" s="3" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="D189" s="3" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="E189" s="3" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="F189" s="3" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="G189" s="3" t="s">
         <v>135</v>
@@ -9284,125 +9295,125 @@
         <v>135</v>
       </c>
       <c r="L189" s="3" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
     </row>
     <row r="190" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A190" s="3" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="B190" s="3"/>
       <c r="C190" s="3" t="s">
         <v>758</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>755</v>
-      </c>
-      <c r="E190" s="3" t="s">
         <v>759</v>
       </c>
+      <c r="E190" s="3"/>
       <c r="F190" s="3" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G190" s="3" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="H190" s="3" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="I190" s="3"/>
       <c r="J190" s="3" t="s">
         <v>82</v>
       </c>
       <c r="K190" s="3" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="L190" s="3" t="s">
-        <v>757</v>
+        <v>761</v>
       </c>
     </row>
     <row r="191" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A191" s="3" t="s">
-        <v>732</v>
+        <v>762</v>
       </c>
       <c r="B191" s="3"/>
       <c r="C191" s="3" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>761</v>
-      </c>
-      <c r="E191" s="3"/>
+        <v>764</v>
+      </c>
+      <c r="E191" s="3" t="s">
+        <v>765</v>
+      </c>
       <c r="F191" s="3" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="G191" s="3" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="H191" s="3" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="I191" s="3"/>
       <c r="J191" s="3" t="s">
-        <v>82</v>
+        <v>131</v>
       </c>
       <c r="K191" s="3" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="L191" s="3" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A192" s="3" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="B192" s="3"/>
       <c r="C192" s="3" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="D192" s="3" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="E192" s="3" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="F192" s="3" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="G192" s="3" t="s">
-        <v>129</v>
+        <v>17</v>
       </c>
       <c r="H192" s="3" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="I192" s="3"/>
       <c r="J192" s="3" t="s">
-        <v>131</v>
+        <v>18</v>
       </c>
       <c r="K192" s="3" t="s">
-        <v>129</v>
+        <v>17</v>
       </c>
       <c r="L192" s="3" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
     </row>
     <row r="193" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A193" s="3" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="B193" s="3"/>
       <c r="C193" s="3" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="D193" s="3" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="E193" s="3" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="F193" s="3" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="G193" s="3" t="s">
         <v>17</v>
@@ -9418,59 +9429,59 @@
         <v>17</v>
       </c>
       <c r="L193" s="3" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
     </row>
     <row r="194" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A194" s="3" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="B194" s="3"/>
       <c r="C194" s="3" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>775</v>
+        <v>867</v>
       </c>
       <c r="E194" s="3" t="s">
-        <v>776</v>
+        <v>868</v>
       </c>
       <c r="F194" s="3" t="s">
-        <v>777</v>
+        <v>869</v>
       </c>
       <c r="G194" s="3" t="s">
-        <v>17</v>
+        <v>129</v>
       </c>
       <c r="H194" s="3" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="I194" s="3"/>
       <c r="J194" s="3" t="s">
-        <v>18</v>
+        <v>131</v>
       </c>
       <c r="K194" s="3" t="s">
-        <v>17</v>
+        <v>129</v>
       </c>
       <c r="L194" s="3" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
     </row>
     <row r="195" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A195" s="3" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="B195" s="3"/>
       <c r="C195" s="3" t="s">
+        <v>780</v>
+      </c>
+      <c r="D195" s="3" t="s">
+        <v>777</v>
+      </c>
+      <c r="E195" s="3" t="s">
         <v>778</v>
       </c>
-      <c r="D195" s="3" t="s">
-        <v>869</v>
-      </c>
-      <c r="E195" s="3" t="s">
-        <v>870</v>
-      </c>
       <c r="F195" s="3" t="s">
-        <v>871</v>
+        <v>779</v>
       </c>
       <c r="G195" s="3" t="s">
         <v>129</v>
@@ -9486,25 +9497,25 @@
         <v>129</v>
       </c>
       <c r="L195" s="3" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
     </row>
     <row r="196" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A196" s="3" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="B196" s="3"/>
       <c r="C196" s="3" t="s">
+        <v>783</v>
+      </c>
+      <c r="D196" s="3" t="s">
+        <v>781</v>
+      </c>
+      <c r="E196" s="3" t="s">
+        <v>778</v>
+      </c>
+      <c r="F196" s="3" t="s">
         <v>782</v>
-      </c>
-      <c r="D196" s="3" t="s">
-        <v>779</v>
-      </c>
-      <c r="E196" s="3" t="s">
-        <v>780</v>
-      </c>
-      <c r="F196" s="3" t="s">
-        <v>781</v>
       </c>
       <c r="G196" s="3" t="s">
         <v>129</v>
@@ -9520,25 +9531,25 @@
         <v>129</v>
       </c>
       <c r="L196" s="3" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
     </row>
     <row r="197" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A197" s="3" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="B197" s="3"/>
       <c r="C197" s="3" t="s">
+        <v>787</v>
+      </c>
+      <c r="D197" s="3" t="s">
+        <v>784</v>
+      </c>
+      <c r="E197" s="3" t="s">
         <v>785</v>
       </c>
-      <c r="D197" s="3" t="s">
-        <v>783</v>
-      </c>
-      <c r="E197" s="3" t="s">
-        <v>780</v>
-      </c>
       <c r="F197" s="3" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="G197" s="3" t="s">
         <v>129</v>
@@ -9554,93 +9565,93 @@
         <v>129</v>
       </c>
       <c r="L197" s="3" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
     </row>
     <row r="198" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A198" s="3" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="B198" s="3"/>
       <c r="C198" s="3" t="s">
+        <v>794</v>
+      </c>
+      <c r="D198" s="3" t="s">
+        <v>788</v>
+      </c>
+      <c r="E198" s="3" t="s">
         <v>789</v>
       </c>
-      <c r="D198" s="3" t="s">
-        <v>786</v>
-      </c>
-      <c r="E198" s="3" t="s">
-        <v>787</v>
-      </c>
       <c r="F198" s="3" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="G198" s="3" t="s">
-        <v>129</v>
+        <v>791</v>
       </c>
       <c r="H198" s="3" t="s">
-        <v>130</v>
+        <v>792</v>
       </c>
       <c r="I198" s="3"/>
       <c r="J198" s="3" t="s">
         <v>131</v>
       </c>
       <c r="K198" s="3" t="s">
-        <v>129</v>
+        <v>791</v>
       </c>
       <c r="L198" s="3" t="s">
-        <v>769</v>
+        <v>793</v>
       </c>
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A199" s="3" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="B199" s="3"/>
       <c r="C199" s="3" t="s">
+        <v>799</v>
+      </c>
+      <c r="D199" s="3" t="s">
+        <v>795</v>
+      </c>
+      <c r="E199" s="3" t="s">
         <v>796</v>
       </c>
-      <c r="D199" s="3" t="s">
-        <v>790</v>
-      </c>
-      <c r="E199" s="3" t="s">
-        <v>791</v>
-      </c>
       <c r="F199" s="3" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="G199" s="3" t="s">
-        <v>793</v>
+        <v>264</v>
       </c>
       <c r="H199" s="3" t="s">
-        <v>794</v>
+        <v>263</v>
       </c>
       <c r="I199" s="3"/>
       <c r="J199" s="3" t="s">
-        <v>131</v>
+        <v>82</v>
       </c>
       <c r="K199" s="3" t="s">
-        <v>793</v>
+        <v>264</v>
       </c>
       <c r="L199" s="3" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
     </row>
     <row r="200" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A200" s="3" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="B200" s="3"/>
       <c r="C200" s="3" t="s">
         <v>801</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="E200" s="3" t="s">
-        <v>798</v>
+        <v>585</v>
       </c>
       <c r="F200" s="3" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="G200" s="3" t="s">
         <v>264</v>
@@ -9656,31 +9667,29 @@
         <v>264</v>
       </c>
       <c r="L200" s="3" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
     </row>
     <row r="201" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A201" s="3" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="B201" s="3"/>
       <c r="C201" s="3" t="s">
+        <v>805</v>
+      </c>
+      <c r="D201" s="3" t="s">
+        <v>802</v>
+      </c>
+      <c r="E201" s="3"/>
+      <c r="F201" s="3" t="s">
         <v>803</v>
-      </c>
-      <c r="D201" s="3" t="s">
-        <v>797</v>
-      </c>
-      <c r="E201" s="3" t="s">
-        <v>587</v>
-      </c>
-      <c r="F201" s="3" t="s">
-        <v>802</v>
       </c>
       <c r="G201" s="3" t="s">
         <v>264</v>
       </c>
       <c r="H201" s="3" t="s">
-        <v>263</v>
+        <v>444</v>
       </c>
       <c r="I201" s="3"/>
       <c r="J201" s="3" t="s">
@@ -9690,125 +9699,127 @@
         <v>264</v>
       </c>
       <c r="L201" s="3" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
     </row>
     <row r="202" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A202" s="3" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="B202" s="3"/>
       <c r="C202" s="3" t="s">
+        <v>810</v>
+      </c>
+      <c r="D202" s="3" t="s">
+        <v>806</v>
+      </c>
+      <c r="E202" s="3" t="s">
         <v>807</v>
       </c>
-      <c r="D202" s="3" t="s">
-        <v>804</v>
-      </c>
-      <c r="E202" s="3"/>
       <c r="F202" s="3" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="G202" s="3" t="s">
-        <v>264</v>
+        <v>202</v>
       </c>
       <c r="H202" s="3" t="s">
-        <v>446</v>
+        <v>121</v>
       </c>
       <c r="I202" s="3"/>
       <c r="J202" s="3" t="s">
-        <v>82</v>
+        <v>203</v>
       </c>
       <c r="K202" s="3" t="s">
-        <v>264</v>
+        <v>202</v>
       </c>
       <c r="L202" s="3" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
     </row>
     <row r="203" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A203" s="3" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="B203" s="3"/>
       <c r="C203" s="3" t="s">
+        <v>818</v>
+      </c>
+      <c r="D203" s="3" t="s">
+        <v>811</v>
+      </c>
+      <c r="E203" s="3" t="s">
         <v>812</v>
       </c>
-      <c r="D203" s="3" t="s">
-        <v>808</v>
-      </c>
-      <c r="E203" s="3" t="s">
-        <v>809</v>
-      </c>
       <c r="F203" s="3" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="G203" s="3" t="s">
-        <v>202</v>
+        <v>814</v>
       </c>
       <c r="H203" s="3" t="s">
-        <v>121</v>
+        <v>815</v>
       </c>
       <c r="I203" s="3"/>
       <c r="J203" s="3" t="s">
-        <v>203</v>
+        <v>816</v>
       </c>
       <c r="K203" s="3" t="s">
-        <v>202</v>
+        <v>814</v>
       </c>
       <c r="L203" s="3" t="s">
-        <v>811</v>
+        <v>817</v>
       </c>
     </row>
     <row r="204" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A204" s="3" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="B204" s="3"/>
       <c r="C204" s="3" t="s">
+        <v>823</v>
+      </c>
+      <c r="D204" s="3" t="s">
+        <v>819</v>
+      </c>
+      <c r="E204" s="3" t="s">
         <v>820</v>
       </c>
-      <c r="D204" s="3" t="s">
-        <v>813</v>
-      </c>
-      <c r="E204" s="3" t="s">
-        <v>814</v>
-      </c>
       <c r="F204" s="3" t="s">
-        <v>815</v>
+        <v>821</v>
       </c>
       <c r="G204" s="3" t="s">
-        <v>816</v>
+        <v>121</v>
       </c>
       <c r="H204" s="3" t="s">
-        <v>817</v>
+        <v>121</v>
       </c>
       <c r="I204" s="3"/>
       <c r="J204" s="3" t="s">
-        <v>818</v>
+        <v>82</v>
       </c>
       <c r="K204" s="3" t="s">
-        <v>816</v>
+        <v>121</v>
       </c>
       <c r="L204" s="3" t="s">
-        <v>819</v>
+        <v>822</v>
       </c>
     </row>
     <row r="205" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A205" s="3" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="B205" s="3"/>
       <c r="C205" s="3" t="s">
+        <v>826</v>
+      </c>
+      <c r="D205" s="3" t="s">
+        <v>819</v>
+      </c>
+      <c r="E205" s="3" t="s">
+        <v>824</v>
+      </c>
+      <c r="F205" s="3" t="s">
         <v>825</v>
-      </c>
-      <c r="D205" s="3" t="s">
-        <v>821</v>
-      </c>
-      <c r="E205" s="3" t="s">
-        <v>822</v>
-      </c>
-      <c r="F205" s="3" t="s">
-        <v>823</v>
       </c>
       <c r="G205" s="3" t="s">
         <v>121</v>
@@ -9824,65 +9835,65 @@
         <v>121</v>
       </c>
       <c r="L205" s="3" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
     </row>
     <row r="206" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A206" s="3" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="B206" s="3"/>
       <c r="C206" s="3" t="s">
+        <v>831</v>
+      </c>
+      <c r="D206" s="3" t="s">
+        <v>827</v>
+      </c>
+      <c r="E206" s="3" t="s">
         <v>828</v>
       </c>
-      <c r="D206" s="3" t="s">
-        <v>821</v>
-      </c>
-      <c r="E206" s="3" t="s">
-        <v>826</v>
-      </c>
       <c r="F206" s="3" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="G206" s="3" t="s">
-        <v>121</v>
+        <v>264</v>
       </c>
       <c r="H206" s="3" t="s">
-        <v>121</v>
+        <v>444</v>
       </c>
       <c r="I206" s="3"/>
       <c r="J206" s="3" t="s">
         <v>82</v>
       </c>
       <c r="K206" s="3" t="s">
-        <v>121</v>
+        <v>264</v>
       </c>
       <c r="L206" s="3" t="s">
-        <v>824</v>
+        <v>830</v>
       </c>
     </row>
     <row r="207" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A207" s="3" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="B207" s="3"/>
       <c r="C207" s="3" t="s">
         <v>833</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="E207" s="3" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="F207" s="3" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="G207" s="3" t="s">
         <v>264</v>
       </c>
       <c r="H207" s="3" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="I207" s="3"/>
       <c r="J207" s="3" t="s">
@@ -9892,91 +9903,89 @@
         <v>264</v>
       </c>
       <c r="L207" s="3" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
     </row>
     <row r="208" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A208" s="3" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="B208" s="3"/>
       <c r="C208" s="3" t="s">
+        <v>837</v>
+      </c>
+      <c r="D208" s="3" t="s">
+        <v>834</v>
+      </c>
+      <c r="E208" s="3" t="s">
         <v>835</v>
       </c>
-      <c r="D208" s="3" t="s">
-        <v>829</v>
-      </c>
-      <c r="E208" s="3" t="s">
-        <v>830</v>
-      </c>
       <c r="F208" s="3" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="G208" s="3" t="s">
-        <v>264</v>
+        <v>814</v>
       </c>
       <c r="H208" s="3" t="s">
-        <v>446</v>
+        <v>815</v>
       </c>
       <c r="I208" s="3"/>
       <c r="J208" s="3" t="s">
-        <v>82</v>
+        <v>816</v>
       </c>
       <c r="K208" s="3" t="s">
-        <v>264</v>
+        <v>814</v>
       </c>
       <c r="L208" s="3" t="s">
-        <v>832</v>
+        <v>817</v>
       </c>
     </row>
     <row r="209" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A209" s="3" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="B209" s="3"/>
       <c r="C209" s="3" t="s">
+        <v>841</v>
+      </c>
+      <c r="D209" s="3" t="s">
+        <v>838</v>
+      </c>
+      <c r="E209" s="3"/>
+      <c r="F209" s="3" t="s">
         <v>839</v>
       </c>
-      <c r="D209" s="3" t="s">
-        <v>836</v>
-      </c>
-      <c r="E209" s="3" t="s">
-        <v>837</v>
-      </c>
-      <c r="F209" s="3" t="s">
-        <v>838</v>
-      </c>
       <c r="G209" s="3" t="s">
-        <v>816</v>
+        <v>264</v>
       </c>
       <c r="H209" s="3" t="s">
-        <v>817</v>
+        <v>263</v>
       </c>
       <c r="I209" s="3"/>
       <c r="J209" s="3" t="s">
-        <v>818</v>
+        <v>82</v>
       </c>
       <c r="K209" s="3" t="s">
-        <v>816</v>
+        <v>264</v>
       </c>
       <c r="L209" s="3" t="s">
-        <v>819</v>
+        <v>840</v>
       </c>
     </row>
     <row r="210" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A210" s="3" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="B210" s="3"/>
       <c r="C210" s="3" t="s">
         <v>843</v>
       </c>
       <c r="D210" s="3" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="E210" s="3"/>
       <c r="F210" s="3" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="G210" s="3" t="s">
         <v>264</v>
@@ -9992,241 +10001,263 @@
         <v>264</v>
       </c>
       <c r="L210" s="3" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="211" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A211" s="3" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="B211" s="3"/>
       <c r="C211" s="3" t="s">
+        <v>870</v>
+      </c>
+      <c r="D211" s="3" t="s">
+        <v>844</v>
+      </c>
+      <c r="E211" s="3" t="s">
         <v>845</v>
       </c>
-      <c r="D211" s="3" t="s">
-        <v>840</v>
-      </c>
-      <c r="E211" s="3"/>
-      <c r="F211" s="3" t="s">
-        <v>844</v>
-      </c>
+      <c r="F211" s="3"/>
       <c r="G211" s="3" t="s">
-        <v>264</v>
+        <v>246</v>
       </c>
       <c r="H211" s="3" t="s">
-        <v>263</v>
+        <v>244</v>
       </c>
       <c r="I211" s="3"/>
       <c r="J211" s="3" t="s">
-        <v>82</v>
+        <v>245</v>
       </c>
       <c r="K211" s="3" t="s">
-        <v>264</v>
+        <v>246</v>
       </c>
       <c r="L211" s="3" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
     </row>
     <row r="212" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A212" s="3" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="B212" s="3"/>
       <c r="C212" s="3" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="D212" s="3" t="s">
-        <v>846</v>
+        <v>877</v>
       </c>
       <c r="E212" s="3" t="s">
-        <v>847</v>
-      </c>
-      <c r="F212" s="3"/>
+        <v>378</v>
+      </c>
+      <c r="F212" s="3" t="s">
+        <v>874</v>
+      </c>
       <c r="G212" s="3" t="s">
-        <v>246</v>
+        <v>129</v>
       </c>
       <c r="H212" s="3" t="s">
-        <v>244</v>
+        <v>130</v>
       </c>
       <c r="I212" s="3"/>
       <c r="J212" s="3" t="s">
-        <v>245</v>
+        <v>131</v>
       </c>
       <c r="K212" s="3" t="s">
-        <v>246</v>
+        <v>129</v>
       </c>
       <c r="L212" s="3" t="s">
-        <v>848</v>
+        <v>379</v>
       </c>
     </row>
     <row r="213" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A213" s="3" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="B213" s="3"/>
       <c r="C213" s="3" t="s">
-        <v>849</v>
+        <v>875</v>
       </c>
       <c r="D213" s="3" t="s">
-        <v>850</v>
-      </c>
-      <c r="E213" s="3" t="s">
-        <v>851</v>
-      </c>
-      <c r="F213" s="3" t="s">
-        <v>852</v>
-      </c>
-      <c r="G213" s="3" t="s">
-        <v>853</v>
-      </c>
-      <c r="H213" s="3" t="s">
-        <v>817</v>
-      </c>
+        <v>876</v>
+      </c>
+      <c r="E213" s="3"/>
+      <c r="F213" s="3"/>
+      <c r="G213" s="3"/>
+      <c r="H213" s="3"/>
       <c r="I213" s="3"/>
-      <c r="J213" s="3" t="s">
-        <v>854</v>
-      </c>
-      <c r="K213" s="3" t="s">
-        <v>853</v>
-      </c>
-      <c r="L213" s="3" t="s">
-        <v>855</v>
-      </c>
+      <c r="J213" s="3"/>
+      <c r="K213" s="3"/>
+      <c r="L213" s="3"/>
     </row>
     <row r="214" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A214" s="3" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="B214" s="3"/>
       <c r="C214" s="3" t="s">
+        <v>847</v>
+      </c>
+      <c r="D214" s="3" t="s">
+        <v>848</v>
+      </c>
+      <c r="E214" s="3" t="s">
         <v>849</v>
       </c>
-      <c r="D214" s="3" t="s">
+      <c r="F214" s="3" t="s">
         <v>850</v>
       </c>
-      <c r="E214" s="3" t="s">
-        <v>856</v>
-      </c>
-      <c r="F214" s="3" t="s">
-        <v>857</v>
-      </c>
       <c r="G214" s="3" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="H214" s="3" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="I214" s="3"/>
       <c r="J214" s="3" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="K214" s="3" t="s">
+        <v>851</v>
+      </c>
+      <c r="L214" s="3" t="s">
         <v>853</v>
-      </c>
-      <c r="L214" s="3" t="s">
-        <v>855</v>
       </c>
     </row>
     <row r="215" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A215" s="3" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="B215" s="3"/>
       <c r="C215" s="3" t="s">
-        <v>858</v>
+        <v>847</v>
       </c>
       <c r="D215" s="3" t="s">
-        <v>859</v>
+        <v>848</v>
       </c>
       <c r="E215" s="3" t="s">
+        <v>854</v>
+      </c>
+      <c r="F215" s="3" t="s">
+        <v>855</v>
+      </c>
+      <c r="G215" s="3" t="s">
         <v>851</v>
       </c>
-      <c r="F215" s="3" t="s">
-        <v>860</v>
-      </c>
-      <c r="G215" s="3" t="s">
-        <v>853</v>
-      </c>
       <c r="H215" s="3" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="I215" s="3"/>
       <c r="J215" s="3" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="K215" s="3" t="s">
+        <v>851</v>
+      </c>
+      <c r="L215" s="3" t="s">
         <v>853</v>
-      </c>
-      <c r="L215" s="3" t="s">
-        <v>861</v>
       </c>
     </row>
     <row r="216" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A216" s="3" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="B216" s="3"/>
       <c r="C216" s="3" t="s">
+        <v>856</v>
+      </c>
+      <c r="D216" s="3" t="s">
+        <v>857</v>
+      </c>
+      <c r="E216" s="3" t="s">
+        <v>849</v>
+      </c>
+      <c r="F216" s="3" t="s">
         <v>858</v>
       </c>
-      <c r="D216" s="3" t="s">
-        <v>859</v>
-      </c>
-      <c r="E216" s="3" t="s">
-        <v>856</v>
-      </c>
-      <c r="F216" s="3" t="s">
-        <v>862</v>
-      </c>
       <c r="G216" s="3" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="H216" s="3" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="I216" s="3"/>
       <c r="J216" s="3" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="K216" s="3" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="L216" s="3" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
     </row>
     <row r="217" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A217" s="3" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="B217" s="3"/>
       <c r="C217" s="3" t="s">
-        <v>863</v>
+        <v>856</v>
       </c>
       <c r="D217" s="3" t="s">
-        <v>864</v>
+        <v>857</v>
       </c>
       <c r="E217" s="3" t="s">
+        <v>854</v>
+      </c>
+      <c r="F217" s="3" t="s">
+        <v>860</v>
+      </c>
+      <c r="G217" s="3" t="s">
         <v>851</v>
       </c>
-      <c r="F217" s="3" t="s">
-        <v>865</v>
-      </c>
-      <c r="G217" s="3" t="s">
-        <v>866</v>
-      </c>
       <c r="H217" s="3" t="s">
-        <v>866</v>
+        <v>815</v>
       </c>
       <c r="I217" s="3"/>
       <c r="J217" s="3" t="s">
+        <v>852</v>
+      </c>
+      <c r="K217" s="3" t="s">
+        <v>851</v>
+      </c>
+      <c r="L217" s="3" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="218" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A218" s="3" t="s">
+        <v>762</v>
+      </c>
+      <c r="B218" s="3"/>
+      <c r="C218" s="3" t="s">
+        <v>861</v>
+      </c>
+      <c r="D218" s="3" t="s">
+        <v>862</v>
+      </c>
+      <c r="E218" s="3" t="s">
+        <v>849</v>
+      </c>
+      <c r="F218" s="3" t="s">
+        <v>863</v>
+      </c>
+      <c r="G218" s="3" t="s">
+        <v>864</v>
+      </c>
+      <c r="H218" s="3" t="s">
+        <v>864</v>
+      </c>
+      <c r="I218" s="3"/>
+      <c r="J218" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="K217" s="3" t="s">
-        <v>866</v>
-      </c>
-      <c r="L217" s="3" t="s">
-        <v>855</v>
+      <c r="K218" s="3" t="s">
+        <v>864</v>
+      </c>
+      <c r="L218" s="3" t="s">
+        <v>853</v>
       </c>
     </row>
   </sheetData>
